--- a/TABLERO_PA_C.xlsx
+++ b/TABLERO_PA_C.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="202300"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e2a95cfba4fb0187/Escritorio/Tableros de Control/2. Contraloría/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="304" documentId="13_ncr:1_{5037B3AD-B0A2-4521-8F49-D3B2F1605E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2A565F5-459A-43AC-82A5-1EEBC90AFBF6}"/>
+  <xr:revisionPtr revIDLastSave="379" documentId="13_ncr:1_{5037B3AD-B0A2-4521-8F49-D3B2F1605E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F711A8B7-0757-46FA-91A0-512815830261}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="10" xr2:uid="{E38B2051-8614-49B4-943E-B3707D980583}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="10" xr2:uid="{E38B2051-8614-49B4-943E-B3707D980583}"/>
   </bookViews>
   <sheets>
     <sheet name="Tablero" sheetId="3" r:id="rId1"/>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2575" uniqueCount="798">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2577" uniqueCount="800">
   <si>
     <t>No.</t>
   </si>
@@ -2680,6 +2680,12 @@
   </si>
   <si>
     <t>0.5</t>
+  </si>
+  <si>
+    <t>Se implementa el Manual Gestión Inmobiliaria Código: GIM-MN01, con el fin de proporcionar al personal involucrado en el proces, una guía que regule su accionar en las actividades administrativas y de control inherentes a los bienes inmuebles de la TTSA.</t>
+  </si>
+  <si>
+    <t>Se verifica la efectividad de la acción mediante la Resolución No. 0090 del 25/03/2026 de la Secretaría de Hacienda de Soacha (saneamiento de intereses moratorios) y el Recibo de Impuesto Predial No. 26982690 (Vigencias 2025-2026). Los soportes acreditan la depuración de la cartera y la actualización oficial del área del predio</t>
   </si>
 </sst>
 </file>
@@ -2868,7 +2874,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2992,6 +2998,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3193,7 +3205,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="233">
+  <cellXfs count="235">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3837,6 +3849,9 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="19" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3854,6 +3869,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -5358,21 +5376,6 @@
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="3" tint="0.499984740745262"/>
@@ -5479,6 +5482,21 @@
     </dxf>
     <dxf>
       <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
@@ -13287,7 +13305,9 @@
           <cell r="G5" t="str">
             <v>SUB GERENCIA DE SERVICIOS OPERACIONALES E INFRAESTRUCTURA</v>
           </cell>
-          <cell r="S5"/>
+          <cell r="S5">
+            <v>46203</v>
+          </cell>
         </row>
         <row r="6">
           <cell r="A6" t="str">
@@ -15016,7 +15036,9 @@
           <cell r="G142" t="str">
             <v>SUB GERENCIA DE SERVICIOS OPERACIONALES E INFRAESTRUCTURA</v>
           </cell>
-          <cell r="S142"/>
+          <cell r="S142">
+            <v>46203</v>
+          </cell>
         </row>
         <row r="143">
           <cell r="A143" t="str">
@@ -15028,7 +15050,9 @@
           <cell r="G143" t="str">
             <v>SUB GERENCIA DE SERVICIOS OPERACIONALES E INFRAESTRUCTURA</v>
           </cell>
-          <cell r="S143"/>
+          <cell r="S143">
+            <v>46203</v>
+          </cell>
         </row>
         <row r="144">
           <cell r="A144" t="str">
@@ -15052,7 +15076,9 @@
           <cell r="G145" t="str">
             <v>SUB GERENCIA DE SERVICIOS OPERACIONALES E INFRAESTRUCTURA</v>
           </cell>
-          <cell r="S145"/>
+          <cell r="S145">
+            <v>46203</v>
+          </cell>
         </row>
         <row r="146">
           <cell r="A146" t="str">
@@ -15064,7 +15090,9 @@
           <cell r="G146" t="str">
             <v>SUB GERENCIA DE SERVICIOS OPERACIONALES E INFRAESTRUCTURA</v>
           </cell>
-          <cell r="S146"/>
+          <cell r="S146">
+            <v>46203</v>
+          </cell>
         </row>
         <row r="147">
           <cell r="A147" t="str">
@@ -15100,7 +15128,9 @@
           <cell r="G149" t="str">
             <v>DIRECCIÓN DE SEGURIDAD OPERACIONAL</v>
           </cell>
-          <cell r="S149"/>
+          <cell r="S149">
+            <v>46161</v>
+          </cell>
         </row>
         <row r="150">
           <cell r="A150" t="str">
@@ -20464,129 +20494,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B6C7AB91-8822-4E2E-BE9B-A9578BEEAA20}" name="TablaDinámica3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:G7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="19">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-    <i i="2">
-      <x v="2"/>
-    </i>
-    <i i="3">
-      <x v="3"/>
-    </i>
-    <i i="4">
-      <x v="4"/>
-    </i>
-    <i i="5">
-      <x v="5"/>
-    </i>
-  </colItems>
-  <dataFields count="6">
-    <dataField name="Cuenta de No. Hallazgo" fld="2" subtotal="count" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Total Planes de acción" fld="5" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Abiertos" fld="6" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Vencidos" fld="7" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Finalizados" fld="8" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Auditoría" fld="1" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="5">
-    <format dxfId="240">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="239">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="238">
-      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0"/>
-    </format>
-    <format dxfId="237">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="236">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="4">
-            <x v="0"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5E7F1577-F431-4B0C-B786-3FF0F4829E0F}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A9:E35" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
@@ -20780,6 +20687,255 @@
     <dataField name="Suma de Finalizados" fld="8" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="20">
+    <format dxfId="255">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="254">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="253">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0"/>
+    </format>
+    <format dxfId="252">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="251">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="250">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="249">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="248">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="247">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="14"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="246">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="19"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="245">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="20"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="244">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="23"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="243">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="25"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="242">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="42"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="241">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="43"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="240">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="44"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="239">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="46"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="238">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="47"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="237">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="50"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="236">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="12"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B6C7AB91-8822-4E2E-BE9B-A9578BEEAA20}" name="TablaDinámica3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:G7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="19">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+    <i i="3">
+      <x v="3"/>
+    </i>
+    <i i="4">
+      <x v="4"/>
+    </i>
+    <i i="5">
+      <x v="5"/>
+    </i>
+  </colItems>
+  <dataFields count="6">
+    <dataField name="Cuenta de No. Hallazgo" fld="2" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Total Planes de acción" fld="5" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Abiertos" fld="6" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Vencidos" fld="7" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Finalizados" fld="8" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Auditoría" fld="1" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="5">
     <format dxfId="260">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
@@ -20793,139 +20949,13 @@
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
     <format dxfId="256">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="3" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="255">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="254">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="253">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="252">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="14"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="251">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="19"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="250">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="20"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="249">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="23"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="248">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="25"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="247">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="42"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="246">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="43"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="245">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="44"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="244">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="46"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="243">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="47"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="242">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="50"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="241">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="12"/>
+          <reference field="4294967294" count="4">
+            <x v="0"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
           </reference>
         </references>
       </pivotArea>
@@ -27750,6 +27780,80 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A9C7B425-127F-4B5F-B2E3-C2AB4F050E7C}" name="TablaDinámica3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A12:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="19">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Suma de Total Planes de acción" fld="5" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="1">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="0">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{53017CE7-FCFE-4C73-9C32-3A18A27FC23C}" name="TablaDinámica7" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
   <location ref="F13:G16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
@@ -27924,7 +28028,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DD0BBB6E-FA08-4903-950F-5C10965A7D8D}" name="TablaDinámica6" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A26:B31" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
@@ -28049,10 +28153,10 @@
     <dataField name="Suma de Finalizados" fld="8" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="1">
+    <format dxfId="3">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="0">
+    <format dxfId="2">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
   </formats>
@@ -28068,7 +28172,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3B3AE9AA-616F-416E-8D70-C9530CA01C24}" name="TablaDinámica4" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A19:B23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
@@ -28119,85 +28223,11 @@
     <dataField name="Suma de Alerta 30" fld="11" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="3">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="2">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A9C7B425-127F-4B5F-B2E3-C2AB4F050E7C}" name="TablaDinámica3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A12:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="19">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Suma de Total Planes de acción" fld="5" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="2">
     <format dxfId="5">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
     <format dxfId="4">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
@@ -29014,8 +29044,8 @@
     <col min="21" max="21" width="47.109375" style="58" customWidth="1"/>
     <col min="22" max="22" width="19.21875" style="140" customWidth="1"/>
     <col min="23" max="23" width="26.21875" style="218" customWidth="1"/>
-    <col min="24" max="24" width="20.109375" style="58" customWidth="1"/>
-    <col min="25" max="25" width="20.33203125" style="58" customWidth="1"/>
+    <col min="24" max="24" width="20.109375" style="58" hidden="1" customWidth="1"/>
+    <col min="25" max="25" width="20.33203125" style="58" hidden="1" customWidth="1"/>
     <col min="26" max="26" width="39.109375" style="133" customWidth="1"/>
     <col min="27" max="27" width="16.77734375" style="58" customWidth="1"/>
     <col min="28" max="28" width="38.5546875" style="58" customWidth="1"/>
@@ -29071,7 +29101,7 @@
       <c r="N1" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="56" t="s">
+      <c r="O1" s="227" t="s">
         <v>13</v>
       </c>
       <c r="P1" s="210" t="s">
@@ -29896,107 +29926,111 @@
       </c>
     </row>
     <row r="9" spans="1:36" ht="136.80000000000001">
-      <c r="A9" s="59">
+      <c r="A9" s="141">
         <v>193</v>
       </c>
-      <c r="B9" s="60" t="s">
+      <c r="B9" s="75" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="60" t="s">
+      <c r="C9" s="75" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="60" t="s">
+      <c r="D9" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="60" t="s">
+      <c r="E9" s="75" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="60">
+      <c r="F9" s="75">
         <v>2025</v>
       </c>
-      <c r="G9" s="60">
+      <c r="G9" s="75">
         <v>90</v>
       </c>
-      <c r="H9" s="60" t="s">
+      <c r="H9" s="75" t="s">
         <v>80</v>
       </c>
-      <c r="I9" s="60">
+      <c r="I9" s="75">
         <v>1</v>
       </c>
-      <c r="J9" s="61" t="s">
+      <c r="J9" s="162" t="s">
         <v>31</v>
       </c>
-      <c r="K9" s="62"/>
-      <c r="L9" s="60" t="s">
+      <c r="K9" s="234"/>
+      <c r="L9" s="75" t="s">
         <v>32</v>
       </c>
-      <c r="M9" s="60"/>
-      <c r="N9" s="60"/>
-      <c r="O9" s="60" t="s">
+      <c r="M9" s="75"/>
+      <c r="N9" s="75"/>
+      <c r="O9" s="75" t="s">
         <v>81</v>
       </c>
-      <c r="P9" s="60" t="s">
+      <c r="P9" s="75" t="s">
         <v>82</v>
       </c>
-      <c r="Q9" s="60" t="s">
+      <c r="Q9" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="R9" s="60" t="s">
+      <c r="R9" s="75" t="s">
         <v>84</v>
       </c>
-      <c r="S9" s="60" t="s">
+      <c r="S9" s="75" t="s">
         <v>85</v>
       </c>
-      <c r="T9" s="60">
+      <c r="T9" s="75">
         <v>100</v>
       </c>
-      <c r="U9" s="60" t="s">
+      <c r="U9" s="75" t="s">
         <v>679</v>
       </c>
-      <c r="V9" s="137" t="s">
+      <c r="V9" s="142" t="s">
         <v>38</v>
       </c>
-      <c r="W9" s="137" t="s">
+      <c r="W9" s="142" t="s">
         <v>86</v>
       </c>
-      <c r="X9" s="60" t="s">
+      <c r="X9" s="75" t="s">
         <v>40</v>
       </c>
-      <c r="Y9" s="60" t="s">
+      <c r="Y9" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="Z9" s="129"/>
-      <c r="AA9" s="64" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB9" s="97" t="s">
+      <c r="Z9" s="144" t="s">
+        <v>798</v>
+      </c>
+      <c r="AA9" s="145" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB9" s="146" t="s">
         <v>87</v>
       </c>
-      <c r="AC9" s="66">
+      <c r="AC9" s="147" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="AD9" s="67">
+        <v/>
+      </c>
+      <c r="AD9" s="148">
         <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="AE9" s="67">
+      <c r="AE9" s="148">
         <f t="shared" ca="1" si="2"/>
         <v>0</v>
       </c>
-      <c r="AF9" s="67">
+      <c r="AF9" s="148">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="AG9" s="67">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="148">
         <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
-      <c r="AH9" s="94" t="s">
+      <c r="AH9" s="149" t="s">
         <v>646</v>
       </c>
-      <c r="AI9" s="67"/>
-      <c r="AJ9" s="67">
+      <c r="AI9" s="220">
+        <v>46293</v>
+      </c>
+      <c r="AJ9" s="148">
         <v>1</v>
       </c>
     </row>
@@ -30070,16 +30104,18 @@
       <c r="Y10" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="Z10" s="129"/>
+      <c r="Z10" s="129" t="s">
+        <v>799</v>
+      </c>
       <c r="AA10" s="64" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AB10" s="97" t="s">
         <v>94</v>
       </c>
-      <c r="AC10" s="66">
+      <c r="AC10" s="66" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>28</v>
+        <v/>
       </c>
       <c r="AD10" s="67">
         <f t="shared" ca="1" si="1"/>
@@ -30091,7 +30127,7 @@
       </c>
       <c r="AF10" s="67">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG10" s="67">
         <f t="shared" ca="1" si="4"/>
@@ -30100,7 +30136,9 @@
       <c r="AH10" s="94" t="s">
         <v>645</v>
       </c>
-      <c r="AI10" s="67"/>
+      <c r="AI10" s="98">
+        <v>46293</v>
+      </c>
       <c r="AJ10" s="67">
         <v>0.33</v>
       </c>
@@ -30184,7 +30222,7 @@
       </c>
       <c r="AC11" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="AD11" s="67">
         <f t="shared" ca="1" si="1"/>
@@ -30192,11 +30230,11 @@
       </c>
       <c r="AE11" s="67">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF11" s="67">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG11" s="67">
         <f t="shared" ca="1" si="4"/>
@@ -30289,7 +30327,7 @@
       </c>
       <c r="AC12" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="AD12" s="67">
         <f t="shared" ca="1" si="1"/>
@@ -30297,11 +30335,11 @@
       </c>
       <c r="AE12" s="67">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF12" s="67">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG12" s="67">
         <f t="shared" ca="1" si="4"/>
@@ -30424,7 +30462,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="14" spans="1:36" ht="125.4">
+    <row r="14" spans="1:36" ht="136.80000000000001">
       <c r="A14" s="59">
         <v>200</v>
       </c>
@@ -30721,7 +30759,7 @@
       </c>
       <c r="AC16" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="AD16" s="67">
         <f t="shared" ca="1" si="1"/>
@@ -30729,11 +30767,11 @@
       </c>
       <c r="AE16" s="67">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF16" s="67">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG16" s="67">
         <f t="shared" ca="1" si="4"/>
@@ -31607,7 +31645,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="25" spans="1:36" ht="193.8">
+    <row r="25" spans="1:36" ht="205.2">
       <c r="A25" s="59">
         <v>245</v>
       </c>
@@ -31716,7 +31754,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="26" spans="1:36" ht="136.80000000000001">
+    <row r="26" spans="1:36" ht="148.19999999999999">
       <c r="A26" s="59">
         <v>246</v>
       </c>
@@ -31795,7 +31833,7 @@
       </c>
       <c r="AC26" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="AD26" s="67">
         <f t="shared" ca="1" si="1"/>
@@ -31803,11 +31841,11 @@
       </c>
       <c r="AE26" s="67">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF26" s="67">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG26" s="67">
         <f t="shared" ca="1" si="4"/>
@@ -31900,7 +31938,7 @@
       </c>
       <c r="AC27" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="AD27" s="67">
         <f t="shared" ca="1" si="1"/>
@@ -31908,11 +31946,11 @@
       </c>
       <c r="AE27" s="67">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF27" s="67">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG27" s="67">
         <f t="shared" ca="1" si="4"/>
@@ -32005,7 +32043,7 @@
       </c>
       <c r="AC28" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="AD28" s="67">
         <f t="shared" ca="1" si="1"/>
@@ -32013,11 +32051,11 @@
       </c>
       <c r="AE28" s="67">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF28" s="67">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG28" s="67">
         <f t="shared" ca="1" si="4"/>
@@ -32031,7 +32069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:36" ht="102.6">
+    <row r="29" spans="1:36" ht="114">
       <c r="A29" s="59">
         <v>256</v>
       </c>
@@ -32110,7 +32148,7 @@
       </c>
       <c r="AC29" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="AD29" s="67">
         <f t="shared" ca="1" si="1"/>
@@ -32118,11 +32156,11 @@
       </c>
       <c r="AE29" s="67">
         <f t="shared" ca="1" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF29" s="67">
         <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG29" s="67">
         <f t="shared" ca="1" si="4"/>
@@ -33753,7 +33791,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="45" spans="1:36" ht="125.4">
+    <row r="45" spans="1:36" ht="136.80000000000001">
       <c r="A45" s="83">
         <v>215</v>
       </c>
@@ -34290,7 +34328,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="50" spans="1:36" ht="205.2">
+    <row r="50" spans="1:36" ht="239.4">
       <c r="A50" s="59">
         <v>220</v>
       </c>
@@ -34825,7 +34863,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="55" spans="1:36" ht="125.4">
+    <row r="55" spans="1:36" ht="136.80000000000001">
       <c r="A55" s="78">
         <v>229</v>
       </c>
@@ -35907,7 +35945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:36" ht="171">
+    <row r="65" spans="1:36" ht="193.8">
       <c r="A65" s="59">
         <v>184</v>
       </c>
@@ -36020,7 +36058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:36" ht="205.2">
+    <row r="66" spans="1:36" ht="239.4">
       <c r="A66" s="59">
         <v>186</v>
       </c>
@@ -36133,7 +36171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:36" ht="171">
+    <row r="67" spans="1:36" ht="193.8">
       <c r="A67" s="59">
         <v>187</v>
       </c>
@@ -36246,7 +36284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:36" ht="171">
+    <row r="68" spans="1:36" ht="193.8">
       <c r="A68" s="59">
         <v>188</v>
       </c>
@@ -36470,7 +36508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:36" ht="228">
+    <row r="70" spans="1:36" ht="239.4">
       <c r="A70" s="59">
         <v>221</v>
       </c>
@@ -36581,7 +36619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:36" ht="239.4">
+    <row r="71" spans="1:36" ht="262.2">
       <c r="A71" s="59">
         <v>222</v>
       </c>
@@ -36692,7 +36730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:36" ht="228">
+    <row r="72" spans="1:36" ht="239.4">
       <c r="A72" s="78">
         <v>224</v>
       </c>
@@ -36916,7 +36954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:36" ht="193.8">
+    <row r="74" spans="1:36" ht="228">
       <c r="A74" s="59">
         <v>232</v>
       </c>
@@ -37140,7 +37178,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="76" spans="1:36" ht="262.2">
+    <row r="76" spans="1:36" ht="273.60000000000002">
       <c r="A76" s="59">
         <v>234</v>
       </c>
@@ -37364,7 +37402,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="78" spans="1:36" ht="262.2">
+    <row r="78" spans="1:36" ht="273.60000000000002">
       <c r="A78" s="59">
         <v>236</v>
       </c>
@@ -37477,7 +37515,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="79" spans="1:36" ht="159.6">
+    <row r="79" spans="1:36" ht="171">
       <c r="A79" s="59">
         <v>237</v>
       </c>
@@ -37812,7 +37850,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="82" spans="1:36" ht="125.4">
+    <row r="82" spans="1:36" ht="136.80000000000001">
       <c r="A82" s="59">
         <v>241</v>
       </c>
@@ -38034,7 +38072,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="84" spans="1:36" ht="228">
+    <row r="84" spans="1:36" ht="239.4">
       <c r="A84" s="59">
         <v>243</v>
       </c>
@@ -38145,7 +38183,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="85" spans="1:36" ht="205.2">
+    <row r="85" spans="1:36" ht="228">
       <c r="A85" s="59">
         <v>244</v>
       </c>
@@ -39078,13 +39116,13 @@
       <c r="E6" s="16"/>
     </row>
     <row r="7" spans="3:14" ht="76.2" customHeight="1">
-      <c r="C7" s="231" t="s">
+      <c r="C7" s="232" t="s">
         <v>686</v>
       </c>
-      <c r="D7" s="231"/>
-      <c r="E7" s="231"/>
-      <c r="F7" s="231"/>
-      <c r="G7" s="231"/>
+      <c r="D7" s="232"/>
+      <c r="E7" s="232"/>
+      <c r="F7" s="232"/>
+      <c r="G7" s="232"/>
     </row>
     <row r="8" spans="3:14">
       <c r="C8" s="105" t="s">
@@ -39332,13 +39370,13 @@
       <c r="E17" s="16"/>
     </row>
     <row r="18" spans="3:14" ht="85.2" customHeight="1">
-      <c r="C18" s="232" t="s">
+      <c r="C18" s="233" t="s">
         <v>690</v>
       </c>
-      <c r="D18" s="232"/>
-      <c r="E18" s="232"/>
-      <c r="F18" s="232"/>
-      <c r="G18" s="232"/>
+      <c r="D18" s="233"/>
+      <c r="E18" s="233"/>
+      <c r="F18" s="233"/>
+      <c r="G18" s="233"/>
     </row>
     <row r="19" spans="3:14">
       <c r="C19" s="108" t="s">
@@ -39485,13 +39523,13 @@
       </c>
     </row>
     <row r="27" spans="3:14" ht="58.2" customHeight="1">
-      <c r="C27" s="231" t="s">
+      <c r="C27" s="232" t="s">
         <v>694</v>
       </c>
-      <c r="D27" s="231"/>
-      <c r="E27" s="231"/>
-      <c r="F27" s="231"/>
-      <c r="G27" s="231"/>
+      <c r="D27" s="232"/>
+      <c r="E27" s="232"/>
+      <c r="F27" s="232"/>
+      <c r="G27" s="232"/>
       <c r="J27" s="203" t="s">
         <v>777</v>
       </c>
@@ -39592,13 +39630,13 @@
       <c r="E34" s="16"/>
     </row>
     <row r="35" spans="3:14" ht="71.400000000000006" customHeight="1">
-      <c r="C35" s="231" t="s">
+      <c r="C35" s="232" t="s">
         <v>700</v>
       </c>
-      <c r="D35" s="231"/>
-      <c r="E35" s="231"/>
-      <c r="F35" s="231"/>
-      <c r="G35" s="231"/>
+      <c r="D35" s="232"/>
+      <c r="E35" s="232"/>
+      <c r="F35" s="232"/>
+      <c r="G35" s="232"/>
     </row>
     <row r="36" spans="3:14" ht="26.4" customHeight="1">
       <c r="C36" s="105" t="s">
@@ -39696,13 +39734,13 @@
       <c r="E42" s="16"/>
     </row>
     <row r="43" spans="3:14" ht="108.6" customHeight="1">
-      <c r="C43" s="231" t="s">
+      <c r="C43" s="232" t="s">
         <v>713</v>
       </c>
-      <c r="D43" s="231"/>
-      <c r="E43" s="231"/>
-      <c r="F43" s="231"/>
-      <c r="G43" s="231"/>
+      <c r="D43" s="232"/>
+      <c r="E43" s="232"/>
+      <c r="F43" s="232"/>
+      <c r="G43" s="232"/>
     </row>
     <row r="45" spans="3:14">
       <c r="C45" s="108" t="s">
@@ -39803,13 +39841,13 @@
       </c>
     </row>
     <row r="52" spans="3:14" ht="70.8" customHeight="1">
-      <c r="C52" s="231" t="s">
+      <c r="C52" s="232" t="s">
         <v>718</v>
       </c>
-      <c r="D52" s="231"/>
-      <c r="E52" s="231"/>
-      <c r="F52" s="231"/>
-      <c r="G52" s="231"/>
+      <c r="D52" s="232"/>
+      <c r="E52" s="232"/>
+      <c r="F52" s="232"/>
+      <c r="G52" s="232"/>
     </row>
     <row r="54" spans="3:14">
       <c r="C54" s="105" t="s">
@@ -40028,7 +40066,7 @@
   <dimension ref="A1:AF4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:32" ht="297.60000000000002">
+    <row r="1" spans="1:32" ht="307.2">
       <c r="A1" s="47">
         <v>70</v>
       </c>
@@ -40122,7 +40160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:32" ht="230.4">
+    <row r="2" spans="1:32" ht="240">
       <c r="A2" s="48">
         <v>113</v>
       </c>
@@ -40218,7 +40256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:32" ht="297.60000000000002">
+    <row r="3" spans="1:32" ht="307.2">
       <c r="A3" s="48">
         <v>114</v>
       </c>
@@ -40314,7 +40352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:32" ht="297.60000000000002">
+    <row r="4" spans="1:32" ht="316.8">
       <c r="A4" s="47">
         <v>185</v>
       </c>
@@ -41227,11 +41265,11 @@
       </c>
     </row>
     <row r="9" spans="3:15" ht="12">
-      <c r="C9" s="227" t="s">
+      <c r="C9" s="228" t="s">
         <v>752</v>
       </c>
-      <c r="D9" s="227"/>
-      <c r="E9" s="227"/>
+      <c r="D9" s="228"/>
+      <c r="E9" s="228"/>
       <c r="F9" s="185">
         <f>SUM(F6:F8)</f>
         <v>84</v>
@@ -41761,7 +41799,7 @@
       <c r="S37" s="177"/>
     </row>
     <row r="38" spans="11:19" ht="24">
-      <c r="K38" s="228" t="s">
+      <c r="K38" s="229" t="s">
         <v>735</v>
       </c>
       <c r="L38" s="179" t="s">
@@ -41783,7 +41821,7 @@
       <c r="S38" s="177"/>
     </row>
     <row r="39" spans="11:19" ht="12">
-      <c r="K39" s="229"/>
+      <c r="K39" s="230"/>
       <c r="L39" s="190">
         <f>+L16+L33</f>
         <v>84</v>
@@ -42080,7 +42118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="201.6">
+    <row r="10" spans="1:20" ht="216">
       <c r="A10" s="165"/>
       <c r="B10" s="20"/>
       <c r="C10" s="20" t="s">
@@ -42215,7 +42253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="100.8">
+    <row r="14" spans="1:20" ht="115.2">
       <c r="A14" s="165"/>
       <c r="B14" s="20"/>
       <c r="C14" s="20" t="s">
@@ -42911,7 +42949,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="163.19999999999999">
+    <row r="5" spans="2:9" ht="173.4">
       <c r="B5" s="200">
         <v>2025</v>
       </c>
@@ -42937,7 +42975,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="163.19999999999999">
+    <row r="6" spans="2:9" ht="173.4">
       <c r="B6" s="200">
         <v>2025</v>
       </c>
@@ -42963,7 +43001,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="163.19999999999999">
+    <row r="7" spans="2:9" ht="173.4">
       <c r="B7" s="200">
         <v>2025</v>
       </c>
@@ -43314,7 +43352,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="125.4">
+    <row r="8" spans="2:8" ht="136.80000000000001">
       <c r="B8" s="170">
         <v>2025</v>
       </c>
@@ -43364,7 +43402,7 @@
       <c r="D10" s="28" t="s">
         <v>215</v>
       </c>
-      <c r="E10" s="230" t="s">
+      <c r="E10" s="231" t="s">
         <v>216</v>
       </c>
       <c r="F10" s="171" t="s">
@@ -43385,7 +43423,7 @@
       <c r="D11" s="28" t="s">
         <v>215</v>
       </c>
-      <c r="E11" s="230"/>
+      <c r="E11" s="231"/>
       <c r="F11" s="171" t="s">
         <v>222</v>
       </c>
@@ -43822,7 +43860,7 @@
       </c>
       <c r="I8" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C8,'Base de Datos'!$G:$G,$D8,'Base de Datos'!$H:$H,$E8,'Base de Datos'!$U:$U,$F8,'Base de Datos'!$AA:$AA,"Abierta")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C8,'Base de Datos'!$G:$G,$D8,'Base de Datos'!$H:$H,$E8,'Base de Datos'!$U:$U,$F8,'Base de Datos'!$AA:$AA,"Vencida")</f>
@@ -43830,22 +43868,22 @@
       </c>
       <c r="K8" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C8,'Base de Datos'!$G:$G,$D8,'Base de Datos'!$H:$H,$E8,'Base de Datos'!$U:$U,$F8,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="29">
-        <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C8,'Base de Datos'!$G:$G,$D8,'Base de Datos'!$H:$H,$E8,'Base de Datos'!$U:$U,$F8,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
+        <f>COUNTIFS('Base de Datos'!$F:$F,$C8,'Base de Datos'!$G:$G,$D8,'Base de Datos'!$H:$H,$E8,'Base de Datos'!$U:$U,$F8,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
         <v>0</v>
       </c>
       <c r="M8" s="29">
-        <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C8,'Base de Datos'!$G:$G,$D8,'Base de Datos'!$H:$H,$E8,'Base de Datos'!$U:$U,$F8,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=20",'Base de Datos'!$AC:$AC,"&gt;10")</f>
+        <f>COUNTIFS('Base de Datos'!$F:$F,$C8,'Base de Datos'!$G:$G,$D8,'Base de Datos'!$H:$H,$E8,'Base de Datos'!$U:$U,$F8,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=20",'Base de Datos'!$AC:$AC,"&gt;10")</f>
         <v>0</v>
       </c>
       <c r="N8" s="32">
-        <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C8,'Base de Datos'!$G:$G,$D8,'Base de Datos'!$H:$H,$E8,'Base de Datos'!$U:$U,$F8,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=30",'Base de Datos'!$AC:$AC,"&gt;20")</f>
-        <v>1</v>
+        <f>COUNTIFS('Base de Datos'!$F:$F,$C8,'Base de Datos'!$G:$G,$D8,'Base de Datos'!$H:$H,$E8,'Base de Datos'!$U:$U,$F8,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=30",'Base de Datos'!$AC:$AC,"&gt;20")</f>
+        <v>0</v>
       </c>
       <c r="O8" s="29">
-        <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C8,'Base de Datos'!$G:$G,$D8,'Base de Datos'!$H:$H,$E8,'Base de Datos'!$U:$U,$F8,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AG:$AG,1)</f>
+        <f>COUNTIFS('Base de Datos'!$F:$F,$C8,'Base de Datos'!$G:$G,$D8,'Base de Datos'!$H:$H,$E8,'Base de Datos'!$U:$U,$F8,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AG:$AG,1)</f>
         <v>0</v>
       </c>
       <c r="P8" s="29" t="e">
@@ -43896,7 +43934,7 @@
       </c>
       <c r="I9" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C9,'Base de Datos'!$G:$G,$D9,'Base de Datos'!$H:$H,$E9,'Base de Datos'!$U:$U,$F9,'Base de Datos'!$AA:$AA,"Abierta")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C9,'Base de Datos'!$G:$G,$D9,'Base de Datos'!$H:$H,$E9,'Base de Datos'!$U:$U,$F9,'Base de Datos'!$AA:$AA,"Vencida")</f>
@@ -43904,22 +43942,22 @@
       </c>
       <c r="K9" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C9,'Base de Datos'!$G:$G,$D9,'Base de Datos'!$H:$H,$E9,'Base de Datos'!$U:$U,$F9,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="29">
-        <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C9,'Base de Datos'!$G:$G,$D9,'Base de Datos'!$H:$H,$E9,'Base de Datos'!$U:$U,$F9,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
+        <f>COUNTIFS('Base de Datos'!$F:$F,$C9,'Base de Datos'!$G:$G,$D9,'Base de Datos'!$H:$H,$E9,'Base de Datos'!$U:$U,$F9,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
         <v>0</v>
       </c>
       <c r="M9" s="29">
-        <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C9,'Base de Datos'!$G:$G,$D9,'Base de Datos'!$H:$H,$E9,'Base de Datos'!$U:$U,$F9,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=20",'Base de Datos'!$AC:$AC,"&gt;10")</f>
+        <f>COUNTIFS('Base de Datos'!$F:$F,$C9,'Base de Datos'!$G:$G,$D9,'Base de Datos'!$H:$H,$E9,'Base de Datos'!$U:$U,$F9,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=20",'Base de Datos'!$AC:$AC,"&gt;10")</f>
         <v>0</v>
       </c>
       <c r="N9" s="32">
-        <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C9,'Base de Datos'!$G:$G,$D9,'Base de Datos'!$H:$H,$E9,'Base de Datos'!$U:$U,$F9,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=30",'Base de Datos'!$AC:$AC,"&gt;20")</f>
-        <v>1</v>
+        <f>COUNTIFS('Base de Datos'!$F:$F,$C9,'Base de Datos'!$G:$G,$D9,'Base de Datos'!$H:$H,$E9,'Base de Datos'!$U:$U,$F9,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=30",'Base de Datos'!$AC:$AC,"&gt;20")</f>
+        <v>0</v>
       </c>
       <c r="O9" s="29">
-        <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C9,'Base de Datos'!$G:$G,$D9,'Base de Datos'!$H:$H,$E9,'Base de Datos'!$U:$U,$F9,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AG:$AG,1)</f>
+        <f>COUNTIFS('Base de Datos'!$F:$F,$C9,'Base de Datos'!$G:$G,$D9,'Base de Datos'!$H:$H,$E9,'Base de Datos'!$U:$U,$F9,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AG:$AG,1)</f>
         <v>0</v>
       </c>
       <c r="P9" s="29" t="e">
@@ -43986,11 +44024,11 @@
       </c>
       <c r="M10" s="29">
         <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C10,'Base de Datos'!$G:$G,$D10,'Base de Datos'!$H:$H,$E10,'Base de Datos'!$U:$U,$F10,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=20",'Base de Datos'!$AC:$AC,"&gt;10")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" s="32">
         <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C10,'Base de Datos'!$G:$G,$D10,'Base de Datos'!$H:$H,$E10,'Base de Datos'!$U:$U,$F10,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=30",'Base de Datos'!$AC:$AC,"&gt;20")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" s="29">
         <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C10,'Base de Datos'!$G:$G,$D10,'Base de Datos'!$H:$H,$E10,'Base de Datos'!$U:$U,$F10,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AG:$AG,1)</f>
@@ -44060,11 +44098,11 @@
       </c>
       <c r="M11" s="29">
         <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C11,'Base de Datos'!$G:$G,$D11,'Base de Datos'!$H:$H,$E11,'Base de Datos'!$U:$U,$F11,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=20",'Base de Datos'!$AC:$AC,"&gt;10")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" s="32">
         <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C11,'Base de Datos'!$G:$G,$D11,'Base de Datos'!$H:$H,$E11,'Base de Datos'!$U:$U,$F11,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=30",'Base de Datos'!$AC:$AC,"&gt;20")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" s="29">
         <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C11,'Base de Datos'!$G:$G,$D11,'Base de Datos'!$H:$H,$E11,'Base de Datos'!$U:$U,$F11,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AG:$AG,1)</f>
@@ -44356,11 +44394,11 @@
       </c>
       <c r="M15" s="29">
         <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C15,'Base de Datos'!$G:$G,$D15,'Base de Datos'!$H:$H,$E15,'Base de Datos'!$U:$U,$F15,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=20",'Base de Datos'!$AC:$AC,"&gt;10")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" s="32">
         <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C15,'Base de Datos'!$G:$G,$D15,'Base de Datos'!$H:$H,$E15,'Base de Datos'!$U:$U,$F15,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=30",'Base de Datos'!$AC:$AC,"&gt;20")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" s="29">
         <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C15,'Base de Datos'!$G:$G,$D15,'Base de Datos'!$H:$H,$E15,'Base de Datos'!$U:$U,$F15,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AG:$AG,1)</f>
@@ -45096,11 +45134,11 @@
       </c>
       <c r="M25" s="29">
         <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C25,'Base de Datos'!$G:$G,$D25,'Base de Datos'!$H:$H,$E25,'Base de Datos'!$U:$U,$F25,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=20",'Base de Datos'!$AC:$AC,"&gt;10")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N25" s="32">
         <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C25,'Base de Datos'!$G:$G,$D25,'Base de Datos'!$H:$H,$E25,'Base de Datos'!$U:$U,$F25,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=30",'Base de Datos'!$AC:$AC,"&gt;20")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O25" s="29">
         <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C25,'Base de Datos'!$G:$G,$D25,'Base de Datos'!$H:$H,$E25,'Base de Datos'!$U:$U,$F25,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AG:$AG,1)</f>
@@ -45174,11 +45212,11 @@
       </c>
       <c r="M26" s="29">
         <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C26,'Base de Datos'!$G:$G,$D26,'Base de Datos'!$H:$H,$E26,'Base de Datos'!$U:$U,$F26,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=20",'Base de Datos'!$AC:$AC,"&gt;10")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26" s="32">
         <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C26,'Base de Datos'!$G:$G,$D26,'Base de Datos'!$H:$H,$E26,'Base de Datos'!$U:$U,$F26,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=30",'Base de Datos'!$AC:$AC,"&gt;20")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26" s="29">
         <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C26,'Base de Datos'!$G:$G,$D26,'Base de Datos'!$H:$H,$E26,'Base de Datos'!$U:$U,$F26,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AG:$AG,1)</f>
@@ -45248,11 +45286,11 @@
       </c>
       <c r="M27" s="29">
         <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C27,'Base de Datos'!$G:$G,$D27,'Base de Datos'!$H:$H,$E27,'Base de Datos'!$U:$U,$F27,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=20",'Base de Datos'!$AC:$AC,"&gt;10")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" s="32">
         <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C27,'Base de Datos'!$G:$G,$D27,'Base de Datos'!$H:$H,$E27,'Base de Datos'!$U:$U,$F27,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=30",'Base de Datos'!$AC:$AC,"&gt;20")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27" s="29">
         <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C27,'Base de Datos'!$G:$G,$D27,'Base de Datos'!$H:$H,$E27,'Base de Datos'!$U:$U,$F27,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AG:$AG,1)</f>

--- a/TABLERO_PA_C.xlsx
+++ b/TABLERO_PA_C.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e2a95cfba4fb0187/Escritorio/Tableros de Control/2. Contraloría/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="379" documentId="13_ncr:1_{5037B3AD-B0A2-4521-8F49-D3B2F1605E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F711A8B7-0757-46FA-91A0-512815830261}"/>
+  <xr:revisionPtr revIDLastSave="468" documentId="13_ncr:1_{5037B3AD-B0A2-4521-8F49-D3B2F1605E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{006F8367-AF81-496C-A145-A8AEAF4ECE89}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="10" xr2:uid="{E38B2051-8614-49B4-943E-B3707D980583}"/>
   </bookViews>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2577" uniqueCount="800">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2577" uniqueCount="828">
   <si>
     <t>No.</t>
   </si>
@@ -2686,6 +2686,99 @@
   </si>
   <si>
     <t>Se verifica la efectividad de la acción mediante la Resolución No. 0090 del 25/03/2026 de la Secretaría de Hacienda de Soacha (saneamiento de intereses moratorios) y el Recibo de Impuesto Predial No. 26982690 (Vigencias 2025-2026). Los soportes acreditan la depuración de la cartera y la actualización oficial del área del predio</t>
+  </si>
+  <si>
+    <t>DIRECCIÓN DE GESTIÓN FINANCIERA 
+DIRECCIÓN DE RECURSOS FÍSICOS Y NEGOCIOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIRECCIÓN DE GESTIÓN FINANCIERA </t>
+  </si>
+  <si>
+    <t>DIRECCIÓN DE RECURSOS FÍSICOS Y NEGOCIOS</t>
+  </si>
+  <si>
+    <t>DIRECCIÓN DE GESTIÓN HUMANA</t>
+  </si>
+  <si>
+    <t>DIRECCIÓN DE RECURSOS FÍSICOS Y NEGOCIOS SUBGERENCIAJ URÍDICA</t>
+  </si>
+  <si>
+    <t>SUBGERENCIA JURÍDICA</t>
+  </si>
+  <si>
+    <t>DIRECCIÓN DE GESTIÓN FINANCIERA SUBGERENCIAJURÍDICA</t>
+  </si>
+  <si>
+    <t>DIRECCIÓN DE GESTIÓN FINANCIERA</t>
+  </si>
+  <si>
+    <t>SUBGERENCIA CORPORATIVA 
+DIRECCIÓN DE GESTIÓN FINANCIERA</t>
+  </si>
+  <si>
+    <t>SUBGERENCIA DE SERVICIOS PERACIONALES E INFRAESTRUCTURA</t>
+  </si>
+  <si>
+    <t>DIRECCIÓN DE SERVICIO AL TRANSPORTADOR DIRECCIÓN DE RECURSOST ECNOLÓGICOS</t>
+  </si>
+  <si>
+    <t>SUBGERENCIA CORPORATIVA</t>
+  </si>
+  <si>
+    <t>DIRECCIÓN DE INFRAESTRUCTURA</t>
+  </si>
+  <si>
+    <t>SUBGERENCIA DE SERVICIOS OPERACIONALES E INFRAESTRUCTURA</t>
+  </si>
+  <si>
+    <t>DIRECCIÓN DE RECURSOS TECNOLÓGICOS
+DIRECCIÓNDEGESTIÓNFINANCIERA</t>
+  </si>
+  <si>
+    <t>SUBGERENCIA CORPORATIVA 
+DIRECCIÓN DE RECURSOS TECNOLÓGICOS</t>
+  </si>
+  <si>
+    <t>DIRECCIÓN DE SERVICIO ALTRANSPORTADOR</t>
+  </si>
+  <si>
+    <t>DIRECCIÓN DE SERVICIO AL TRANSPORTADOR</t>
+  </si>
+  <si>
+    <t>DIRECCIÓN DE RECURSOS FÍSICOS</t>
+  </si>
+  <si>
+    <t>DIRECCIÓN DE SEGURIDAD OPERACIONAL</t>
+  </si>
+  <si>
+    <t>SUBGERENCIA JURÍDICA 
+DIRECCIÓN DE GESTIÓN HUMANA</t>
+  </si>
+  <si>
+    <t>SUBGERENCIA DE PLANEACIÓN Y PROYECTOS DIRECCIÓN DE RECURSOS FÍSICOS Y NEGOCIOS</t>
+  </si>
+  <si>
+    <t>SUBGERENCIA CORPORATIVA 
+DIRECCIÓN DE GESTIÓN FINANCIERA 
+DIRECCIÓN DE RECURSOS TECNOLÓGICOS</t>
+  </si>
+  <si>
+    <t>OFICINA DE AUDITORÍA INTERNA 
+SUBGERENCIA JURÍDICA 
+DIRECCIÓNFINANCIERA</t>
+  </si>
+  <si>
+    <t>SUBGERENCIA PLANEACIÓN Y PROYECTOS</t>
+  </si>
+  <si>
+    <t>SUB GERENCIA DE SERVICIOS OPERACIONALES E INFRAESTRUCTURA</t>
+  </si>
+  <si>
+    <t>SUBGERENCIA DE PLANEACIÓN Y PROYECTOS DIRECCIÓN DE GESTIÓN HUMANA</t>
+  </si>
+  <si>
+    <t>SUBGERENCIAJ URÍDICA</t>
   </si>
 </sst>
 </file>
@@ -3852,6 +3945,9 @@
     <xf numFmtId="0" fontId="11" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="19" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3869,9 +3965,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -5376,6 +5469,21 @@
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="3" tint="0.499984740745262"/>
@@ -5482,21 +5590,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
@@ -20494,6 +20587,129 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B6C7AB91-8822-4E2E-BE9B-A9578BEEAA20}" name="TablaDinámica3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:G7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="19">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+    <i i="3">
+      <x v="3"/>
+    </i>
+    <i i="4">
+      <x v="4"/>
+    </i>
+    <i i="5">
+      <x v="5"/>
+    </i>
+  </colItems>
+  <dataFields count="6">
+    <dataField name="Cuenta de No. Hallazgo" fld="2" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Total Planes de acción" fld="5" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Abiertos" fld="6" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Vencidos" fld="7" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Finalizados" fld="8" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Auditoría" fld="1" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="5">
+    <format dxfId="240">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="239">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="238">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0"/>
+    </format>
+    <format dxfId="237">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="236">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="4">
+            <x v="0"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5E7F1577-F431-4B0C-B786-3FF0F4829E0F}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A9:E35" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
@@ -20687,255 +20903,6 @@
     <dataField name="Suma de Finalizados" fld="8" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="20">
-    <format dxfId="255">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="254">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="253">
-      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0"/>
-    </format>
-    <format dxfId="252">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="251">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="250">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="249">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="248">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="247">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="14"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="246">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="19"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="245">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="20"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="244">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="23"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="243">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="25"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="242">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="42"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="241">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="43"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="240">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="44"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="239">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="46"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="238">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="47"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="237">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="50"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="236">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="12"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B6C7AB91-8822-4E2E-BE9B-A9578BEEAA20}" name="TablaDinámica3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:G7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="19">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-    <i i="2">
-      <x v="2"/>
-    </i>
-    <i i="3">
-      <x v="3"/>
-    </i>
-    <i i="4">
-      <x v="4"/>
-    </i>
-    <i i="5">
-      <x v="5"/>
-    </i>
-  </colItems>
-  <dataFields count="6">
-    <dataField name="Cuenta de No. Hallazgo" fld="2" subtotal="count" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Total Planes de acción" fld="5" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Abiertos" fld="6" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Vencidos" fld="7" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Finalizados" fld="8" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Auditoría" fld="1" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="5">
     <format dxfId="260">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
@@ -20949,13 +20916,139 @@
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
     <format dxfId="256">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
-          <reference field="4294967294" count="4">
-            <x v="0"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="255">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="254">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="253">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="252">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="14"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="251">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="19"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="250">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="20"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="249">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="23"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="248">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="25"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="247">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="42"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="246">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="43"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="245">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="44"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="244">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="46"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="243">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="47"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="242">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="50"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="241">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="12"/>
           </reference>
         </references>
       </pivotArea>
@@ -27780,255 +27873,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A9C7B425-127F-4B5F-B2E3-C2AB4F050E7C}" name="TablaDinámica3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A12:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="19">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Suma de Total Planes de acción" fld="5" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="1">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="0">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{53017CE7-FCFE-4C73-9C32-3A18A27FC23C}" name="TablaDinámica7" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
-  <location ref="F13:G16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="19">
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="54">
-        <item m="1" x="25"/>
-        <item m="1" x="26"/>
-        <item m="1" x="31"/>
-        <item m="1" x="28"/>
-        <item m="1" x="36"/>
-        <item m="1" x="42"/>
-        <item m="1" x="27"/>
-        <item m="1" x="29"/>
-        <item m="1" x="38"/>
-        <item m="1" x="43"/>
-        <item m="1" x="41"/>
-        <item m="1" x="34"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item x="11"/>
-        <item x="16"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="12"/>
-        <item x="17"/>
-        <item x="15"/>
-        <item x="9"/>
-        <item m="1" x="48"/>
-        <item x="21"/>
-        <item m="1" x="46"/>
-        <item m="1" x="52"/>
-        <item m="1" x="49"/>
-        <item m="1" x="50"/>
-        <item m="1" x="35"/>
-        <item m="1" x="32"/>
-        <item m="1" x="47"/>
-        <item m="1" x="39"/>
-        <item m="1" x="40"/>
-        <item m="1" x="45"/>
-        <item m="1" x="51"/>
-        <item m="1" x="37"/>
-        <item m="1" x="33"/>
-        <item m="1" x="30"/>
-        <item m="1" x="44"/>
-        <item x="10"/>
-        <item x="7"/>
-        <item x="13"/>
-        <item x="20"/>
-        <item x="14"/>
-        <item x="24"/>
-        <item x="19"/>
-        <item x="8"/>
-        <item x="5"/>
-        <item x="18"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="-2"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-    <i i="2">
-      <x v="2"/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="3">
-    <dataField name="Suma de Abiertos" fld="6" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Vencidos" fld="7" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Finalizados" fld="8" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="5">
-    <chartFormat chart="4" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="3">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="4">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="5">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DD0BBB6E-FA08-4903-950F-5C10965A7D8D}" name="TablaDinámica6" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A26:B31" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
@@ -28153,10 +27997,10 @@
     <dataField name="Suma de Finalizados" fld="8" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="3">
+    <format dxfId="1">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="2">
+    <format dxfId="0">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
   </formats>
@@ -28172,7 +28016,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3B3AE9AA-616F-416E-8D70-C9530CA01C24}" name="TablaDinámica4" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A19:B23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
@@ -28223,13 +28067,262 @@
     <dataField name="Suma de Alerta 30" fld="11" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
+    <format dxfId="3">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="2">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A9C7B425-127F-4B5F-B2E3-C2AB4F050E7C}" name="TablaDinámica3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A12:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="19">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Suma de Total Planes de acción" fld="5" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="2">
     <format dxfId="5">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
     <format dxfId="4">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0"/>
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{53017CE7-FCFE-4C73-9C32-3A18A27FC23C}" name="TablaDinámica7" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+  <location ref="F13:G16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="19">
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="54">
+        <item m="1" x="25"/>
+        <item m="1" x="26"/>
+        <item m="1" x="31"/>
+        <item m="1" x="28"/>
+        <item m="1" x="36"/>
+        <item m="1" x="42"/>
+        <item m="1" x="27"/>
+        <item m="1" x="29"/>
+        <item m="1" x="38"/>
+        <item m="1" x="43"/>
+        <item m="1" x="41"/>
+        <item m="1" x="34"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="11"/>
+        <item x="16"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="12"/>
+        <item x="17"/>
+        <item x="15"/>
+        <item x="9"/>
+        <item m="1" x="48"/>
+        <item x="21"/>
+        <item m="1" x="46"/>
+        <item m="1" x="52"/>
+        <item m="1" x="49"/>
+        <item m="1" x="50"/>
+        <item m="1" x="35"/>
+        <item m="1" x="32"/>
+        <item m="1" x="47"/>
+        <item m="1" x="39"/>
+        <item m="1" x="40"/>
+        <item m="1" x="45"/>
+        <item m="1" x="51"/>
+        <item m="1" x="37"/>
+        <item m="1" x="33"/>
+        <item m="1" x="30"/>
+        <item m="1" x="44"/>
+        <item x="10"/>
+        <item x="7"/>
+        <item x="13"/>
+        <item x="20"/>
+        <item x="14"/>
+        <item x="24"/>
+        <item x="19"/>
+        <item x="8"/>
+        <item x="5"/>
+        <item x="18"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="-2"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="3">
+    <dataField name="Suma de Abiertos" fld="6" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Vencidos" fld="7" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Finalizados" fld="8" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="5">
+    <chartFormat chart="4" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -29224,7 +29317,7 @@
         <v>100</v>
       </c>
       <c r="U2" s="60" t="s">
-        <v>678</v>
+        <v>800</v>
       </c>
       <c r="V2" s="138">
         <v>45957</v>
@@ -29329,7 +29422,7 @@
         <v>100</v>
       </c>
       <c r="U3" s="60" t="s">
-        <v>659</v>
+        <v>801</v>
       </c>
       <c r="V3" s="138">
         <v>45957</v>
@@ -29438,7 +29531,7 @@
         <v>100</v>
       </c>
       <c r="U4" s="60" t="s">
-        <v>660</v>
+        <v>802</v>
       </c>
       <c r="V4" s="137" t="s">
         <v>38</v>
@@ -29547,7 +29640,7 @@
         <v>100</v>
       </c>
       <c r="U5" s="60" t="s">
-        <v>660</v>
+        <v>802</v>
       </c>
       <c r="V5" s="137" t="s">
         <v>38</v>
@@ -29654,7 +29747,7 @@
         <v>100</v>
       </c>
       <c r="U6" s="60" t="s">
-        <v>661</v>
+        <v>803</v>
       </c>
       <c r="V6" s="137" t="s">
         <v>38</v>
@@ -29763,7 +29856,7 @@
         <v>100</v>
       </c>
       <c r="U7" s="60" t="s">
-        <v>661</v>
+        <v>803</v>
       </c>
       <c r="V7" s="137" t="s">
         <v>38</v>
@@ -29872,7 +29965,7 @@
         <v>100</v>
       </c>
       <c r="U8" s="60" t="s">
-        <v>661</v>
+        <v>803</v>
       </c>
       <c r="V8" s="137" t="s">
         <v>38</v>
@@ -29956,7 +30049,7 @@
       <c r="J9" s="162" t="s">
         <v>31</v>
       </c>
-      <c r="K9" s="234"/>
+      <c r="K9" s="228"/>
       <c r="L9" s="75" t="s">
         <v>32</v>
       </c>
@@ -29981,7 +30074,7 @@
         <v>100</v>
       </c>
       <c r="U9" s="75" t="s">
-        <v>679</v>
+        <v>804</v>
       </c>
       <c r="V9" s="142" t="s">
         <v>38</v>
@@ -30090,7 +30183,7 @@
         <v>100</v>
       </c>
       <c r="U10" s="60" t="s">
-        <v>660</v>
+        <v>802</v>
       </c>
       <c r="V10" s="137" t="s">
         <v>38</v>
@@ -30199,7 +30292,7 @@
         <v>100</v>
       </c>
       <c r="U11" s="60" t="s">
-        <v>659</v>
+        <v>801</v>
       </c>
       <c r="V11" s="137" t="s">
         <v>38</v>
@@ -30222,7 +30315,7 @@
       </c>
       <c r="AC11" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AD11" s="67">
         <f t="shared" ca="1" si="1"/>
@@ -30304,7 +30397,7 @@
         <v>100</v>
       </c>
       <c r="U12" s="60" t="s">
-        <v>662</v>
+        <v>805</v>
       </c>
       <c r="V12" s="137" t="s">
         <v>38</v>
@@ -30327,7 +30420,7 @@
       </c>
       <c r="AC12" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AD12" s="67">
         <f t="shared" ca="1" si="1"/>
@@ -30409,7 +30502,7 @@
         <v>100</v>
       </c>
       <c r="U13" s="60" t="s">
-        <v>660</v>
+        <v>802</v>
       </c>
       <c r="V13" s="137" t="s">
         <v>38</v>
@@ -30462,7 +30555,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="14" spans="1:36" ht="136.80000000000001">
+    <row r="14" spans="1:36" ht="125.4">
       <c r="A14" s="59">
         <v>200</v>
       </c>
@@ -30518,7 +30611,7 @@
         <v>100</v>
       </c>
       <c r="U14" s="60" t="s">
-        <v>659</v>
+        <v>801</v>
       </c>
       <c r="V14" s="137" t="s">
         <v>38</v>
@@ -30736,7 +30829,7 @@
         <v>100</v>
       </c>
       <c r="U16" s="60" t="s">
-        <v>662</v>
+        <v>805</v>
       </c>
       <c r="V16" s="137" t="s">
         <v>38</v>
@@ -30759,7 +30852,7 @@
       </c>
       <c r="AC16" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AD16" s="67">
         <f t="shared" ca="1" si="1"/>
@@ -30841,7 +30934,7 @@
         <v>100</v>
       </c>
       <c r="U17" s="60" t="s">
-        <v>680</v>
+        <v>806</v>
       </c>
       <c r="V17" s="137" t="s">
         <v>38</v>
@@ -30950,7 +31043,7 @@
         <v>100</v>
       </c>
       <c r="U18" s="60" t="s">
-        <v>659</v>
+        <v>807</v>
       </c>
       <c r="V18" s="137" t="s">
         <v>38</v>
@@ -31059,7 +31152,7 @@
         <v>100</v>
       </c>
       <c r="U19" s="60" t="s">
-        <v>659</v>
+        <v>807</v>
       </c>
       <c r="V19" s="137" t="s">
         <v>38</v>
@@ -31168,7 +31261,7 @@
         <v>100</v>
       </c>
       <c r="U20" s="60" t="s">
-        <v>659</v>
+        <v>807</v>
       </c>
       <c r="V20" s="137" t="s">
         <v>38</v>
@@ -31277,7 +31370,7 @@
         <v>100</v>
       </c>
       <c r="U21" s="75" t="s">
-        <v>681</v>
+        <v>808</v>
       </c>
       <c r="V21" s="142" t="s">
         <v>38</v>
@@ -31382,7 +31475,7 @@
         <v>100</v>
       </c>
       <c r="U22" s="75" t="s">
-        <v>681</v>
+        <v>808</v>
       </c>
       <c r="V22" s="142" t="s">
         <v>38</v>
@@ -31487,7 +31580,7 @@
         <v>100</v>
       </c>
       <c r="U23" s="75" t="s">
-        <v>681</v>
+        <v>808</v>
       </c>
       <c r="V23" s="142" t="s">
         <v>38</v>
@@ -31592,7 +31685,7 @@
         <v>100</v>
       </c>
       <c r="U24" s="75" t="s">
-        <v>663</v>
+        <v>809</v>
       </c>
       <c r="V24" s="142" t="s">
         <v>38</v>
@@ -31645,7 +31738,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="25" spans="1:36" ht="205.2">
+    <row r="25" spans="1:36" ht="193.8">
       <c r="A25" s="59">
         <v>245</v>
       </c>
@@ -31701,7 +31794,7 @@
         <v>100</v>
       </c>
       <c r="U25" s="60" t="s">
-        <v>682</v>
+        <v>810</v>
       </c>
       <c r="V25" s="137" t="s">
         <v>38</v>
@@ -31754,7 +31847,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="26" spans="1:36" ht="148.19999999999999">
+    <row r="26" spans="1:36" ht="136.80000000000001">
       <c r="A26" s="59">
         <v>246</v>
       </c>
@@ -31810,7 +31903,7 @@
         <v>100</v>
       </c>
       <c r="U26" s="60" t="s">
-        <v>664</v>
+        <v>811</v>
       </c>
       <c r="V26" s="137" t="s">
         <v>38</v>
@@ -31833,7 +31926,7 @@
       </c>
       <c r="AC26" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AD26" s="67">
         <f t="shared" ca="1" si="1"/>
@@ -31915,7 +32008,7 @@
         <v>100</v>
       </c>
       <c r="U27" s="60" t="s">
-        <v>664</v>
+        <v>811</v>
       </c>
       <c r="V27" s="137" t="s">
         <v>38</v>
@@ -31938,7 +32031,7 @@
       </c>
       <c r="AC27" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AD27" s="67">
         <f t="shared" ca="1" si="1"/>
@@ -32020,7 +32113,7 @@
         <v>100</v>
       </c>
       <c r="U28" s="60" t="s">
-        <v>665</v>
+        <v>812</v>
       </c>
       <c r="V28" s="137" t="s">
         <v>38</v>
@@ -32043,7 +32136,7 @@
       </c>
       <c r="AC28" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AD28" s="67">
         <f t="shared" ca="1" si="1"/>
@@ -32069,7 +32162,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:36" ht="114">
+    <row r="29" spans="1:36" ht="102.6">
       <c r="A29" s="59">
         <v>256</v>
       </c>
@@ -32125,7 +32218,7 @@
         <v>100</v>
       </c>
       <c r="U29" s="60" t="s">
-        <v>662</v>
+        <v>805</v>
       </c>
       <c r="V29" s="137" t="s">
         <v>38</v>
@@ -32148,7 +32241,7 @@
       </c>
       <c r="AC29" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AD29" s="67">
         <f t="shared" ca="1" si="1"/>
@@ -32230,7 +32323,7 @@
         <v>100</v>
       </c>
       <c r="U30" s="152" t="s">
-        <v>665</v>
+        <v>812</v>
       </c>
       <c r="V30" s="153" t="s">
         <v>38</v>
@@ -32339,7 +32432,7 @@
         <v>100</v>
       </c>
       <c r="U31" s="75" t="s">
-        <v>662</v>
+        <v>805</v>
       </c>
       <c r="V31" s="142" t="s">
         <v>38</v>
@@ -32448,7 +32541,7 @@
         <v>100</v>
       </c>
       <c r="U32" s="75" t="s">
-        <v>659</v>
+        <v>807</v>
       </c>
       <c r="V32" s="142" t="s">
         <v>38</v>
@@ -32553,7 +32646,7 @@
         <v>100</v>
       </c>
       <c r="U33" s="75" t="s">
-        <v>659</v>
+        <v>807</v>
       </c>
       <c r="V33" s="142" t="s">
         <v>38</v>
@@ -32662,7 +32755,7 @@
         <v>100</v>
       </c>
       <c r="U34" s="60" t="s">
-        <v>661</v>
+        <v>803</v>
       </c>
       <c r="V34" s="137" t="s">
         <v>38</v>
@@ -32769,7 +32862,7 @@
         <v>100</v>
       </c>
       <c r="U35" s="60" t="s">
-        <v>663</v>
+        <v>813</v>
       </c>
       <c r="V35" s="137" t="s">
         <v>38</v>
@@ -32878,7 +32971,7 @@
         <v>100</v>
       </c>
       <c r="U36" s="60" t="s">
-        <v>659</v>
+        <v>807</v>
       </c>
       <c r="V36" s="137" t="s">
         <v>244</v>
@@ -32987,7 +33080,7 @@
         <v>100</v>
       </c>
       <c r="U37" s="60" t="s">
-        <v>666</v>
+        <v>814</v>
       </c>
       <c r="V37" s="137" t="s">
         <v>244</v>
@@ -33094,7 +33187,7 @@
         <v>100</v>
       </c>
       <c r="U38" s="60" t="s">
-        <v>664</v>
+        <v>811</v>
       </c>
       <c r="V38" s="137" t="s">
         <v>244</v>
@@ -33201,7 +33294,7 @@
         <v>100</v>
       </c>
       <c r="U39" s="75" t="s">
-        <v>683</v>
+        <v>815</v>
       </c>
       <c r="V39" s="142" t="s">
         <v>244</v>
@@ -33308,7 +33401,7 @@
         <v>100</v>
       </c>
       <c r="U40" s="60" t="s">
-        <v>667</v>
+        <v>270</v>
       </c>
       <c r="V40" s="137" t="s">
         <v>244</v>
@@ -33415,7 +33508,7 @@
         <v>100</v>
       </c>
       <c r="U41" s="60" t="s">
-        <v>661</v>
+        <v>803</v>
       </c>
       <c r="V41" s="137" t="s">
         <v>244</v>
@@ -33524,7 +33617,7 @@
         <v>100</v>
       </c>
       <c r="U42" s="60" t="s">
-        <v>659</v>
+        <v>807</v>
       </c>
       <c r="V42" s="137" t="s">
         <v>244</v>
@@ -33633,7 +33726,7 @@
         <v>100</v>
       </c>
       <c r="U43" s="75" t="s">
-        <v>683</v>
+        <v>815</v>
       </c>
       <c r="V43" s="142" t="s">
         <v>244</v>
@@ -33740,7 +33833,7 @@
         <v>100</v>
       </c>
       <c r="U44" s="60" t="s">
-        <v>668</v>
+        <v>816</v>
       </c>
       <c r="V44" s="137" t="s">
         <v>244</v>
@@ -33791,7 +33884,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="45" spans="1:36" ht="136.80000000000001">
+    <row r="45" spans="1:36" ht="125.4">
       <c r="A45" s="83">
         <v>215</v>
       </c>
@@ -33847,7 +33940,7 @@
         <v>100</v>
       </c>
       <c r="U45" s="84" t="s">
-        <v>668</v>
+        <v>817</v>
       </c>
       <c r="V45" s="139" t="s">
         <v>244</v>
@@ -33954,7 +34047,7 @@
         <v>100</v>
       </c>
       <c r="U46" s="60" t="s">
-        <v>667</v>
+        <v>270</v>
       </c>
       <c r="V46" s="137" t="s">
         <v>244</v>
@@ -34061,7 +34154,7 @@
         <v>100</v>
       </c>
       <c r="U47" s="60" t="s">
-        <v>667</v>
+        <v>270</v>
       </c>
       <c r="V47" s="137" t="s">
         <v>244</v>
@@ -34168,7 +34261,7 @@
         <v>100</v>
       </c>
       <c r="U48" s="60" t="s">
-        <v>667</v>
+        <v>270</v>
       </c>
       <c r="V48" s="137" t="s">
         <v>244</v>
@@ -34277,7 +34370,7 @@
         <v>100</v>
       </c>
       <c r="U49" s="60" t="s">
-        <v>669</v>
+        <v>818</v>
       </c>
       <c r="V49" s="137" t="s">
         <v>244</v>
@@ -34328,7 +34421,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="50" spans="1:36" ht="239.4">
+    <row r="50" spans="1:36" ht="205.2">
       <c r="A50" s="59">
         <v>220</v>
       </c>
@@ -34384,7 +34477,7 @@
         <v>100</v>
       </c>
       <c r="U50" s="60" t="s">
-        <v>669</v>
+        <v>818</v>
       </c>
       <c r="V50" s="137" t="s">
         <v>244</v>
@@ -34491,7 +34584,7 @@
         <v>100</v>
       </c>
       <c r="U51" s="60" t="s">
-        <v>670</v>
+        <v>819</v>
       </c>
       <c r="V51" s="137" t="s">
         <v>244</v>
@@ -34598,7 +34691,7 @@
         <v>100</v>
       </c>
       <c r="U52" s="60" t="s">
-        <v>667</v>
+        <v>270</v>
       </c>
       <c r="V52" s="137" t="s">
         <v>244</v>
@@ -34705,7 +34798,7 @@
         <v>100</v>
       </c>
       <c r="U53" s="60" t="s">
-        <v>667</v>
+        <v>270</v>
       </c>
       <c r="V53" s="137" t="s">
         <v>244</v>
@@ -34812,7 +34905,7 @@
         <v>100</v>
       </c>
       <c r="U54" s="60" t="s">
-        <v>667</v>
+        <v>270</v>
       </c>
       <c r="V54" s="137" t="s">
         <v>244</v>
@@ -34863,7 +34956,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="55" spans="1:36" ht="136.80000000000001">
+    <row r="55" spans="1:36" ht="125.4">
       <c r="A55" s="78">
         <v>229</v>
       </c>
@@ -34919,7 +35012,7 @@
         <v>100</v>
       </c>
       <c r="U55" s="60" t="s">
-        <v>667</v>
+        <v>270</v>
       </c>
       <c r="V55" s="137" t="s">
         <v>244</v>
@@ -35026,7 +35119,7 @@
         <v>100</v>
       </c>
       <c r="U56" s="60" t="s">
-        <v>667</v>
+        <v>270</v>
       </c>
       <c r="V56" s="137" t="s">
         <v>244</v>
@@ -35133,7 +35226,7 @@
         <v>100</v>
       </c>
       <c r="U57" s="60" t="s">
-        <v>671</v>
+        <v>820</v>
       </c>
       <c r="V57" s="137" t="s">
         <v>244</v>
@@ -35240,7 +35333,7 @@
         <v>100</v>
       </c>
       <c r="U58" s="60" t="s">
-        <v>667</v>
+        <v>270</v>
       </c>
       <c r="V58" s="137" t="s">
         <v>244</v>
@@ -35347,7 +35440,7 @@
         <v>100</v>
       </c>
       <c r="U59" s="60" t="s">
-        <v>667</v>
+        <v>270</v>
       </c>
       <c r="V59" s="137" t="s">
         <v>244</v>
@@ -35454,7 +35547,7 @@
         <v>100</v>
       </c>
       <c r="U60" s="60" t="s">
-        <v>667</v>
+        <v>270</v>
       </c>
       <c r="V60" s="137" t="s">
         <v>244</v>
@@ -35561,7 +35654,7 @@
         <v>100</v>
       </c>
       <c r="U61" s="60" t="s">
-        <v>672</v>
+        <v>821</v>
       </c>
       <c r="V61" s="137" t="s">
         <v>244</v>
@@ -35672,7 +35765,7 @@
         <v>100</v>
       </c>
       <c r="U62" s="60" t="s">
-        <v>667</v>
+        <v>270</v>
       </c>
       <c r="V62" s="60" t="s">
         <v>446</v>
@@ -35783,7 +35876,7 @@
         <v>100</v>
       </c>
       <c r="U63" s="60" t="s">
-        <v>673</v>
+        <v>822</v>
       </c>
       <c r="V63" s="60" t="s">
         <v>455</v>
@@ -35894,7 +35987,7 @@
         <v>100</v>
       </c>
       <c r="U64" s="60" t="s">
-        <v>674</v>
+        <v>823</v>
       </c>
       <c r="V64" s="60" t="s">
         <v>455</v>
@@ -35945,7 +36038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:36" ht="193.8">
+    <row r="65" spans="1:36" ht="171">
       <c r="A65" s="59">
         <v>184</v>
       </c>
@@ -36005,7 +36098,7 @@
         <v>100</v>
       </c>
       <c r="U65" s="60" t="s">
-        <v>659</v>
+        <v>807</v>
       </c>
       <c r="V65" s="60" t="s">
         <v>455</v>
@@ -36058,7 +36151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:36" ht="239.4">
+    <row r="66" spans="1:36" ht="205.2">
       <c r="A66" s="59">
         <v>186</v>
       </c>
@@ -36118,7 +36211,7 @@
         <v>100</v>
       </c>
       <c r="U66" s="60" t="s">
-        <v>659</v>
+        <v>807</v>
       </c>
       <c r="V66" s="60" t="s">
         <v>446</v>
@@ -36171,7 +36264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:36" ht="193.8">
+    <row r="67" spans="1:36" ht="171">
       <c r="A67" s="59">
         <v>187</v>
       </c>
@@ -36231,7 +36324,7 @@
         <v>100</v>
       </c>
       <c r="U67" s="60" t="s">
-        <v>659</v>
+        <v>807</v>
       </c>
       <c r="V67" s="60" t="s">
         <v>455</v>
@@ -36284,7 +36377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:36" ht="193.8">
+    <row r="68" spans="1:36" ht="171">
       <c r="A68" s="59">
         <v>188</v>
       </c>
@@ -36344,7 +36437,7 @@
         <v>100</v>
       </c>
       <c r="U68" s="60" t="s">
-        <v>659</v>
+        <v>807</v>
       </c>
       <c r="V68" s="60" t="s">
         <v>455</v>
@@ -36457,7 +36550,7 @@
         <v>100</v>
       </c>
       <c r="U69" s="60" t="s">
-        <v>675</v>
+        <v>824</v>
       </c>
       <c r="V69" s="60" t="s">
         <v>500</v>
@@ -36508,7 +36601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:36" ht="239.4">
+    <row r="70" spans="1:36" ht="228">
       <c r="A70" s="59">
         <v>221</v>
       </c>
@@ -36568,7 +36661,7 @@
         <v>100</v>
       </c>
       <c r="U70" s="60" t="s">
-        <v>676</v>
+        <v>825</v>
       </c>
       <c r="V70" s="60" t="s">
         <v>500</v>
@@ -36619,7 +36712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:36" ht="262.2">
+    <row r="71" spans="1:36" ht="239.4">
       <c r="A71" s="59">
         <v>222</v>
       </c>
@@ -36679,7 +36772,7 @@
         <v>100</v>
       </c>
       <c r="U71" s="60" t="s">
-        <v>676</v>
+        <v>825</v>
       </c>
       <c r="V71" s="60" t="s">
         <v>500</v>
@@ -36730,7 +36823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:36" ht="239.4">
+    <row r="72" spans="1:36" ht="228">
       <c r="A72" s="78">
         <v>224</v>
       </c>
@@ -36790,7 +36883,7 @@
         <v>100</v>
       </c>
       <c r="U72" s="60" t="s">
-        <v>676</v>
+        <v>825</v>
       </c>
       <c r="V72" s="60" t="s">
         <v>500</v>
@@ -36901,7 +36994,7 @@
         <v>100</v>
       </c>
       <c r="U73" s="60" t="s">
-        <v>661</v>
+        <v>803</v>
       </c>
       <c r="V73" s="60" t="s">
         <v>500</v>
@@ -36954,7 +37047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:36" ht="228">
+    <row r="74" spans="1:36" ht="193.8">
       <c r="A74" s="59">
         <v>232</v>
       </c>
@@ -37014,7 +37107,7 @@
         <v>100</v>
       </c>
       <c r="U74" s="60" t="s">
-        <v>661</v>
+        <v>803</v>
       </c>
       <c r="V74" s="60" t="s">
         <v>500</v>
@@ -37127,7 +37220,7 @@
         <v>100</v>
       </c>
       <c r="U75" s="60" t="s">
-        <v>677</v>
+        <v>826</v>
       </c>
       <c r="V75" s="60" t="s">
         <v>500</v>
@@ -37178,7 +37271,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="76" spans="1:36" ht="273.60000000000002">
+    <row r="76" spans="1:36" ht="262.2">
       <c r="A76" s="59">
         <v>234</v>
       </c>
@@ -37238,7 +37331,7 @@
         <v>100</v>
       </c>
       <c r="U76" s="60" t="s">
-        <v>677</v>
+        <v>826</v>
       </c>
       <c r="V76" s="60" t="s">
         <v>500</v>
@@ -37349,7 +37442,7 @@
         <v>100</v>
       </c>
       <c r="U77" s="60" t="s">
-        <v>661</v>
+        <v>803</v>
       </c>
       <c r="V77" s="60" t="s">
         <v>500</v>
@@ -37402,7 +37495,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="78" spans="1:36" ht="273.60000000000002">
+    <row r="78" spans="1:36" ht="262.2">
       <c r="A78" s="59">
         <v>236</v>
       </c>
@@ -37462,7 +37555,7 @@
         <v>100</v>
       </c>
       <c r="U78" s="60" t="s">
-        <v>661</v>
+        <v>803</v>
       </c>
       <c r="V78" s="60" t="s">
         <v>500</v>
@@ -37515,7 +37608,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="79" spans="1:36" ht="171">
+    <row r="79" spans="1:36" ht="159.6">
       <c r="A79" s="59">
         <v>237</v>
       </c>
@@ -37575,7 +37668,7 @@
         <v>100</v>
       </c>
       <c r="U79" s="60" t="s">
-        <v>661</v>
+        <v>803</v>
       </c>
       <c r="V79" s="60" t="s">
         <v>500</v>
@@ -37688,7 +37781,7 @@
         <v>100</v>
       </c>
       <c r="U80" s="60" t="s">
-        <v>662</v>
+        <v>827</v>
       </c>
       <c r="V80" s="60" t="s">
         <v>578</v>
@@ -37799,7 +37892,7 @@
         <v>100</v>
       </c>
       <c r="U81" s="60" t="s">
-        <v>662</v>
+        <v>803</v>
       </c>
       <c r="V81" s="60" t="s">
         <v>578</v>
@@ -37850,7 +37943,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="82" spans="1:36" ht="136.80000000000001">
+    <row r="82" spans="1:36" ht="125.4">
       <c r="A82" s="59">
         <v>241</v>
       </c>
@@ -37910,7 +38003,7 @@
         <v>100</v>
       </c>
       <c r="U82" s="60" t="s">
-        <v>662</v>
+        <v>805</v>
       </c>
       <c r="V82" s="60" t="s">
         <v>592</v>
@@ -38021,7 +38114,7 @@
         <v>100</v>
       </c>
       <c r="U83" s="60" t="s">
-        <v>662</v>
+        <v>805</v>
       </c>
       <c r="V83" s="60" t="s">
         <v>592</v>
@@ -38072,7 +38165,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="84" spans="1:36" ht="239.4">
+    <row r="84" spans="1:36" ht="228">
       <c r="A84" s="59">
         <v>243</v>
       </c>
@@ -38132,7 +38225,7 @@
         <v>100</v>
       </c>
       <c r="U84" s="60" t="s">
-        <v>662</v>
+        <v>805</v>
       </c>
       <c r="V84" s="60" t="s">
         <v>592</v>
@@ -38183,7 +38276,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="85" spans="1:36" ht="228">
+    <row r="85" spans="1:36" ht="205.2">
       <c r="A85" s="59">
         <v>244</v>
       </c>
@@ -38243,7 +38336,7 @@
         <v>100</v>
       </c>
       <c r="U85" s="60" t="s">
-        <v>662</v>
+        <v>805</v>
       </c>
       <c r="V85" s="60" t="s">
         <v>592</v>
@@ -39116,13 +39209,13 @@
       <c r="E6" s="16"/>
     </row>
     <row r="7" spans="3:14" ht="76.2" customHeight="1">
-      <c r="C7" s="232" t="s">
+      <c r="C7" s="233" t="s">
         <v>686</v>
       </c>
-      <c r="D7" s="232"/>
-      <c r="E7" s="232"/>
-      <c r="F7" s="232"/>
-      <c r="G7" s="232"/>
+      <c r="D7" s="233"/>
+      <c r="E7" s="233"/>
+      <c r="F7" s="233"/>
+      <c r="G7" s="233"/>
     </row>
     <row r="8" spans="3:14">
       <c r="C8" s="105" t="s">
@@ -39370,13 +39463,13 @@
       <c r="E17" s="16"/>
     </row>
     <row r="18" spans="3:14" ht="85.2" customHeight="1">
-      <c r="C18" s="233" t="s">
+      <c r="C18" s="234" t="s">
         <v>690</v>
       </c>
-      <c r="D18" s="233"/>
-      <c r="E18" s="233"/>
-      <c r="F18" s="233"/>
-      <c r="G18" s="233"/>
+      <c r="D18" s="234"/>
+      <c r="E18" s="234"/>
+      <c r="F18" s="234"/>
+      <c r="G18" s="234"/>
     </row>
     <row r="19" spans="3:14">
       <c r="C19" s="108" t="s">
@@ -39523,13 +39616,13 @@
       </c>
     </row>
     <row r="27" spans="3:14" ht="58.2" customHeight="1">
-      <c r="C27" s="232" t="s">
+      <c r="C27" s="233" t="s">
         <v>694</v>
       </c>
-      <c r="D27" s="232"/>
-      <c r="E27" s="232"/>
-      <c r="F27" s="232"/>
-      <c r="G27" s="232"/>
+      <c r="D27" s="233"/>
+      <c r="E27" s="233"/>
+      <c r="F27" s="233"/>
+      <c r="G27" s="233"/>
       <c r="J27" s="203" t="s">
         <v>777</v>
       </c>
@@ -39630,13 +39723,13 @@
       <c r="E34" s="16"/>
     </row>
     <row r="35" spans="3:14" ht="71.400000000000006" customHeight="1">
-      <c r="C35" s="232" t="s">
+      <c r="C35" s="233" t="s">
         <v>700</v>
       </c>
-      <c r="D35" s="232"/>
-      <c r="E35" s="232"/>
-      <c r="F35" s="232"/>
-      <c r="G35" s="232"/>
+      <c r="D35" s="233"/>
+      <c r="E35" s="233"/>
+      <c r="F35" s="233"/>
+      <c r="G35" s="233"/>
     </row>
     <row r="36" spans="3:14" ht="26.4" customHeight="1">
       <c r="C36" s="105" t="s">
@@ -39734,13 +39827,13 @@
       <c r="E42" s="16"/>
     </row>
     <row r="43" spans="3:14" ht="108.6" customHeight="1">
-      <c r="C43" s="232" t="s">
+      <c r="C43" s="233" t="s">
         <v>713</v>
       </c>
-      <c r="D43" s="232"/>
-      <c r="E43" s="232"/>
-      <c r="F43" s="232"/>
-      <c r="G43" s="232"/>
+      <c r="D43" s="233"/>
+      <c r="E43" s="233"/>
+      <c r="F43" s="233"/>
+      <c r="G43" s="233"/>
     </row>
     <row r="45" spans="3:14">
       <c r="C45" s="108" t="s">
@@ -39841,13 +39934,13 @@
       </c>
     </row>
     <row r="52" spans="3:14" ht="70.8" customHeight="1">
-      <c r="C52" s="232" t="s">
+      <c r="C52" s="233" t="s">
         <v>718</v>
       </c>
-      <c r="D52" s="232"/>
-      <c r="E52" s="232"/>
-      <c r="F52" s="232"/>
-      <c r="G52" s="232"/>
+      <c r="D52" s="233"/>
+      <c r="E52" s="233"/>
+      <c r="F52" s="233"/>
+      <c r="G52" s="233"/>
     </row>
     <row r="54" spans="3:14">
       <c r="C54" s="105" t="s">
@@ -40066,7 +40159,7 @@
   <dimension ref="A1:AF4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:32" ht="307.2">
+    <row r="1" spans="1:32" ht="297.60000000000002">
       <c r="A1" s="47">
         <v>70</v>
       </c>
@@ -40160,7 +40253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:32" ht="240">
+    <row r="2" spans="1:32" ht="230.4">
       <c r="A2" s="48">
         <v>113</v>
       </c>
@@ -40256,7 +40349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:32" ht="307.2">
+    <row r="3" spans="1:32" ht="297.60000000000002">
       <c r="A3" s="48">
         <v>114</v>
       </c>
@@ -40352,7 +40445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:32" ht="316.8">
+    <row r="4" spans="1:32" ht="297.60000000000002">
       <c r="A4" s="47">
         <v>185</v>
       </c>
@@ -41265,11 +41358,11 @@
       </c>
     </row>
     <row r="9" spans="3:15" ht="12">
-      <c r="C9" s="228" t="s">
+      <c r="C9" s="229" t="s">
         <v>752</v>
       </c>
-      <c r="D9" s="228"/>
-      <c r="E9" s="228"/>
+      <c r="D9" s="229"/>
+      <c r="E9" s="229"/>
       <c r="F9" s="185">
         <f>SUM(F6:F8)</f>
         <v>84</v>
@@ -41799,7 +41892,7 @@
       <c r="S37" s="177"/>
     </row>
     <row r="38" spans="11:19" ht="24">
-      <c r="K38" s="229" t="s">
+      <c r="K38" s="230" t="s">
         <v>735</v>
       </c>
       <c r="L38" s="179" t="s">
@@ -41821,7 +41914,7 @@
       <c r="S38" s="177"/>
     </row>
     <row r="39" spans="11:19" ht="12">
-      <c r="K39" s="230"/>
+      <c r="K39" s="231"/>
       <c r="L39" s="190">
         <f>+L16+L33</f>
         <v>84</v>
@@ -42118,7 +42211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="216">
+    <row r="10" spans="1:20" ht="201.6">
       <c r="A10" s="165"/>
       <c r="B10" s="20"/>
       <c r="C10" s="20" t="s">
@@ -42253,7 +42346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="115.2">
+    <row r="14" spans="1:20" ht="100.8">
       <c r="A14" s="165"/>
       <c r="B14" s="20"/>
       <c r="C14" s="20" t="s">
@@ -42949,7 +43042,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="173.4">
+    <row r="5" spans="2:9" ht="163.19999999999999">
       <c r="B5" s="200">
         <v>2025</v>
       </c>
@@ -42975,7 +43068,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="173.4">
+    <row r="6" spans="2:9" ht="163.19999999999999">
       <c r="B6" s="200">
         <v>2025</v>
       </c>
@@ -43001,7 +43094,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="173.4">
+    <row r="7" spans="2:9" ht="163.19999999999999">
       <c r="B7" s="200">
         <v>2025</v>
       </c>
@@ -43352,7 +43445,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="136.80000000000001">
+    <row r="8" spans="2:8" ht="125.4">
       <c r="B8" s="170">
         <v>2025</v>
       </c>
@@ -43402,7 +43495,7 @@
       <c r="D10" s="28" t="s">
         <v>215</v>
       </c>
-      <c r="E10" s="231" t="s">
+      <c r="E10" s="232" t="s">
         <v>216</v>
       </c>
       <c r="F10" s="171" t="s">
@@ -43423,7 +43516,7 @@
       <c r="D11" s="28" t="s">
         <v>215</v>
       </c>
-      <c r="E11" s="231"/>
+      <c r="E11" s="232"/>
       <c r="F11" s="171" t="s">
         <v>222</v>
       </c>
@@ -43560,7 +43653,7 @@
       </c>
       <c r="H4" s="29" cm="1">
         <f t="array" ref="H4">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C4))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D4))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E4))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F4))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C4,'Base de Datos'!$G:$G,$D4,'Base de Datos'!$H:$H,$E4,'Base de Datos'!$U:$U,$F4,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -43568,7 +43661,7 @@
       </c>
       <c r="J4" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C4,'Base de Datos'!$G:$G,$D4,'Base de Datos'!$H:$H,$E4,'Base de Datos'!$U:$U,$F4,'Base de Datos'!$AA:$AA,"Vencida")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C4,'Base de Datos'!$G:$G,$D4,'Base de Datos'!$H:$H,$E4,'Base de Datos'!$U:$U,$F4,'Base de Datos'!$AA:$AA,"Finalizada")</f>
@@ -43634,7 +43727,7 @@
       </c>
       <c r="H5" s="29" cm="1">
         <f t="array" ref="H5">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C5))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D5))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E5))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F5))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C5,'Base de Datos'!$G:$G,$D5,'Base de Datos'!$H:$H,$E5,'Base de Datos'!$U:$U,$F5,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -43646,7 +43739,7 @@
       </c>
       <c r="K5" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C5,'Base de Datos'!$G:$G,$D5,'Base de Datos'!$H:$H,$E5,'Base de Datos'!$U:$U,$F5,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C5,'Base de Datos'!$G:$G,$D5,'Base de Datos'!$H:$H,$E5,'Base de Datos'!$U:$U,$F5,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -43708,7 +43801,7 @@
       </c>
       <c r="H6" s="29" cm="1">
         <f t="array" ref="H6">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C6))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D6))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E6))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F6))&amp;""))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C6,'Base de Datos'!$G:$G,$D6,'Base de Datos'!$H:$H,$E6,'Base de Datos'!$U:$U,$F6,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -43720,7 +43813,7 @@
       </c>
       <c r="K6" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C6,'Base de Datos'!$G:$G,$D6,'Base de Datos'!$H:$H,$E6,'Base de Datos'!$U:$U,$F6,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L6" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C6,'Base de Datos'!$G:$G,$D6,'Base de Datos'!$H:$H,$E6,'Base de Datos'!$U:$U,$F6,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -43782,7 +43875,7 @@
       </c>
       <c r="H7" s="29" cm="1">
         <f t="array" ref="H7">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C7))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D7))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E7))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F7))&amp;""))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I7" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C7,'Base de Datos'!$G:$G,$D7,'Base de Datos'!$H:$H,$E7,'Base de Datos'!$U:$U,$F7,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -43794,7 +43887,7 @@
       </c>
       <c r="K7" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C7,'Base de Datos'!$G:$G,$D7,'Base de Datos'!$H:$H,$E7,'Base de Datos'!$U:$U,$F7,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L7" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C7,'Base de Datos'!$G:$G,$D7,'Base de Datos'!$H:$H,$E7,'Base de Datos'!$U:$U,$F7,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -43856,7 +43949,7 @@
       </c>
       <c r="H8" s="29" cm="1">
         <f t="array" ref="H8">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C8))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D8))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E8))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F8))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C8,'Base de Datos'!$G:$G,$D8,'Base de Datos'!$H:$H,$E8,'Base de Datos'!$U:$U,$F8,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -43868,7 +43961,7 @@
       </c>
       <c r="K8" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C8,'Base de Datos'!$G:$G,$D8,'Base de Datos'!$H:$H,$E8,'Base de Datos'!$U:$U,$F8,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C8,'Base de Datos'!$G:$G,$D8,'Base de Datos'!$H:$H,$E8,'Base de Datos'!$U:$U,$F8,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -43930,7 +44023,7 @@
       </c>
       <c r="H9" s="29" cm="1">
         <f t="array" ref="H9">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C9))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D9))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E9))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F9))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C9,'Base de Datos'!$G:$G,$D9,'Base de Datos'!$H:$H,$E9,'Base de Datos'!$U:$U,$F9,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -43942,7 +44035,7 @@
       </c>
       <c r="K9" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C9,'Base de Datos'!$G:$G,$D9,'Base de Datos'!$H:$H,$E9,'Base de Datos'!$U:$U,$F9,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C9,'Base de Datos'!$G:$G,$D9,'Base de Datos'!$H:$H,$E9,'Base de Datos'!$U:$U,$F9,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -44004,11 +44097,11 @@
       </c>
       <c r="H10" s="29" cm="1">
         <f t="array" ref="H10">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C10))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D10))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E10))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F10))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C10,'Base de Datos'!$G:$G,$D10,'Base de Datos'!$H:$H,$E10,'Base de Datos'!$U:$U,$F10,'Base de Datos'!$AA:$AA,"Abierta")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C10,'Base de Datos'!$G:$G,$D10,'Base de Datos'!$H:$H,$E10,'Base de Datos'!$U:$U,$F10,'Base de Datos'!$AA:$AA,"Vencida")</f>
@@ -44019,19 +44112,19 @@
         <v>0</v>
       </c>
       <c r="L10" s="29">
-        <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C10,'Base de Datos'!$G:$G,$D10,'Base de Datos'!$H:$H,$E10,'Base de Datos'!$U:$U,$F10,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
+        <f>COUNTIFS('Base de Datos'!$F:$F,$C10,'Base de Datos'!$G:$G,$D10,'Base de Datos'!$H:$H,$E10,'Base de Datos'!$U:$U,$F10,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
         <v>0</v>
       </c>
       <c r="M10" s="29">
-        <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C10,'Base de Datos'!$G:$G,$D10,'Base de Datos'!$H:$H,$E10,'Base de Datos'!$U:$U,$F10,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=20",'Base de Datos'!$AC:$AC,"&gt;10")</f>
-        <v>1</v>
+        <f>COUNTIFS('Base de Datos'!$F:$F,$C10,'Base de Datos'!$G:$G,$D10,'Base de Datos'!$H:$H,$E10,'Base de Datos'!$U:$U,$F10,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=20",'Base de Datos'!$AC:$AC,"&gt;10")</f>
+        <v>0</v>
       </c>
       <c r="N10" s="32">
-        <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C10,'Base de Datos'!$G:$G,$D10,'Base de Datos'!$H:$H,$E10,'Base de Datos'!$U:$U,$F10,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=30",'Base de Datos'!$AC:$AC,"&gt;20")</f>
+        <f>COUNTIFS('Base de Datos'!$F:$F,$C10,'Base de Datos'!$G:$G,$D10,'Base de Datos'!$H:$H,$E10,'Base de Datos'!$U:$U,$F10,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=30",'Base de Datos'!$AC:$AC,"&gt;20")</f>
         <v>0</v>
       </c>
       <c r="O10" s="29">
-        <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C10,'Base de Datos'!$G:$G,$D10,'Base de Datos'!$H:$H,$E10,'Base de Datos'!$U:$U,$F10,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AG:$AG,1)</f>
+        <f>COUNTIFS('Base de Datos'!$F:$F,$C10,'Base de Datos'!$G:$G,$D10,'Base de Datos'!$H:$H,$E10,'Base de Datos'!$U:$U,$F10,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AG:$AG,1)</f>
         <v>0</v>
       </c>
       <c r="P10" s="29" t="e">
@@ -44078,11 +44171,11 @@
       </c>
       <c r="H11" s="29" cm="1">
         <f t="array" ref="H11">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C11))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D11))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E11))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F11))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C11,'Base de Datos'!$G:$G,$D11,'Base de Datos'!$H:$H,$E11,'Base de Datos'!$U:$U,$F11,'Base de Datos'!$AA:$AA,"Abierta")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C11,'Base de Datos'!$G:$G,$D11,'Base de Datos'!$H:$H,$E11,'Base de Datos'!$U:$U,$F11,'Base de Datos'!$AA:$AA,"Vencida")</f>
@@ -44093,19 +44186,19 @@
         <v>0</v>
       </c>
       <c r="L11" s="29">
-        <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C11,'Base de Datos'!$G:$G,$D11,'Base de Datos'!$H:$H,$E11,'Base de Datos'!$U:$U,$F11,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
+        <f>COUNTIFS('Base de Datos'!$F:$F,$C11,'Base de Datos'!$G:$G,$D11,'Base de Datos'!$H:$H,$E11,'Base de Datos'!$U:$U,$F11,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
         <v>0</v>
       </c>
       <c r="M11" s="29">
-        <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C11,'Base de Datos'!$G:$G,$D11,'Base de Datos'!$H:$H,$E11,'Base de Datos'!$U:$U,$F11,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=20",'Base de Datos'!$AC:$AC,"&gt;10")</f>
-        <v>1</v>
+        <f>COUNTIFS('Base de Datos'!$F:$F,$C11,'Base de Datos'!$G:$G,$D11,'Base de Datos'!$H:$H,$E11,'Base de Datos'!$U:$U,$F11,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=20",'Base de Datos'!$AC:$AC,"&gt;10")</f>
+        <v>0</v>
       </c>
       <c r="N11" s="32">
-        <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C11,'Base de Datos'!$G:$G,$D11,'Base de Datos'!$H:$H,$E11,'Base de Datos'!$U:$U,$F11,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=30",'Base de Datos'!$AC:$AC,"&gt;20")</f>
+        <f>COUNTIFS('Base de Datos'!$F:$F,$C11,'Base de Datos'!$G:$G,$D11,'Base de Datos'!$H:$H,$E11,'Base de Datos'!$U:$U,$F11,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=30",'Base de Datos'!$AC:$AC,"&gt;20")</f>
         <v>0</v>
       </c>
       <c r="O11" s="29">
-        <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C11,'Base de Datos'!$G:$G,$D11,'Base de Datos'!$H:$H,$E11,'Base de Datos'!$U:$U,$F11,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AG:$AG,1)</f>
+        <f>COUNTIFS('Base de Datos'!$F:$F,$C11,'Base de Datos'!$G:$G,$D11,'Base de Datos'!$H:$H,$E11,'Base de Datos'!$U:$U,$F11,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AG:$AG,1)</f>
         <v>0</v>
       </c>
       <c r="P11" s="29" t="e">
@@ -44152,7 +44245,7 @@
       </c>
       <c r="H12" s="29" cm="1">
         <f t="array" ref="H12">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C12))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D12))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E12))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F12))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C12,'Base de Datos'!$G:$G,$D12,'Base de Datos'!$H:$H,$E12,'Base de Datos'!$U:$U,$F12,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -44164,7 +44257,7 @@
       </c>
       <c r="K12" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C12,'Base de Datos'!$G:$G,$D12,'Base de Datos'!$H:$H,$E12,'Base de Datos'!$U:$U,$F12,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C12,'Base de Datos'!$G:$G,$D12,'Base de Datos'!$H:$H,$E12,'Base de Datos'!$U:$U,$F12,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -44226,7 +44319,7 @@
       </c>
       <c r="H13" s="29" cm="1">
         <f t="array" ref="H13">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C13))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D13))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E13))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F13))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C13,'Base de Datos'!$G:$G,$D13,'Base de Datos'!$H:$H,$E13,'Base de Datos'!$U:$U,$F13,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -44238,7 +44331,7 @@
       </c>
       <c r="K13" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C13,'Base de Datos'!$G:$G,$D13,'Base de Datos'!$H:$H,$E13,'Base de Datos'!$U:$U,$F13,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C13,'Base de Datos'!$G:$G,$D13,'Base de Datos'!$H:$H,$E13,'Base de Datos'!$U:$U,$F13,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -44374,11 +44467,11 @@
       </c>
       <c r="H15" s="29" cm="1">
         <f t="array" ref="H15">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C15))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D15))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E15))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F15))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C15,'Base de Datos'!$G:$G,$D15,'Base de Datos'!$H:$H,$E15,'Base de Datos'!$U:$U,$F15,'Base de Datos'!$AA:$AA,"Abierta")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C15,'Base de Datos'!$G:$G,$D15,'Base de Datos'!$H:$H,$E15,'Base de Datos'!$U:$U,$F15,'Base de Datos'!$AA:$AA,"Vencida")</f>
@@ -44389,19 +44482,19 @@
         <v>0</v>
       </c>
       <c r="L15" s="29">
-        <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C15,'Base de Datos'!$G:$G,$D15,'Base de Datos'!$H:$H,$E15,'Base de Datos'!$U:$U,$F15,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
+        <f>COUNTIFS('Base de Datos'!$F:$F,$C15,'Base de Datos'!$G:$G,$D15,'Base de Datos'!$H:$H,$E15,'Base de Datos'!$U:$U,$F15,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
         <v>0</v>
       </c>
       <c r="M15" s="29">
-        <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C15,'Base de Datos'!$G:$G,$D15,'Base de Datos'!$H:$H,$E15,'Base de Datos'!$U:$U,$F15,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=20",'Base de Datos'!$AC:$AC,"&gt;10")</f>
-        <v>1</v>
+        <f>COUNTIFS('Base de Datos'!$F:$F,$C15,'Base de Datos'!$G:$G,$D15,'Base de Datos'!$H:$H,$E15,'Base de Datos'!$U:$U,$F15,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=20",'Base de Datos'!$AC:$AC,"&gt;10")</f>
+        <v>0</v>
       </c>
       <c r="N15" s="32">
-        <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C15,'Base de Datos'!$G:$G,$D15,'Base de Datos'!$H:$H,$E15,'Base de Datos'!$U:$U,$F15,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=30",'Base de Datos'!$AC:$AC,"&gt;20")</f>
+        <f>COUNTIFS('Base de Datos'!$F:$F,$C15,'Base de Datos'!$G:$G,$D15,'Base de Datos'!$H:$H,$E15,'Base de Datos'!$U:$U,$F15,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=30",'Base de Datos'!$AC:$AC,"&gt;20")</f>
         <v>0</v>
       </c>
       <c r="O15" s="29">
-        <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C15,'Base de Datos'!$G:$G,$D15,'Base de Datos'!$H:$H,$E15,'Base de Datos'!$U:$U,$F15,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AG:$AG,1)</f>
+        <f>COUNTIFS('Base de Datos'!$F:$F,$C15,'Base de Datos'!$G:$G,$D15,'Base de Datos'!$H:$H,$E15,'Base de Datos'!$U:$U,$F15,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AG:$AG,1)</f>
         <v>0</v>
       </c>
       <c r="P15" s="29" t="e">
@@ -44448,7 +44541,7 @@
       </c>
       <c r="H16" s="29" cm="1">
         <f t="array" ref="H16">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C16))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D16))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E16))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F16))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C16,'Base de Datos'!$G:$G,$D16,'Base de Datos'!$H:$H,$E16,'Base de Datos'!$U:$U,$F16,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -44460,7 +44553,7 @@
       </c>
       <c r="K16" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C16,'Base de Datos'!$G:$G,$D16,'Base de Datos'!$H:$H,$E16,'Base de Datos'!$U:$U,$F16,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C16,'Base de Datos'!$G:$G,$D16,'Base de Datos'!$H:$H,$E16,'Base de Datos'!$U:$U,$F16,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -44522,7 +44615,7 @@
       </c>
       <c r="H17" s="29" cm="1">
         <f t="array" ref="H17">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C17))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D17))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E17))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F17))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C17,'Base de Datos'!$G:$G,$D17,'Base de Datos'!$H:$H,$E17,'Base de Datos'!$U:$U,$F17,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -44534,7 +44627,7 @@
       </c>
       <c r="K17" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C17,'Base de Datos'!$G:$G,$D17,'Base de Datos'!$H:$H,$E17,'Base de Datos'!$U:$U,$F17,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C17,'Base de Datos'!$G:$G,$D17,'Base de Datos'!$H:$H,$E17,'Base de Datos'!$U:$U,$F17,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -44596,7 +44689,7 @@
       </c>
       <c r="H18" s="29" cm="1">
         <f t="array" ref="H18">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C18))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D18))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E18))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F18))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C18,'Base de Datos'!$G:$G,$D18,'Base de Datos'!$H:$H,$E18,'Base de Datos'!$U:$U,$F18,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -44608,7 +44701,7 @@
       </c>
       <c r="K18" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C18,'Base de Datos'!$G:$G,$D18,'Base de Datos'!$H:$H,$E18,'Base de Datos'!$U:$U,$F18,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C18,'Base de Datos'!$G:$G,$D18,'Base de Datos'!$H:$H,$E18,'Base de Datos'!$U:$U,$F18,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -44670,7 +44763,7 @@
       </c>
       <c r="H19" s="29" cm="1">
         <f t="array" ref="H19">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C19))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D19))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E19))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F19))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C19,'Base de Datos'!$G:$G,$D19,'Base de Datos'!$H:$H,$E19,'Base de Datos'!$U:$U,$F19,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -44682,7 +44775,7 @@
       </c>
       <c r="K19" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C19,'Base de Datos'!$G:$G,$D19,'Base de Datos'!$H:$H,$E19,'Base de Datos'!$U:$U,$F19,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C19,'Base de Datos'!$G:$G,$D19,'Base de Datos'!$H:$H,$E19,'Base de Datos'!$U:$U,$F19,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -44744,7 +44837,7 @@
       </c>
       <c r="H20" s="29" cm="1">
         <f t="array" ref="H20">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C20))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D20))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E20))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F20))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C20,'Base de Datos'!$G:$G,$D20,'Base de Datos'!$H:$H,$E20,'Base de Datos'!$U:$U,$F20,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -44752,7 +44845,7 @@
       </c>
       <c r="J20" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C20,'Base de Datos'!$G:$G,$D20,'Base de Datos'!$H:$H,$E20,'Base de Datos'!$U:$U,$F20,'Base de Datos'!$AA:$AA,"Vencida")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C20,'Base de Datos'!$G:$G,$D20,'Base de Datos'!$H:$H,$E20,'Base de Datos'!$U:$U,$F20,'Base de Datos'!$AA:$AA,"Finalizada")</f>
@@ -44818,7 +44911,7 @@
       </c>
       <c r="H21" s="29" cm="1">
         <f t="array" ref="H21">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C21))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D21))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E21))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F21))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C21,'Base de Datos'!$G:$G,$D21,'Base de Datos'!$H:$H,$E21,'Base de Datos'!$U:$U,$F21,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -44826,7 +44919,7 @@
       </c>
       <c r="J21" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C21,'Base de Datos'!$G:$G,$D21,'Base de Datos'!$H:$H,$E21,'Base de Datos'!$U:$U,$F21,'Base de Datos'!$AA:$AA,"Vencida")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C21,'Base de Datos'!$G:$G,$D21,'Base de Datos'!$H:$H,$E21,'Base de Datos'!$U:$U,$F21,'Base de Datos'!$AA:$AA,"Finalizada")</f>
@@ -44892,7 +44985,7 @@
       </c>
       <c r="H22" s="29" cm="1">
         <f t="array" ref="H22">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C22))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D22))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E22))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F22))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C22,'Base de Datos'!$G:$G,$D22,'Base de Datos'!$H:$H,$E22,'Base de Datos'!$U:$U,$F22,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -44900,7 +44993,7 @@
       </c>
       <c r="J22" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C22,'Base de Datos'!$G:$G,$D22,'Base de Datos'!$H:$H,$E22,'Base de Datos'!$U:$U,$F22,'Base de Datos'!$AA:$AA,"Vencida")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C22,'Base de Datos'!$G:$G,$D22,'Base de Datos'!$H:$H,$E22,'Base de Datos'!$U:$U,$F22,'Base de Datos'!$AA:$AA,"Finalizada")</f>
@@ -44966,7 +45059,7 @@
       </c>
       <c r="H23" s="29" cm="1">
         <f t="array" ref="H23">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C23))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D23))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E23))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F23))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C23,'Base de Datos'!$G:$G,$D23,'Base de Datos'!$H:$H,$E23,'Base de Datos'!$U:$U,$F23,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -44978,7 +45071,7 @@
       </c>
       <c r="K23" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C23,'Base de Datos'!$G:$G,$D23,'Base de Datos'!$H:$H,$E23,'Base de Datos'!$U:$U,$F23,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C23,'Base de Datos'!$G:$G,$D23,'Base de Datos'!$H:$H,$E23,'Base de Datos'!$U:$U,$F23,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -45040,7 +45133,7 @@
       </c>
       <c r="H24" s="29" cm="1">
         <f t="array" ref="H24">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C24))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D24))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E24))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F24))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C24,'Base de Datos'!$G:$G,$D24,'Base de Datos'!$H:$H,$E24,'Base de Datos'!$U:$U,$F24,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -45052,7 +45145,7 @@
       </c>
       <c r="K24" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C24,'Base de Datos'!$G:$G,$D24,'Base de Datos'!$H:$H,$E24,'Base de Datos'!$U:$U,$F24,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C24,'Base de Datos'!$G:$G,$D24,'Base de Datos'!$H:$H,$E24,'Base de Datos'!$U:$U,$F24,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -45114,11 +45207,11 @@
       </c>
       <c r="H25" s="29" cm="1">
         <f t="array" ref="H25">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C25))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D25))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E25))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F25))&amp;""))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I25" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C25,'Base de Datos'!$G:$G,$D25,'Base de Datos'!$H:$H,$E25,'Base de Datos'!$U:$U,$F25,'Base de Datos'!$AA:$AA,"Abierta")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J25" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C25,'Base de Datos'!$G:$G,$D25,'Base de Datos'!$H:$H,$E25,'Base de Datos'!$U:$U,$F25,'Base de Datos'!$AA:$AA,"Vencida")</f>
@@ -45129,19 +45222,19 @@
         <v>0</v>
       </c>
       <c r="L25" s="29">
-        <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C25,'Base de Datos'!$G:$G,$D25,'Base de Datos'!$H:$H,$E25,'Base de Datos'!$U:$U,$F25,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
+        <f>COUNTIFS('Base de Datos'!$F:$F,$C25,'Base de Datos'!$G:$G,$D25,'Base de Datos'!$H:$H,$E25,'Base de Datos'!$U:$U,$F25,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
         <v>0</v>
       </c>
       <c r="M25" s="29">
-        <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C25,'Base de Datos'!$G:$G,$D25,'Base de Datos'!$H:$H,$E25,'Base de Datos'!$U:$U,$F25,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=20",'Base de Datos'!$AC:$AC,"&gt;10")</f>
-        <v>2</v>
+        <f>COUNTIFS('Base de Datos'!$F:$F,$C25,'Base de Datos'!$G:$G,$D25,'Base de Datos'!$H:$H,$E25,'Base de Datos'!$U:$U,$F25,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=20",'Base de Datos'!$AC:$AC,"&gt;10")</f>
+        <v>0</v>
       </c>
       <c r="N25" s="32">
-        <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C25,'Base de Datos'!$G:$G,$D25,'Base de Datos'!$H:$H,$E25,'Base de Datos'!$U:$U,$F25,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=30",'Base de Datos'!$AC:$AC,"&gt;20")</f>
+        <f>COUNTIFS('Base de Datos'!$F:$F,$C25,'Base de Datos'!$G:$G,$D25,'Base de Datos'!$H:$H,$E25,'Base de Datos'!$U:$U,$F25,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=30",'Base de Datos'!$AC:$AC,"&gt;20")</f>
         <v>0</v>
       </c>
       <c r="O25" s="29">
-        <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C25,'Base de Datos'!$G:$G,$D25,'Base de Datos'!$H:$H,$E25,'Base de Datos'!$U:$U,$F25,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AG:$AG,1)</f>
+        <f>COUNTIFS('Base de Datos'!$F:$F,$C25,'Base de Datos'!$G:$G,$D25,'Base de Datos'!$H:$H,$E25,'Base de Datos'!$U:$U,$F25,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AG:$AG,1)</f>
         <v>0</v>
       </c>
       <c r="P25" s="29" t="e">
@@ -45192,11 +45285,11 @@
       </c>
       <c r="H26" s="29" cm="1">
         <f t="array" ref="H26">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C26))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D26))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E26))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F26))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C26,'Base de Datos'!$G:$G,$D26,'Base de Datos'!$H:$H,$E26,'Base de Datos'!$U:$U,$F26,'Base de Datos'!$AA:$AA,"Abierta")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C26,'Base de Datos'!$G:$G,$D26,'Base de Datos'!$H:$H,$E26,'Base de Datos'!$U:$U,$F26,'Base de Datos'!$AA:$AA,"Vencida")</f>
@@ -45207,19 +45300,19 @@
         <v>0</v>
       </c>
       <c r="L26" s="29">
-        <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C26,'Base de Datos'!$G:$G,$D26,'Base de Datos'!$H:$H,$E26,'Base de Datos'!$U:$U,$F26,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
+        <f>COUNTIFS('Base de Datos'!$F:$F,$C26,'Base de Datos'!$G:$G,$D26,'Base de Datos'!$H:$H,$E26,'Base de Datos'!$U:$U,$F26,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
         <v>0</v>
       </c>
       <c r="M26" s="29">
-        <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C26,'Base de Datos'!$G:$G,$D26,'Base de Datos'!$H:$H,$E26,'Base de Datos'!$U:$U,$F26,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=20",'Base de Datos'!$AC:$AC,"&gt;10")</f>
-        <v>1</v>
+        <f>COUNTIFS('Base de Datos'!$F:$F,$C26,'Base de Datos'!$G:$G,$D26,'Base de Datos'!$H:$H,$E26,'Base de Datos'!$U:$U,$F26,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=20",'Base de Datos'!$AC:$AC,"&gt;10")</f>
+        <v>0</v>
       </c>
       <c r="N26" s="32">
-        <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C26,'Base de Datos'!$G:$G,$D26,'Base de Datos'!$H:$H,$E26,'Base de Datos'!$U:$U,$F26,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=30",'Base de Datos'!$AC:$AC,"&gt;20")</f>
+        <f>COUNTIFS('Base de Datos'!$F:$F,$C26,'Base de Datos'!$G:$G,$D26,'Base de Datos'!$H:$H,$E26,'Base de Datos'!$U:$U,$F26,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=30",'Base de Datos'!$AC:$AC,"&gt;20")</f>
         <v>0</v>
       </c>
       <c r="O26" s="29">
-        <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C26,'Base de Datos'!$G:$G,$D26,'Base de Datos'!$H:$H,$E26,'Base de Datos'!$U:$U,$F26,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AG:$AG,1)</f>
+        <f>COUNTIFS('Base de Datos'!$F:$F,$C26,'Base de Datos'!$G:$G,$D26,'Base de Datos'!$H:$H,$E26,'Base de Datos'!$U:$U,$F26,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AG:$AG,1)</f>
         <v>0</v>
       </c>
       <c r="P26" s="29" t="e">
@@ -45266,11 +45359,11 @@
       </c>
       <c r="H27" s="29" cm="1">
         <f t="array" ref="H27">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C27))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D27))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E27))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F27))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C27,'Base de Datos'!$G:$G,$D27,'Base de Datos'!$H:$H,$E27,'Base de Datos'!$U:$U,$F27,'Base de Datos'!$AA:$AA,"Abierta")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C27,'Base de Datos'!$G:$G,$D27,'Base de Datos'!$H:$H,$E27,'Base de Datos'!$U:$U,$F27,'Base de Datos'!$AA:$AA,"Vencida")</f>
@@ -45281,19 +45374,19 @@
         <v>0</v>
       </c>
       <c r="L27" s="29">
-        <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C27,'Base de Datos'!$G:$G,$D27,'Base de Datos'!$H:$H,$E27,'Base de Datos'!$U:$U,$F27,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
+        <f>COUNTIFS('Base de Datos'!$F:$F,$C27,'Base de Datos'!$G:$G,$D27,'Base de Datos'!$H:$H,$E27,'Base de Datos'!$U:$U,$F27,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
         <v>0</v>
       </c>
       <c r="M27" s="29">
-        <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C27,'Base de Datos'!$G:$G,$D27,'Base de Datos'!$H:$H,$E27,'Base de Datos'!$U:$U,$F27,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=20",'Base de Datos'!$AC:$AC,"&gt;10")</f>
-        <v>1</v>
+        <f>COUNTIFS('Base de Datos'!$F:$F,$C27,'Base de Datos'!$G:$G,$D27,'Base de Datos'!$H:$H,$E27,'Base de Datos'!$U:$U,$F27,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=20",'Base de Datos'!$AC:$AC,"&gt;10")</f>
+        <v>0</v>
       </c>
       <c r="N27" s="32">
-        <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C27,'Base de Datos'!$G:$G,$D27,'Base de Datos'!$H:$H,$E27,'Base de Datos'!$U:$U,$F27,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=30",'Base de Datos'!$AC:$AC,"&gt;20")</f>
+        <f>COUNTIFS('Base de Datos'!$F:$F,$C27,'Base de Datos'!$G:$G,$D27,'Base de Datos'!$H:$H,$E27,'Base de Datos'!$U:$U,$F27,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=30",'Base de Datos'!$AC:$AC,"&gt;20")</f>
         <v>0</v>
       </c>
       <c r="O27" s="29">
-        <f ca="1">COUNTIFS('Base de Datos'!$F:$F,$C27,'Base de Datos'!$G:$G,$D27,'Base de Datos'!$H:$H,$E27,'Base de Datos'!$U:$U,$F27,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AG:$AG,1)</f>
+        <f>COUNTIFS('Base de Datos'!$F:$F,$C27,'Base de Datos'!$G:$G,$D27,'Base de Datos'!$H:$H,$E27,'Base de Datos'!$U:$U,$F27,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AG:$AG,1)</f>
         <v>0</v>
       </c>
       <c r="P27" s="29" t="e">
@@ -45340,7 +45433,7 @@
       </c>
       <c r="H28" s="29" cm="1">
         <f t="array" ref="H28">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C28))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D28))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E28))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F28))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C28,'Base de Datos'!$G:$G,$D28,'Base de Datos'!$H:$H,$E28,'Base de Datos'!$U:$U,$F28,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -45352,7 +45445,7 @@
       </c>
       <c r="K28" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C28,'Base de Datos'!$G:$G,$D28,'Base de Datos'!$H:$H,$E28,'Base de Datos'!$U:$U,$F28,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C28,'Base de Datos'!$G:$G,$D28,'Base de Datos'!$H:$H,$E28,'Base de Datos'!$U:$U,$F28,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -45414,7 +45507,7 @@
       </c>
       <c r="H29" s="29" cm="1">
         <f t="array" ref="H29">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C29))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D29))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E29))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F29))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C29,'Base de Datos'!$G:$G,$D29,'Base de Datos'!$H:$H,$E29,'Base de Datos'!$U:$U,$F29,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -45426,7 +45519,7 @@
       </c>
       <c r="K29" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C29,'Base de Datos'!$G:$G,$D29,'Base de Datos'!$H:$H,$E29,'Base de Datos'!$U:$U,$F29,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C29,'Base de Datos'!$G:$G,$D29,'Base de Datos'!$H:$H,$E29,'Base de Datos'!$U:$U,$F29,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -45488,7 +45581,7 @@
       </c>
       <c r="H30" s="29" cm="1">
         <f t="array" ref="H30">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C30))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D30))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E30))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F30))&amp;""))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I30" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C30,'Base de Datos'!$G:$G,$D30,'Base de Datos'!$H:$H,$E30,'Base de Datos'!$U:$U,$F30,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -45496,11 +45589,11 @@
       </c>
       <c r="J30" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C30,'Base de Datos'!$G:$G,$D30,'Base de Datos'!$H:$H,$E30,'Base de Datos'!$U:$U,$F30,'Base de Datos'!$AA:$AA,"Vencida")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C30,'Base de Datos'!$G:$G,$D30,'Base de Datos'!$H:$H,$E30,'Base de Datos'!$U:$U,$F30,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C30,'Base de Datos'!$G:$G,$D30,'Base de Datos'!$H:$H,$E30,'Base de Datos'!$U:$U,$F30,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -45562,7 +45655,7 @@
       </c>
       <c r="H31" s="29" cm="1">
         <f t="array" ref="H31">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C31))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D31))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E31))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F31))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C31,'Base de Datos'!$G:$G,$D31,'Base de Datos'!$H:$H,$E31,'Base de Datos'!$U:$U,$F31,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -45574,7 +45667,7 @@
       </c>
       <c r="K31" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C31,'Base de Datos'!$G:$G,$D31,'Base de Datos'!$H:$H,$E31,'Base de Datos'!$U:$U,$F31,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C31,'Base de Datos'!$G:$G,$D31,'Base de Datos'!$H:$H,$E31,'Base de Datos'!$U:$U,$F31,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -45636,7 +45729,7 @@
       </c>
       <c r="H32" s="29" cm="1">
         <f t="array" ref="H32">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C32))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D32))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E32))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F32))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C32,'Base de Datos'!$G:$G,$D32,'Base de Datos'!$H:$H,$E32,'Base de Datos'!$U:$U,$F32,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -45648,7 +45741,7 @@
       </c>
       <c r="K32" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C32,'Base de Datos'!$G:$G,$D32,'Base de Datos'!$H:$H,$E32,'Base de Datos'!$U:$U,$F32,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C32,'Base de Datos'!$G:$G,$D32,'Base de Datos'!$H:$H,$E32,'Base de Datos'!$U:$U,$F32,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -45710,7 +45803,7 @@
       </c>
       <c r="H33" s="29" cm="1">
         <f t="array" ref="H33">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C33))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D33))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E33))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F33))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C33,'Base de Datos'!$G:$G,$D33,'Base de Datos'!$H:$H,$E33,'Base de Datos'!$U:$U,$F33,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -45722,7 +45815,7 @@
       </c>
       <c r="K33" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C33,'Base de Datos'!$G:$G,$D33,'Base de Datos'!$H:$H,$E33,'Base de Datos'!$U:$U,$F33,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C33,'Base de Datos'!$G:$G,$D33,'Base de Datos'!$H:$H,$E33,'Base de Datos'!$U:$U,$F33,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -45784,7 +45877,7 @@
       </c>
       <c r="H34" s="29" cm="1">
         <f t="array" ref="H34">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C34))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D34))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E34))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F34))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C34,'Base de Datos'!$G:$G,$D34,'Base de Datos'!$H:$H,$E34,'Base de Datos'!$U:$U,$F34,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -45796,7 +45889,7 @@
       </c>
       <c r="K34" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C34,'Base de Datos'!$G:$G,$D34,'Base de Datos'!$H:$H,$E34,'Base de Datos'!$U:$U,$F34,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C34,'Base de Datos'!$G:$G,$D34,'Base de Datos'!$H:$H,$E34,'Base de Datos'!$U:$U,$F34,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -45858,7 +45951,7 @@
       </c>
       <c r="H35" s="29" cm="1">
         <f t="array" ref="H35">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C35))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D35))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E35))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F35))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C35,'Base de Datos'!$G:$G,$D35,'Base de Datos'!$H:$H,$E35,'Base de Datos'!$U:$U,$F35,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -45870,7 +45963,7 @@
       </c>
       <c r="K35" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C35,'Base de Datos'!$G:$G,$D35,'Base de Datos'!$H:$H,$E35,'Base de Datos'!$U:$U,$F35,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C35,'Base de Datos'!$G:$G,$D35,'Base de Datos'!$H:$H,$E35,'Base de Datos'!$U:$U,$F35,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -45932,7 +46025,7 @@
       </c>
       <c r="H36" s="29" cm="1">
         <f t="array" ref="H36">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C36))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D36))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E36))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F36))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C36,'Base de Datos'!$G:$G,$D36,'Base de Datos'!$H:$H,$E36,'Base de Datos'!$U:$U,$F36,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -45940,7 +46033,7 @@
       </c>
       <c r="J36" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C36,'Base de Datos'!$G:$G,$D36,'Base de Datos'!$H:$H,$E36,'Base de Datos'!$U:$U,$F36,'Base de Datos'!$AA:$AA,"Vencida")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C36,'Base de Datos'!$G:$G,$D36,'Base de Datos'!$H:$H,$E36,'Base de Datos'!$U:$U,$F36,'Base de Datos'!$AA:$AA,"Finalizada")</f>
@@ -46006,7 +46099,7 @@
       </c>
       <c r="H37" s="29" cm="1">
         <f t="array" ref="H37">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C37))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D37))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E37))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F37))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C37,'Base de Datos'!$G:$G,$D37,'Base de Datos'!$H:$H,$E37,'Base de Datos'!$U:$U,$F37,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -46018,7 +46111,7 @@
       </c>
       <c r="K37" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C37,'Base de Datos'!$G:$G,$D37,'Base de Datos'!$H:$H,$E37,'Base de Datos'!$U:$U,$F37,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C37,'Base de Datos'!$G:$G,$D37,'Base de Datos'!$H:$H,$E37,'Base de Datos'!$U:$U,$F37,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -46080,7 +46173,7 @@
       </c>
       <c r="H38" s="29" cm="1">
         <f t="array" ref="H38">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C38))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D38))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E38))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F38))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C38,'Base de Datos'!$G:$G,$D38,'Base de Datos'!$H:$H,$E38,'Base de Datos'!$U:$U,$F38,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -46092,7 +46185,7 @@
       </c>
       <c r="K38" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C38,'Base de Datos'!$G:$G,$D38,'Base de Datos'!$H:$H,$E38,'Base de Datos'!$U:$U,$F38,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C38,'Base de Datos'!$G:$G,$D38,'Base de Datos'!$H:$H,$E38,'Base de Datos'!$U:$U,$F38,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -46154,7 +46247,7 @@
       </c>
       <c r="H39" s="29" cm="1">
         <f t="array" ref="H39">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C39))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D39))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E39))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F39))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C39,'Base de Datos'!$G:$G,$D39,'Base de Datos'!$H:$H,$E39,'Base de Datos'!$U:$U,$F39,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -46166,7 +46259,7 @@
       </c>
       <c r="K39" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C39,'Base de Datos'!$G:$G,$D39,'Base de Datos'!$H:$H,$E39,'Base de Datos'!$U:$U,$F39,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C39,'Base de Datos'!$G:$G,$D39,'Base de Datos'!$H:$H,$E39,'Base de Datos'!$U:$U,$F39,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -46228,7 +46321,7 @@
       </c>
       <c r="H40" s="29" cm="1">
         <f t="array" ref="H40">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C40))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D40))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E40))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F40))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C40,'Base de Datos'!$G:$G,$D40,'Base de Datos'!$H:$H,$E40,'Base de Datos'!$U:$U,$F40,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -46236,7 +46329,7 @@
       </c>
       <c r="J40" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C40,'Base de Datos'!$G:$G,$D40,'Base de Datos'!$H:$H,$E40,'Base de Datos'!$U:$U,$F40,'Base de Datos'!$AA:$AA,"Vencida")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C40,'Base de Datos'!$G:$G,$D40,'Base de Datos'!$H:$H,$E40,'Base de Datos'!$U:$U,$F40,'Base de Datos'!$AA:$AA,"Finalizada")</f>
@@ -46302,7 +46395,7 @@
       </c>
       <c r="H41" s="29" cm="1">
         <f t="array" ref="H41">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C41))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D41))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E41))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F41))&amp;""))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I41" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C41,'Base de Datos'!$G:$G,$D41,'Base de Datos'!$H:$H,$E41,'Base de Datos'!$U:$U,$F41,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -46314,7 +46407,7 @@
       </c>
       <c r="K41" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C41,'Base de Datos'!$G:$G,$D41,'Base de Datos'!$H:$H,$E41,'Base de Datos'!$U:$U,$F41,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L41" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C41,'Base de Datos'!$G:$G,$D41,'Base de Datos'!$H:$H,$E41,'Base de Datos'!$U:$U,$F41,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -46376,7 +46469,7 @@
       </c>
       <c r="H42" s="29" cm="1">
         <f t="array" ref="H42">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C42))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D42))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E42))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F42))&amp;""))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I42" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C42,'Base de Datos'!$G:$G,$D42,'Base de Datos'!$H:$H,$E42,'Base de Datos'!$U:$U,$F42,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -46388,7 +46481,7 @@
       </c>
       <c r="K42" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C42,'Base de Datos'!$G:$G,$D42,'Base de Datos'!$H:$H,$E42,'Base de Datos'!$U:$U,$F42,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L42" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C42,'Base de Datos'!$G:$G,$D42,'Base de Datos'!$H:$H,$E42,'Base de Datos'!$U:$U,$F42,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -46450,7 +46543,7 @@
       </c>
       <c r="H43" s="29" cm="1">
         <f t="array" ref="H43">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C43))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D43))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E43))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F43))&amp;""))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I43" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C43,'Base de Datos'!$G:$G,$D43,'Base de Datos'!$H:$H,$E43,'Base de Datos'!$U:$U,$F43,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -46462,7 +46555,7 @@
       </c>
       <c r="K43" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C43,'Base de Datos'!$G:$G,$D43,'Base de Datos'!$H:$H,$E43,'Base de Datos'!$U:$U,$F43,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L43" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C43,'Base de Datos'!$G:$G,$D43,'Base de Datos'!$H:$H,$E43,'Base de Datos'!$U:$U,$F43,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -46524,7 +46617,7 @@
       </c>
       <c r="H44" s="29" cm="1">
         <f t="array" ref="H44">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C44))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D44))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E44))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F44))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C44,'Base de Datos'!$G:$G,$D44,'Base de Datos'!$H:$H,$E44,'Base de Datos'!$U:$U,$F44,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -46536,7 +46629,7 @@
       </c>
       <c r="K44" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C44,'Base de Datos'!$G:$G,$D44,'Base de Datos'!$H:$H,$E44,'Base de Datos'!$U:$U,$F44,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C44,'Base de Datos'!$G:$G,$D44,'Base de Datos'!$H:$H,$E44,'Base de Datos'!$U:$U,$F44,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -46598,7 +46691,7 @@
       </c>
       <c r="H45" s="29" cm="1">
         <f t="array" ref="H45">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C45))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D45))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E45))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F45))&amp;""))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I45" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C45,'Base de Datos'!$G:$G,$D45,'Base de Datos'!$H:$H,$E45,'Base de Datos'!$U:$U,$F45,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -46610,7 +46703,7 @@
       </c>
       <c r="K45" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C45,'Base de Datos'!$G:$G,$D45,'Base de Datos'!$H:$H,$E45,'Base de Datos'!$U:$U,$F45,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L45" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C45,'Base de Datos'!$G:$G,$D45,'Base de Datos'!$H:$H,$E45,'Base de Datos'!$U:$U,$F45,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -46672,7 +46765,7 @@
       </c>
       <c r="H46" s="29" cm="1">
         <f t="array" ref="H46">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C46))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D46))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E46))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F46))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C46,'Base de Datos'!$G:$G,$D46,'Base de Datos'!$H:$H,$E46,'Base de Datos'!$U:$U,$F46,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -46684,7 +46777,7 @@
       </c>
       <c r="K46" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C46,'Base de Datos'!$G:$G,$D46,'Base de Datos'!$H:$H,$E46,'Base de Datos'!$U:$U,$F46,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C46,'Base de Datos'!$G:$G,$D46,'Base de Datos'!$H:$H,$E46,'Base de Datos'!$U:$U,$F46,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -46746,7 +46839,7 @@
       </c>
       <c r="H47" s="29" cm="1">
         <f t="array" ref="H47">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C47))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D47))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E47))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F47))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C47,'Base de Datos'!$G:$G,$D47,'Base de Datos'!$H:$H,$E47,'Base de Datos'!$U:$U,$F47,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -46758,7 +46851,7 @@
       </c>
       <c r="K47" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C47,'Base de Datos'!$G:$G,$D47,'Base de Datos'!$H:$H,$E47,'Base de Datos'!$U:$U,$F47,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C47,'Base de Datos'!$G:$G,$D47,'Base de Datos'!$H:$H,$E47,'Base de Datos'!$U:$U,$F47,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -46820,7 +46913,7 @@
       </c>
       <c r="H48" s="29" cm="1">
         <f t="array" ref="H48">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C48))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D48))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E48))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F48))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I48" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C48,'Base de Datos'!$G:$G,$D48,'Base de Datos'!$H:$H,$E48,'Base de Datos'!$U:$U,$F48,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -46832,7 +46925,7 @@
       </c>
       <c r="K48" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C48,'Base de Datos'!$G:$G,$D48,'Base de Datos'!$H:$H,$E48,'Base de Datos'!$U:$U,$F48,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C48,'Base de Datos'!$G:$G,$D48,'Base de Datos'!$H:$H,$E48,'Base de Datos'!$U:$U,$F48,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -46894,7 +46987,7 @@
       </c>
       <c r="H49" s="29" cm="1">
         <f t="array" ref="H49">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C49))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D49))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E49))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F49))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I49" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C49,'Base de Datos'!$G:$G,$D49,'Base de Datos'!$H:$H,$E49,'Base de Datos'!$U:$U,$F49,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -46906,7 +46999,7 @@
       </c>
       <c r="K49" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C49,'Base de Datos'!$G:$G,$D49,'Base de Datos'!$H:$H,$E49,'Base de Datos'!$U:$U,$F49,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L49" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C49,'Base de Datos'!$G:$G,$D49,'Base de Datos'!$H:$H,$E49,'Base de Datos'!$U:$U,$F49,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -46968,7 +47061,7 @@
       </c>
       <c r="H50" s="29" cm="1">
         <f t="array" ref="H50">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C50))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D50))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E50))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F50))&amp;""))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I50" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C50,'Base de Datos'!$G:$G,$D50,'Base de Datos'!$H:$H,$E50,'Base de Datos'!$U:$U,$F50,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -46980,7 +47073,7 @@
       </c>
       <c r="K50" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C50,'Base de Datos'!$G:$G,$D50,'Base de Datos'!$H:$H,$E50,'Base de Datos'!$U:$U,$F50,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L50" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C50,'Base de Datos'!$G:$G,$D50,'Base de Datos'!$H:$H,$E50,'Base de Datos'!$U:$U,$F50,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -47042,7 +47135,7 @@
       </c>
       <c r="H51" s="29" cm="1">
         <f t="array" ref="H51">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C51))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D51))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E51))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F51))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I51" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C51,'Base de Datos'!$G:$G,$D51,'Base de Datos'!$H:$H,$E51,'Base de Datos'!$U:$U,$F51,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -47054,7 +47147,7 @@
       </c>
       <c r="K51" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C51,'Base de Datos'!$G:$G,$D51,'Base de Datos'!$H:$H,$E51,'Base de Datos'!$U:$U,$F51,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L51" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C51,'Base de Datos'!$G:$G,$D51,'Base de Datos'!$H:$H,$E51,'Base de Datos'!$U:$U,$F51,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -47116,7 +47209,7 @@
       </c>
       <c r="H52" s="29" cm="1">
         <f t="array" ref="H52">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C52))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D52))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E52))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F52))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I52" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C52,'Base de Datos'!$G:$G,$D52,'Base de Datos'!$H:$H,$E52,'Base de Datos'!$U:$U,$F52,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -47128,7 +47221,7 @@
       </c>
       <c r="K52" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C52,'Base de Datos'!$G:$G,$D52,'Base de Datos'!$H:$H,$E52,'Base de Datos'!$U:$U,$F52,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C52,'Base de Datos'!$G:$G,$D52,'Base de Datos'!$H:$H,$E52,'Base de Datos'!$U:$U,$F52,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -47190,7 +47283,7 @@
       </c>
       <c r="H53" s="29" cm="1">
         <f t="array" ref="H53">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C53))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D53))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E53))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F53))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C53,'Base de Datos'!$G:$G,$D53,'Base de Datos'!$H:$H,$E53,'Base de Datos'!$U:$U,$F53,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -47202,7 +47295,7 @@
       </c>
       <c r="K53" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C53,'Base de Datos'!$G:$G,$D53,'Base de Datos'!$H:$H,$E53,'Base de Datos'!$U:$U,$F53,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C53,'Base de Datos'!$G:$G,$D53,'Base de Datos'!$H:$H,$E53,'Base de Datos'!$U:$U,$F53,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -47264,7 +47357,7 @@
       </c>
       <c r="H54" s="29" cm="1">
         <f t="array" ref="H54">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C54))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D54))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E54))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F54))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I54" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C54,'Base de Datos'!$G:$G,$D54,'Base de Datos'!$H:$H,$E54,'Base de Datos'!$U:$U,$F54,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -47276,7 +47369,7 @@
       </c>
       <c r="K54" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C54,'Base de Datos'!$G:$G,$D54,'Base de Datos'!$H:$H,$E54,'Base de Datos'!$U:$U,$F54,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L54" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C54,'Base de Datos'!$G:$G,$D54,'Base de Datos'!$H:$H,$E54,'Base de Datos'!$U:$U,$F54,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -47338,7 +47431,7 @@
       </c>
       <c r="H55" s="29" cm="1">
         <f t="array" ref="H55">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C55))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D55))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E55))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F55))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I55" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C55,'Base de Datos'!$G:$G,$D55,'Base de Datos'!$H:$H,$E55,'Base de Datos'!$U:$U,$F55,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -47350,7 +47443,7 @@
       </c>
       <c r="K55" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C55,'Base de Datos'!$G:$G,$D55,'Base de Datos'!$H:$H,$E55,'Base de Datos'!$U:$U,$F55,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C55,'Base de Datos'!$G:$G,$D55,'Base de Datos'!$H:$H,$E55,'Base de Datos'!$U:$U,$F55,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -47412,7 +47505,7 @@
       </c>
       <c r="H56" s="29" cm="1">
         <f t="array" ref="H56">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C56))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D56))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E56))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F56))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I56" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C56,'Base de Datos'!$G:$G,$D56,'Base de Datos'!$H:$H,$E56,'Base de Datos'!$U:$U,$F56,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -47424,7 +47517,7 @@
       </c>
       <c r="K56" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C56,'Base de Datos'!$G:$G,$D56,'Base de Datos'!$H:$H,$E56,'Base de Datos'!$U:$U,$F56,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L56" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C56,'Base de Datos'!$G:$G,$D56,'Base de Datos'!$H:$H,$E56,'Base de Datos'!$U:$U,$F56,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -47486,7 +47579,7 @@
       </c>
       <c r="H57" s="29" cm="1">
         <f t="array" ref="H57">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C57))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D57))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E57))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F57))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I57" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C57,'Base de Datos'!$G:$G,$D57,'Base de Datos'!$H:$H,$E57,'Base de Datos'!$U:$U,$F57,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -47498,7 +47591,7 @@
       </c>
       <c r="K57" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C57,'Base de Datos'!$G:$G,$D57,'Base de Datos'!$H:$H,$E57,'Base de Datos'!$U:$U,$F57,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C57,'Base de Datos'!$G:$G,$D57,'Base de Datos'!$H:$H,$E57,'Base de Datos'!$U:$U,$F57,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -47560,7 +47653,7 @@
       </c>
       <c r="H58" s="29" cm="1">
         <f t="array" ref="H58">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C58))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D58))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E58))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F58))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I58" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C58,'Base de Datos'!$G:$G,$D58,'Base de Datos'!$H:$H,$E58,'Base de Datos'!$U:$U,$F58,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -47572,7 +47665,7 @@
       </c>
       <c r="K58" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C58,'Base de Datos'!$G:$G,$D58,'Base de Datos'!$H:$H,$E58,'Base de Datos'!$U:$U,$F58,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C58,'Base de Datos'!$G:$G,$D58,'Base de Datos'!$H:$H,$E58,'Base de Datos'!$U:$U,$F58,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -47634,7 +47727,7 @@
       </c>
       <c r="H59" s="29" cm="1">
         <f t="array" ref="H59">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C59))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D59))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E59))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F59))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I59" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C59,'Base de Datos'!$G:$G,$D59,'Base de Datos'!$H:$H,$E59,'Base de Datos'!$U:$U,$F59,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -47646,7 +47739,7 @@
       </c>
       <c r="K59" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C59,'Base de Datos'!$G:$G,$D59,'Base de Datos'!$H:$H,$E59,'Base de Datos'!$U:$U,$F59,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C59,'Base de Datos'!$G:$G,$D59,'Base de Datos'!$H:$H,$E59,'Base de Datos'!$U:$U,$F59,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -47708,7 +47801,7 @@
       </c>
       <c r="H60" s="29" cm="1">
         <f t="array" ref="H60">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C60))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D60))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E60))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F60))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I60" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C60,'Base de Datos'!$G:$G,$D60,'Base de Datos'!$H:$H,$E60,'Base de Datos'!$U:$U,$F60,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -47720,7 +47813,7 @@
       </c>
       <c r="K60" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C60,'Base de Datos'!$G:$G,$D60,'Base de Datos'!$H:$H,$E60,'Base de Datos'!$U:$U,$F60,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C60,'Base de Datos'!$G:$G,$D60,'Base de Datos'!$H:$H,$E60,'Base de Datos'!$U:$U,$F60,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -47782,7 +47875,7 @@
       </c>
       <c r="H61" s="29" cm="1">
         <f t="array" ref="H61">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C61))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D61))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E61))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F61))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I61" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C61,'Base de Datos'!$G:$G,$D61,'Base de Datos'!$H:$H,$E61,'Base de Datos'!$U:$U,$F61,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -47794,7 +47887,7 @@
       </c>
       <c r="K61" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C61,'Base de Datos'!$G:$G,$D61,'Base de Datos'!$H:$H,$E61,'Base de Datos'!$U:$U,$F61,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C61,'Base de Datos'!$G:$G,$D61,'Base de Datos'!$H:$H,$E61,'Base de Datos'!$U:$U,$F61,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -47856,7 +47949,7 @@
       </c>
       <c r="H62" s="29" cm="1">
         <f t="array" ref="H62">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C62))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D62))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E62))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F62))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I62" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C62,'Base de Datos'!$G:$G,$D62,'Base de Datos'!$H:$H,$E62,'Base de Datos'!$U:$U,$F62,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -47868,7 +47961,7 @@
       </c>
       <c r="K62" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C62,'Base de Datos'!$G:$G,$D62,'Base de Datos'!$H:$H,$E62,'Base de Datos'!$U:$U,$F62,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C62,'Base de Datos'!$G:$G,$D62,'Base de Datos'!$H:$H,$E62,'Base de Datos'!$U:$U,$F62,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -47930,7 +48023,7 @@
       </c>
       <c r="H63" s="29" cm="1">
         <f t="array" ref="H63">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C63))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D63))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E63))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F63))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I63" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C63,'Base de Datos'!$G:$G,$D63,'Base de Datos'!$H:$H,$E63,'Base de Datos'!$U:$U,$F63,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -47942,7 +48035,7 @@
       </c>
       <c r="K63" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C63,'Base de Datos'!$G:$G,$D63,'Base de Datos'!$H:$H,$E63,'Base de Datos'!$U:$U,$F63,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L63" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C63,'Base de Datos'!$G:$G,$D63,'Base de Datos'!$H:$H,$E63,'Base de Datos'!$U:$U,$F63,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -48004,7 +48097,7 @@
       </c>
       <c r="H64" s="29" cm="1">
         <f t="array" ref="H64">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C64))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D64))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E64))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F64))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I64" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C64,'Base de Datos'!$G:$G,$D64,'Base de Datos'!$H:$H,$E64,'Base de Datos'!$U:$U,$F64,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -48016,7 +48109,7 @@
       </c>
       <c r="K64" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C64,'Base de Datos'!$G:$G,$D64,'Base de Datos'!$H:$H,$E64,'Base de Datos'!$U:$U,$F64,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C64,'Base de Datos'!$G:$G,$D64,'Base de Datos'!$H:$H,$E64,'Base de Datos'!$U:$U,$F64,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -48078,7 +48171,7 @@
       </c>
       <c r="H65" s="29" cm="1">
         <f t="array" ref="H65">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C65))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D65))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E65))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F65))&amp;""))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I65" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C65,'Base de Datos'!$G:$G,$D65,'Base de Datos'!$H:$H,$E65,'Base de Datos'!$U:$U,$F65,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -48090,7 +48183,7 @@
       </c>
       <c r="K65" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C65,'Base de Datos'!$G:$G,$D65,'Base de Datos'!$H:$H,$E65,'Base de Datos'!$U:$U,$F65,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L65" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C65,'Base de Datos'!$G:$G,$D65,'Base de Datos'!$H:$H,$E65,'Base de Datos'!$U:$U,$F65,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -48152,7 +48245,7 @@
       </c>
       <c r="H66" s="29" cm="1">
         <f t="array" ref="H66">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C66))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D66))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E66))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F66))&amp;""))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I66" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C66,'Base de Datos'!$G:$G,$D66,'Base de Datos'!$H:$H,$E66,'Base de Datos'!$U:$U,$F66,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -48164,7 +48257,7 @@
       </c>
       <c r="K66" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C66,'Base de Datos'!$G:$G,$D66,'Base de Datos'!$H:$H,$E66,'Base de Datos'!$U:$U,$F66,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L66" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C66,'Base de Datos'!$G:$G,$D66,'Base de Datos'!$H:$H,$E66,'Base de Datos'!$U:$U,$F66,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -48226,7 +48319,7 @@
       </c>
       <c r="H67" s="29" cm="1">
         <f t="array" ref="H67">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C67))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D67))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E67))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F67))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I67" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C67,'Base de Datos'!$G:$G,$D67,'Base de Datos'!$H:$H,$E67,'Base de Datos'!$U:$U,$F67,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -48238,7 +48331,7 @@
       </c>
       <c r="K67" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C67,'Base de Datos'!$G:$G,$D67,'Base de Datos'!$H:$H,$E67,'Base de Datos'!$U:$U,$F67,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L67" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C67,'Base de Datos'!$G:$G,$D67,'Base de Datos'!$H:$H,$E67,'Base de Datos'!$U:$U,$F67,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -48300,7 +48393,7 @@
       </c>
       <c r="H68" s="29" cm="1">
         <f t="array" ref="H68">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C68))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D68))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E68))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F68))&amp;""))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I68" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C68,'Base de Datos'!$G:$G,$D68,'Base de Datos'!$H:$H,$E68,'Base de Datos'!$U:$U,$F68,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -48312,7 +48405,7 @@
       </c>
       <c r="K68" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C68,'Base de Datos'!$G:$G,$D68,'Base de Datos'!$H:$H,$E68,'Base de Datos'!$U:$U,$F68,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L68" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C68,'Base de Datos'!$G:$G,$D68,'Base de Datos'!$H:$H,$E68,'Base de Datos'!$U:$U,$F68,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -48374,7 +48467,7 @@
       </c>
       <c r="H69" s="29" cm="1">
         <f t="array" ref="H69">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C69))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D69))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E69))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F69))&amp;""))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I69" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C69,'Base de Datos'!$G:$G,$D69,'Base de Datos'!$H:$H,$E69,'Base de Datos'!$U:$U,$F69,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -48386,7 +48479,7 @@
       </c>
       <c r="K69" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C69,'Base de Datos'!$G:$G,$D69,'Base de Datos'!$H:$H,$E69,'Base de Datos'!$U:$U,$F69,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L69" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C69,'Base de Datos'!$G:$G,$D69,'Base de Datos'!$H:$H,$E69,'Base de Datos'!$U:$U,$F69,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>
@@ -48448,7 +48541,7 @@
       </c>
       <c r="H70" s="29" cm="1">
         <f t="array" ref="H70">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C70))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D70))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E70))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F70))&amp;""))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I70" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C70,'Base de Datos'!$G:$G,$D70,'Base de Datos'!$H:$H,$E70,'Base de Datos'!$U:$U,$F70,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -48460,7 +48553,7 @@
       </c>
       <c r="K70" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C70,'Base de Datos'!$G:$G,$D70,'Base de Datos'!$H:$H,$E70,'Base de Datos'!$U:$U,$F70,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L70" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C70,'Base de Datos'!$G:$G,$D70,'Base de Datos'!$H:$H,$E70,'Base de Datos'!$U:$U,$F70,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>

--- a/TABLERO_PA_C.xlsx
+++ b/TABLERO_PA_C.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e2a95cfba4fb0187/Escritorio/Tableros de Control/2. Contraloría/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="468" documentId="13_ncr:1_{5037B3AD-B0A2-4521-8F49-D3B2F1605E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{006F8367-AF81-496C-A145-A8AEAF4ECE89}"/>
+  <xr:revisionPtr revIDLastSave="479" documentId="13_ncr:1_{5037B3AD-B0A2-4521-8F49-D3B2F1605E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FE71772-2C62-4A59-A5D9-553FC6ECAD8A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="10" xr2:uid="{E38B2051-8614-49B4-943E-B3707D980583}"/>
   </bookViews>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2577" uniqueCount="828">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2577" uniqueCount="823">
   <si>
     <t>No.</t>
   </si>
@@ -2717,12 +2717,6 @@
 DIRECCIÓN DE GESTIÓN FINANCIERA</t>
   </si>
   <si>
-    <t>SUBGERENCIA DE SERVICIOS PERACIONALES E INFRAESTRUCTURA</t>
-  </si>
-  <si>
-    <t>DIRECCIÓN DE SERVICIO AL TRANSPORTADOR DIRECCIÓN DE RECURSOST ECNOLÓGICOS</t>
-  </si>
-  <si>
     <t>SUBGERENCIA CORPORATIVA</t>
   </si>
   <si>
@@ -2730,23 +2724,13 @@
   </si>
   <si>
     <t>SUBGERENCIA DE SERVICIOS OPERACIONALES E INFRAESTRUCTURA</t>
-  </si>
-  <si>
-    <t>DIRECCIÓN DE RECURSOS TECNOLÓGICOS
-DIRECCIÓNDEGESTIÓNFINANCIERA</t>
   </si>
   <si>
     <t>SUBGERENCIA CORPORATIVA 
 DIRECCIÓN DE RECURSOS TECNOLÓGICOS</t>
   </si>
   <si>
-    <t>DIRECCIÓN DE SERVICIO ALTRANSPORTADOR</t>
-  </si>
-  <si>
     <t>DIRECCIÓN DE SERVICIO AL TRANSPORTADOR</t>
-  </si>
-  <si>
-    <t>DIRECCIÓN DE RECURSOS FÍSICOS</t>
   </si>
   <si>
     <t>DIRECCIÓN DE SEGURIDAD OPERACIONAL</t>
@@ -2764,21 +2748,22 @@
 DIRECCIÓN DE RECURSOS TECNOLÓGICOS</t>
   </si>
   <si>
+    <t>SUB GERENCIA DE SERVICIOS OPERACIONALES E INFRAESTRUCTURA</t>
+  </si>
+  <si>
+    <t>SUBGERENCIA DE PLANEACIÓN Y PROYECTOS DIRECCIÓN DE GESTIÓN HUMANA</t>
+  </si>
+  <si>
+    <t>DIRECCIÓN DE SERVICIO AL TRANSPORTADOR DIRECCIÓN DE RECURSOS TECNOLÓGICOS</t>
+  </si>
+  <si>
+    <t>DIRECCIÓN DE RECURSOS TECNOLÓGICOS
+DIRECCIÓN DE GESTIÓN FINANCIERA</t>
+  </si>
+  <si>
     <t>OFICINA DE AUDITORÍA INTERNA 
 SUBGERENCIA JURÍDICA 
-DIRECCIÓNFINANCIERA</t>
-  </si>
-  <si>
-    <t>SUBGERENCIA PLANEACIÓN Y PROYECTOS</t>
-  </si>
-  <si>
-    <t>SUB GERENCIA DE SERVICIOS OPERACIONALES E INFRAESTRUCTURA</t>
-  </si>
-  <si>
-    <t>SUBGERENCIA DE PLANEACIÓN Y PROYECTOS DIRECCIÓN DE GESTIÓN HUMANA</t>
-  </si>
-  <si>
-    <t>SUBGERENCIAJ URÍDICA</t>
+DIRECCIÓN DE GESTIÓN FINANCIERA</t>
   </si>
 </sst>
 </file>
@@ -5469,21 +5454,6 @@
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="3" tint="0.499984740745262"/>
@@ -5590,6 +5560,21 @@
     </dxf>
     <dxf>
       <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
@@ -20587,129 +20572,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B6C7AB91-8822-4E2E-BE9B-A9578BEEAA20}" name="TablaDinámica3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:G7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="19">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-    <i i="2">
-      <x v="2"/>
-    </i>
-    <i i="3">
-      <x v="3"/>
-    </i>
-    <i i="4">
-      <x v="4"/>
-    </i>
-    <i i="5">
-      <x v="5"/>
-    </i>
-  </colItems>
-  <dataFields count="6">
-    <dataField name="Cuenta de No. Hallazgo" fld="2" subtotal="count" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Total Planes de acción" fld="5" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Abiertos" fld="6" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Vencidos" fld="7" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Finalizados" fld="8" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Auditoría" fld="1" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="5">
-    <format dxfId="240">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="239">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="238">
-      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0"/>
-    </format>
-    <format dxfId="237">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="236">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="4">
-            <x v="0"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5E7F1577-F431-4B0C-B786-3FF0F4829E0F}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A9:E35" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
@@ -20903,6 +20765,255 @@
     <dataField name="Suma de Finalizados" fld="8" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="20">
+    <format dxfId="255">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="254">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="253">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0"/>
+    </format>
+    <format dxfId="252">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="251">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="250">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="249">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="248">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="247">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="14"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="246">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="19"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="245">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="20"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="244">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="23"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="243">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="25"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="242">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="42"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="241">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="43"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="240">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="44"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="239">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="46"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="238">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="47"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="237">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="50"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="236">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="12"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B6C7AB91-8822-4E2E-BE9B-A9578BEEAA20}" name="TablaDinámica3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:G7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="19">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+    <i i="3">
+      <x v="3"/>
+    </i>
+    <i i="4">
+      <x v="4"/>
+    </i>
+    <i i="5">
+      <x v="5"/>
+    </i>
+  </colItems>
+  <dataFields count="6">
+    <dataField name="Cuenta de No. Hallazgo" fld="2" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Total Planes de acción" fld="5" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Abiertos" fld="6" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Vencidos" fld="7" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Finalizados" fld="8" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Auditoría" fld="1" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="5">
     <format dxfId="260">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
@@ -20916,139 +21027,13 @@
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
     <format dxfId="256">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="3" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="255">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="254">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="253">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="252">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="14"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="251">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="19"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="250">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="20"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="249">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="23"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="248">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="25"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="247">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="42"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="246">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="43"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="245">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="44"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="244">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="46"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="243">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="47"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="242">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="50"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="241">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="12"/>
+          <reference field="4294967294" count="4">
+            <x v="0"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
           </reference>
         </references>
       </pivotArea>
@@ -27873,6 +27858,255 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A9C7B425-127F-4B5F-B2E3-C2AB4F050E7C}" name="TablaDinámica3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A12:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="19">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Suma de Total Planes de acción" fld="5" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="1">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="0">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{53017CE7-FCFE-4C73-9C32-3A18A27FC23C}" name="TablaDinámica7" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+  <location ref="F13:G16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="19">
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="54">
+        <item m="1" x="25"/>
+        <item m="1" x="26"/>
+        <item m="1" x="31"/>
+        <item m="1" x="28"/>
+        <item m="1" x="36"/>
+        <item m="1" x="42"/>
+        <item m="1" x="27"/>
+        <item m="1" x="29"/>
+        <item m="1" x="38"/>
+        <item m="1" x="43"/>
+        <item m="1" x="41"/>
+        <item m="1" x="34"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="11"/>
+        <item x="16"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="12"/>
+        <item x="17"/>
+        <item x="15"/>
+        <item x="9"/>
+        <item m="1" x="48"/>
+        <item x="21"/>
+        <item m="1" x="46"/>
+        <item m="1" x="52"/>
+        <item m="1" x="49"/>
+        <item m="1" x="50"/>
+        <item m="1" x="35"/>
+        <item m="1" x="32"/>
+        <item m="1" x="47"/>
+        <item m="1" x="39"/>
+        <item m="1" x="40"/>
+        <item m="1" x="45"/>
+        <item m="1" x="51"/>
+        <item m="1" x="37"/>
+        <item m="1" x="33"/>
+        <item m="1" x="30"/>
+        <item m="1" x="44"/>
+        <item x="10"/>
+        <item x="7"/>
+        <item x="13"/>
+        <item x="20"/>
+        <item x="14"/>
+        <item x="24"/>
+        <item x="19"/>
+        <item x="8"/>
+        <item x="5"/>
+        <item x="18"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="-2"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="3">
+    <dataField name="Suma de Abiertos" fld="6" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Vencidos" fld="7" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Finalizados" fld="8" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="5">
+    <chartFormat chart="4" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DD0BBB6E-FA08-4903-950F-5C10965A7D8D}" name="TablaDinámica6" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A26:B31" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
@@ -27997,10 +28231,10 @@
     <dataField name="Suma de Finalizados" fld="8" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="1">
+    <format dxfId="3">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="0">
+    <format dxfId="2">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
   </formats>
@@ -28016,7 +28250,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3B3AE9AA-616F-416E-8D70-C9530CA01C24}" name="TablaDinámica4" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A19:B23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
@@ -28067,262 +28301,13 @@
     <dataField name="Suma de Alerta 30" fld="11" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="3">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="2">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A9C7B425-127F-4B5F-B2E3-C2AB4F050E7C}" name="TablaDinámica3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A12:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="19">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Suma de Total Planes de acción" fld="5" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="2">
     <format dxfId="5">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
     <format dxfId="4">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
   </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{53017CE7-FCFE-4C73-9C32-3A18A27FC23C}" name="TablaDinámica7" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
-  <location ref="F13:G16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="19">
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="54">
-        <item m="1" x="25"/>
-        <item m="1" x="26"/>
-        <item m="1" x="31"/>
-        <item m="1" x="28"/>
-        <item m="1" x="36"/>
-        <item m="1" x="42"/>
-        <item m="1" x="27"/>
-        <item m="1" x="29"/>
-        <item m="1" x="38"/>
-        <item m="1" x="43"/>
-        <item m="1" x="41"/>
-        <item m="1" x="34"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item x="11"/>
-        <item x="16"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="12"/>
-        <item x="17"/>
-        <item x="15"/>
-        <item x="9"/>
-        <item m="1" x="48"/>
-        <item x="21"/>
-        <item m="1" x="46"/>
-        <item m="1" x="52"/>
-        <item m="1" x="49"/>
-        <item m="1" x="50"/>
-        <item m="1" x="35"/>
-        <item m="1" x="32"/>
-        <item m="1" x="47"/>
-        <item m="1" x="39"/>
-        <item m="1" x="40"/>
-        <item m="1" x="45"/>
-        <item m="1" x="51"/>
-        <item m="1" x="37"/>
-        <item m="1" x="33"/>
-        <item m="1" x="30"/>
-        <item m="1" x="44"/>
-        <item x="10"/>
-        <item x="7"/>
-        <item x="13"/>
-        <item x="20"/>
-        <item x="14"/>
-        <item x="24"/>
-        <item x="19"/>
-        <item x="8"/>
-        <item x="5"/>
-        <item x="18"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="-2"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-    <i i="2">
-      <x v="2"/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="3">
-    <dataField name="Suma de Abiertos" fld="6" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Vencidos" fld="7" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Finalizados" fld="8" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="5">
-    <chartFormat chart="4" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="3">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="4">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="5">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -28589,7 +28574,21 @@
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CEA19F0D-D53E-4776-BB60-8DAF8AF7C40F}" name="Tabla2" displayName="Tabla2" ref="A1:AJ85" totalsRowShown="0" headerRowDxfId="299" dataDxfId="298" tableBorderDxfId="297">
-  <autoFilter ref="A1:AJ85" xr:uid="{CEA19F0D-D53E-4776-BB60-8DAF8AF7C40F}"/>
+  <autoFilter ref="A1:AJ85" xr:uid="{CEA19F0D-D53E-4776-BB60-8DAF8AF7C40F}">
+    <filterColumn colId="20">
+      <filters>
+        <filter val="DIRECCIÓN DE RECURSOS FÍSICOS"/>
+        <filter val="DIRECCIÓN DE RECURSOS TECNOLÓGICOS_x000a_DIRECCIÓNDEGESTIÓNFINANCIERA"/>
+        <filter val="DIRECCIÓN DE SERVICIO AL TRANSPORTADOR DIRECCIÓN DE RECURSOST ECNOLÓGICOS"/>
+        <filter val="DIRECCIÓN DE SERVICIO ALTRANSPORTADOR"/>
+        <filter val="DIRECCIÓNDEGESTIÓNFINANCIERA"/>
+        <filter val="OFICINA DE AUDITORÍA INTERNA _x000a_SUBGERENCIA JURÍDICA _x000a_DIRECCIÓNFINANCIERA"/>
+        <filter val="SUBGERENCIA DE SERVICIOS PERACIONALES E INFRAESTRUCTURA"/>
+        <filter val="SUBGERENCIA PLANEACIÓN Y PROYECTOS"/>
+        <filter val="SUBGERENCIAJ URÍDICA"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="36">
     <tableColumn id="1" xr3:uid="{7A8D3A5E-E004-426E-B403-310EC9C105F1}" name="No." dataDxfId="296"/>
     <tableColumn id="2" xr3:uid="{657020D6-E9B2-4900-BBA6-15C5F0ADC46D}" name="FECHA REPORTE DE LA INFORMACIÓN" dataDxfId="295"/>
@@ -29261,7 +29260,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="2" spans="1:36" ht="79.8">
+    <row r="2" spans="1:36" ht="79.8" hidden="1">
       <c r="A2" s="59">
         <v>117</v>
       </c>
@@ -29366,7 +29365,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="3" spans="1:36" ht="125.4">
+    <row r="3" spans="1:36" ht="125.4" hidden="1">
       <c r="A3" s="59">
         <v>118</v>
       </c>
@@ -29475,7 +29474,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="4" spans="1:36" ht="125.4">
+    <row r="4" spans="1:36" ht="125.4" hidden="1">
       <c r="A4" s="59">
         <v>123</v>
       </c>
@@ -29584,7 +29583,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:36" ht="125.4">
+    <row r="5" spans="1:36" ht="125.4" hidden="1">
       <c r="A5" s="59">
         <v>124</v>
       </c>
@@ -29691,7 +29690,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:36" ht="136.80000000000001">
+    <row r="6" spans="1:36" ht="136.80000000000001" hidden="1">
       <c r="A6" s="59">
         <v>189</v>
       </c>
@@ -29800,7 +29799,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="7" spans="1:36" ht="136.80000000000001">
+    <row r="7" spans="1:36" ht="136.80000000000001" hidden="1">
       <c r="A7" s="59">
         <v>190</v>
       </c>
@@ -29909,7 +29908,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="8" spans="1:36" ht="136.80000000000001">
+    <row r="8" spans="1:36" ht="136.80000000000001" hidden="1">
       <c r="A8" s="59">
         <v>191</v>
       </c>
@@ -30018,7 +30017,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="9" spans="1:36" ht="136.80000000000001">
+    <row r="9" spans="1:36" ht="136.80000000000001" hidden="1">
       <c r="A9" s="141">
         <v>193</v>
       </c>
@@ -30127,7 +30126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:36" ht="171">
+    <row r="10" spans="1:36" ht="171" hidden="1">
       <c r="A10" s="59">
         <v>196</v>
       </c>
@@ -30236,7 +30235,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="11" spans="1:36" ht="171">
+    <row r="11" spans="1:36" ht="171" hidden="1">
       <c r="A11" s="59">
         <v>197</v>
       </c>
@@ -30341,7 +30340,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="12" spans="1:36" ht="171">
+    <row r="12" spans="1:36" ht="171" hidden="1">
       <c r="A12" s="59">
         <v>198</v>
       </c>
@@ -30446,7 +30445,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="13" spans="1:36" ht="91.2">
+    <row r="13" spans="1:36" ht="91.2" hidden="1">
       <c r="A13" s="59">
         <v>199</v>
       </c>
@@ -30555,7 +30554,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="14" spans="1:36" ht="125.4">
+    <row r="14" spans="1:36" ht="125.4" hidden="1">
       <c r="A14" s="59">
         <v>200</v>
       </c>
@@ -30720,7 +30719,7 @@
         <v>100</v>
       </c>
       <c r="U15" s="60" t="s">
-        <v>659</v>
+        <v>807</v>
       </c>
       <c r="V15" s="137" t="s">
         <v>38</v>
@@ -30773,7 +30772,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:36" ht="159.6">
+    <row r="16" spans="1:36" ht="159.6" hidden="1">
       <c r="A16" s="59">
         <v>214</v>
       </c>
@@ -30878,7 +30877,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="17" spans="1:36" ht="182.4">
+    <row r="17" spans="1:36" ht="182.4" hidden="1">
       <c r="A17" s="59">
         <v>215</v>
       </c>
@@ -30987,7 +30986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:36" ht="68.400000000000006">
+    <row r="18" spans="1:36" ht="68.400000000000006" hidden="1">
       <c r="A18" s="59">
         <v>221</v>
       </c>
@@ -31096,7 +31095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:36" ht="114">
+    <row r="19" spans="1:36" ht="114" hidden="1">
       <c r="A19" s="59">
         <v>222</v>
       </c>
@@ -31205,7 +31204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:36" ht="114">
+    <row r="20" spans="1:36" ht="114" hidden="1">
       <c r="A20" s="59">
         <v>223</v>
       </c>
@@ -31314,7 +31313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:36" ht="91.2">
+    <row r="21" spans="1:36" ht="91.2" hidden="1">
       <c r="A21" s="141">
         <v>230</v>
       </c>
@@ -31419,7 +31418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:36" ht="91.2">
+    <row r="22" spans="1:36" ht="91.2" hidden="1">
       <c r="A22" s="141">
         <v>232</v>
       </c>
@@ -31524,7 +31523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:36" ht="91.2">
+    <row r="23" spans="1:36" ht="91.2" hidden="1">
       <c r="A23" s="141">
         <v>233</v>
       </c>
@@ -31685,7 +31684,7 @@
         <v>100</v>
       </c>
       <c r="U24" s="75" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="V24" s="142" t="s">
         <v>38</v>
@@ -31794,7 +31793,7 @@
         <v>100</v>
       </c>
       <c r="U25" s="60" t="s">
-        <v>810</v>
+        <v>820</v>
       </c>
       <c r="V25" s="137" t="s">
         <v>38</v>
@@ -31847,7 +31846,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="26" spans="1:36" ht="136.80000000000001">
+    <row r="26" spans="1:36" ht="136.80000000000001" hidden="1">
       <c r="A26" s="59">
         <v>246</v>
       </c>
@@ -31903,7 +31902,7 @@
         <v>100</v>
       </c>
       <c r="U26" s="60" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="V26" s="137" t="s">
         <v>38</v>
@@ -31952,7 +31951,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="27" spans="1:36" ht="193.8">
+    <row r="27" spans="1:36" ht="193.8" hidden="1">
       <c r="A27" s="59">
         <v>247</v>
       </c>
@@ -32008,7 +32007,7 @@
         <v>100</v>
       </c>
       <c r="U27" s="60" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="V27" s="137" t="s">
         <v>38</v>
@@ -32057,7 +32056,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="28" spans="1:36" ht="91.2">
+    <row r="28" spans="1:36" ht="91.2" hidden="1">
       <c r="A28" s="59">
         <v>255</v>
       </c>
@@ -32113,7 +32112,7 @@
         <v>100</v>
       </c>
       <c r="U28" s="60" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="V28" s="137" t="s">
         <v>38</v>
@@ -32162,7 +32161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:36" ht="102.6">
+    <row r="29" spans="1:36" ht="102.6" hidden="1">
       <c r="A29" s="59">
         <v>256</v>
       </c>
@@ -32267,7 +32266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:36" ht="91.2">
+    <row r="30" spans="1:36" ht="91.2" hidden="1">
       <c r="A30" s="151">
         <v>259</v>
       </c>
@@ -32323,7 +32322,7 @@
         <v>100</v>
       </c>
       <c r="U30" s="152" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="V30" s="153" t="s">
         <v>38</v>
@@ -32376,7 +32375,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="31" spans="1:36" ht="91.2">
+    <row r="31" spans="1:36" ht="91.2" hidden="1">
       <c r="A31" s="141">
         <v>260</v>
       </c>
@@ -32485,7 +32484,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="32" spans="1:36" ht="136.80000000000001">
+    <row r="32" spans="1:36" ht="136.80000000000001" hidden="1">
       <c r="A32" s="141">
         <v>261</v>
       </c>
@@ -32590,7 +32589,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="33" spans="1:36" ht="136.80000000000001">
+    <row r="33" spans="1:36" ht="136.80000000000001" hidden="1">
       <c r="A33" s="141">
         <v>262</v>
       </c>
@@ -32699,7 +32698,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="34" spans="1:36" ht="136.80000000000001">
+    <row r="34" spans="1:36" ht="136.80000000000001" hidden="1">
       <c r="A34" s="59">
         <v>263</v>
       </c>
@@ -32806,7 +32805,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="35" spans="1:36" ht="148.19999999999999">
+    <row r="35" spans="1:36" ht="148.19999999999999" hidden="1">
       <c r="A35" s="59">
         <v>281</v>
       </c>
@@ -32862,7 +32861,7 @@
         <v>100</v>
       </c>
       <c r="U35" s="60" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="V35" s="137" t="s">
         <v>38</v>
@@ -32915,7 +32914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:36" ht="136.80000000000001">
+    <row r="36" spans="1:36" ht="136.80000000000001" hidden="1">
       <c r="A36" s="59">
         <v>181</v>
       </c>
@@ -33080,7 +33079,7 @@
         <v>100</v>
       </c>
       <c r="U37" s="60" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="V37" s="137" t="s">
         <v>244</v>
@@ -33131,7 +33130,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="38" spans="1:36" ht="125.4">
+    <row r="38" spans="1:36" ht="125.4" hidden="1">
       <c r="A38" s="59">
         <v>183</v>
       </c>
@@ -33187,7 +33186,7 @@
         <v>100</v>
       </c>
       <c r="U38" s="60" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="V38" s="137" t="s">
         <v>244</v>
@@ -33238,7 +33237,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="39" spans="1:36" ht="148.19999999999999">
+    <row r="39" spans="1:36" ht="148.19999999999999" hidden="1">
       <c r="A39" s="161">
         <v>189</v>
       </c>
@@ -33294,7 +33293,7 @@
         <v>100</v>
       </c>
       <c r="U39" s="75" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="V39" s="142" t="s">
         <v>244</v>
@@ -33345,7 +33344,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="40" spans="1:36" ht="159.6">
+    <row r="40" spans="1:36" ht="159.6" hidden="1">
       <c r="A40" s="59">
         <v>190</v>
       </c>
@@ -33452,7 +33451,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="41" spans="1:36" ht="102.6">
+    <row r="41" spans="1:36" ht="102.6" hidden="1">
       <c r="A41" s="78">
         <v>191</v>
       </c>
@@ -33561,7 +33560,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="42" spans="1:36" ht="125.4">
+    <row r="42" spans="1:36" ht="125.4" hidden="1">
       <c r="A42" s="59">
         <v>194</v>
       </c>
@@ -33670,7 +33669,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="43" spans="1:36" ht="148.19999999999999">
+    <row r="43" spans="1:36" ht="148.19999999999999" hidden="1">
       <c r="A43" s="161">
         <v>195</v>
       </c>
@@ -33726,7 +33725,7 @@
         <v>100</v>
       </c>
       <c r="U43" s="75" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="V43" s="142" t="s">
         <v>244</v>
@@ -33833,7 +33832,7 @@
         <v>100</v>
       </c>
       <c r="U44" s="60" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="V44" s="137" t="s">
         <v>244</v>
@@ -33884,7 +33883,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="45" spans="1:36" ht="125.4">
+    <row r="45" spans="1:36" ht="125.4" hidden="1">
       <c r="A45" s="83">
         <v>215</v>
       </c>
@@ -33940,7 +33939,7 @@
         <v>100</v>
       </c>
       <c r="U45" s="84" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="V45" s="139" t="s">
         <v>244</v>
@@ -33991,7 +33990,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="46" spans="1:36" ht="102.6">
+    <row r="46" spans="1:36" ht="102.6" hidden="1">
       <c r="A46" s="78">
         <v>216</v>
       </c>
@@ -34098,7 +34097,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="47" spans="1:36" ht="182.4">
+    <row r="47" spans="1:36" ht="182.4" hidden="1">
       <c r="A47" s="78">
         <v>217</v>
       </c>
@@ -34205,7 +34204,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="48" spans="1:36" ht="131.4" customHeight="1">
+    <row r="48" spans="1:36" ht="131.4" hidden="1" customHeight="1">
       <c r="A48" s="78">
         <v>218</v>
       </c>
@@ -34370,7 +34369,7 @@
         <v>100</v>
       </c>
       <c r="U49" s="60" t="s">
-        <v>818</v>
+        <v>802</v>
       </c>
       <c r="V49" s="137" t="s">
         <v>244</v>
@@ -34477,7 +34476,7 @@
         <v>100</v>
       </c>
       <c r="U50" s="60" t="s">
-        <v>818</v>
+        <v>802</v>
       </c>
       <c r="V50" s="137" t="s">
         <v>244</v>
@@ -34528,7 +34527,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="51" spans="1:36" ht="171">
+    <row r="51" spans="1:36" ht="171" hidden="1">
       <c r="A51" s="59">
         <v>223</v>
       </c>
@@ -34584,7 +34583,7 @@
         <v>100</v>
       </c>
       <c r="U51" s="60" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="V51" s="137" t="s">
         <v>244</v>
@@ -34635,7 +34634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:36" ht="125.4">
+    <row r="52" spans="1:36" ht="125.4" hidden="1">
       <c r="A52" s="59">
         <v>226</v>
       </c>
@@ -34742,7 +34741,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="53" spans="1:36" ht="125.4">
+    <row r="53" spans="1:36" ht="125.4" hidden="1">
       <c r="A53" s="59">
         <v>227</v>
       </c>
@@ -34849,7 +34848,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="54" spans="1:36" ht="193.8">
+    <row r="54" spans="1:36" ht="193.8" hidden="1">
       <c r="A54" s="59">
         <v>228</v>
       </c>
@@ -34956,7 +34955,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="55" spans="1:36" ht="125.4">
+    <row r="55" spans="1:36" ht="125.4" hidden="1">
       <c r="A55" s="78">
         <v>229</v>
       </c>
@@ -35063,7 +35062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:36" ht="136.80000000000001">
+    <row r="56" spans="1:36" ht="136.80000000000001" hidden="1">
       <c r="A56" s="78">
         <v>230</v>
       </c>
@@ -35170,7 +35169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:36" ht="114">
+    <row r="57" spans="1:36" ht="114" hidden="1">
       <c r="A57" s="59">
         <v>231</v>
       </c>
@@ -35226,7 +35225,7 @@
         <v>100</v>
       </c>
       <c r="U57" s="60" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="V57" s="137" t="s">
         <v>244</v>
@@ -35277,7 +35276,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:36" ht="171">
+    <row r="58" spans="1:36" ht="171" hidden="1">
       <c r="A58" s="78">
         <v>240</v>
       </c>
@@ -35384,7 +35383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:36" ht="205.2">
+    <row r="59" spans="1:36" ht="205.2" hidden="1">
       <c r="A59" s="59">
         <v>245</v>
       </c>
@@ -35491,7 +35490,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="60" spans="1:36" ht="68.400000000000006">
+    <row r="60" spans="1:36" ht="68.400000000000006" hidden="1">
       <c r="A60" s="78">
         <v>246</v>
       </c>
@@ -35598,7 +35597,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="61" spans="1:36" ht="148.19999999999999">
+    <row r="61" spans="1:36" ht="148.19999999999999" hidden="1">
       <c r="A61" s="78">
         <v>247</v>
       </c>
@@ -35654,7 +35653,7 @@
         <v>100</v>
       </c>
       <c r="U61" s="60" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
       <c r="V61" s="137" t="s">
         <v>244</v>
@@ -35705,7 +35704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:36" ht="228">
+    <row r="62" spans="1:36" ht="228" hidden="1">
       <c r="A62" s="59">
         <v>120</v>
       </c>
@@ -35816,7 +35815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:36" ht="262.2">
+    <row r="63" spans="1:36" ht="262.2" hidden="1">
       <c r="A63" s="78">
         <v>123</v>
       </c>
@@ -35876,7 +35875,7 @@
         <v>100</v>
       </c>
       <c r="U63" s="60" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="V63" s="60" t="s">
         <v>455</v>
@@ -35987,7 +35986,7 @@
         <v>100</v>
       </c>
       <c r="U64" s="60" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="V64" s="60" t="s">
         <v>455</v>
@@ -36038,7 +36037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:36" ht="171">
+    <row r="65" spans="1:36" ht="171" hidden="1">
       <c r="A65" s="59">
         <v>184</v>
       </c>
@@ -36151,7 +36150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:36" ht="205.2">
+    <row r="66" spans="1:36" ht="205.2" hidden="1">
       <c r="A66" s="59">
         <v>186</v>
       </c>
@@ -36264,7 +36263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:36" ht="171">
+    <row r="67" spans="1:36" ht="171" hidden="1">
       <c r="A67" s="59">
         <v>187</v>
       </c>
@@ -36377,7 +36376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:36" ht="171">
+    <row r="68" spans="1:36" ht="171" hidden="1">
       <c r="A68" s="59">
         <v>188</v>
       </c>
@@ -36550,7 +36549,7 @@
         <v>100</v>
       </c>
       <c r="U69" s="60" t="s">
-        <v>824</v>
+        <v>270</v>
       </c>
       <c r="V69" s="60" t="s">
         <v>500</v>
@@ -36601,7 +36600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:36" ht="228">
+    <row r="70" spans="1:36" ht="228" hidden="1">
       <c r="A70" s="59">
         <v>221</v>
       </c>
@@ -36661,7 +36660,7 @@
         <v>100</v>
       </c>
       <c r="U70" s="60" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
       <c r="V70" s="60" t="s">
         <v>500</v>
@@ -36712,7 +36711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:36" ht="239.4">
+    <row r="71" spans="1:36" ht="239.4" hidden="1">
       <c r="A71" s="59">
         <v>222</v>
       </c>
@@ -36772,7 +36771,7 @@
         <v>100</v>
       </c>
       <c r="U71" s="60" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
       <c r="V71" s="60" t="s">
         <v>500</v>
@@ -36823,7 +36822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:36" ht="228">
+    <row r="72" spans="1:36" ht="228" hidden="1">
       <c r="A72" s="78">
         <v>224</v>
       </c>
@@ -36883,7 +36882,7 @@
         <v>100</v>
       </c>
       <c r="U72" s="60" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
       <c r="V72" s="60" t="s">
         <v>500</v>
@@ -36934,7 +36933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:36" ht="239.4">
+    <row r="73" spans="1:36" ht="239.4" hidden="1">
       <c r="A73" s="59">
         <v>225</v>
       </c>
@@ -37047,7 +37046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:36" ht="193.8">
+    <row r="74" spans="1:36" ht="193.8" hidden="1">
       <c r="A74" s="59">
         <v>232</v>
       </c>
@@ -37160,7 +37159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:36" ht="182.4">
+    <row r="75" spans="1:36" ht="182.4" hidden="1">
       <c r="A75" s="59">
         <v>233</v>
       </c>
@@ -37220,7 +37219,7 @@
         <v>100</v>
       </c>
       <c r="U75" s="60" t="s">
-        <v>826</v>
+        <v>819</v>
       </c>
       <c r="V75" s="60" t="s">
         <v>500</v>
@@ -37271,7 +37270,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="76" spans="1:36" ht="262.2">
+    <row r="76" spans="1:36" ht="262.2" hidden="1">
       <c r="A76" s="59">
         <v>234</v>
       </c>
@@ -37331,7 +37330,7 @@
         <v>100</v>
       </c>
       <c r="U76" s="60" t="s">
-        <v>826</v>
+        <v>819</v>
       </c>
       <c r="V76" s="60" t="s">
         <v>500</v>
@@ -37382,7 +37381,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="77" spans="1:36" ht="205.2">
+    <row r="77" spans="1:36" ht="205.2" hidden="1">
       <c r="A77" s="59">
         <v>235</v>
       </c>
@@ -37495,7 +37494,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="78" spans="1:36" ht="262.2">
+    <row r="78" spans="1:36" ht="262.2" hidden="1">
       <c r="A78" s="59">
         <v>236</v>
       </c>
@@ -37608,7 +37607,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="79" spans="1:36" ht="159.6">
+    <row r="79" spans="1:36" ht="159.6" hidden="1">
       <c r="A79" s="59">
         <v>237</v>
       </c>
@@ -37781,7 +37780,7 @@
         <v>100</v>
       </c>
       <c r="U80" s="60" t="s">
-        <v>827</v>
+        <v>805</v>
       </c>
       <c r="V80" s="60" t="s">
         <v>578</v>
@@ -37832,7 +37831,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="81" spans="1:36" ht="250.8">
+    <row r="81" spans="1:36" ht="250.8" hidden="1">
       <c r="A81" s="59">
         <v>239</v>
       </c>
@@ -37943,7 +37942,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="82" spans="1:36" ht="125.4">
+    <row r="82" spans="1:36" ht="125.4" hidden="1">
       <c r="A82" s="59">
         <v>241</v>
       </c>
@@ -38054,7 +38053,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="83" spans="1:36" ht="114">
+    <row r="83" spans="1:36" ht="114" hidden="1">
       <c r="A83" s="59">
         <v>242</v>
       </c>
@@ -38165,7 +38164,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="84" spans="1:36" ht="228">
+    <row r="84" spans="1:36" ht="228" hidden="1">
       <c r="A84" s="59">
         <v>243</v>
       </c>
@@ -38276,7 +38275,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="85" spans="1:36" ht="205.2">
+    <row r="85" spans="1:36" ht="205.2" hidden="1">
       <c r="A85" s="59">
         <v>244</v>
       </c>
@@ -44393,7 +44392,7 @@
       </c>
       <c r="H14" s="29" cm="1">
         <f t="array" ref="H14">SUMPRODUCT((TRIM(CLEAN('Base de Datos'!$F$2:$F$3000))&amp;""=TRIM(CLEAN(C14))&amp;"")*(TRIM(CLEAN('Base de Datos'!$G$2:$G$3000))&amp;""=TRIM(CLEAN(D14))&amp;"")*(TRIM(CLEAN('Base de Datos'!$H$2:$H$3000))&amp;""=TRIM(CLEAN(E14))&amp;"")*(TRIM(CLEAN('Base de Datos'!$U$2:$U$3000))&amp;""=TRIM(CLEAN(F14))&amp;""))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C14,'Base de Datos'!$G:$G,$D14,'Base de Datos'!$H:$H,$E14,'Base de Datos'!$U:$U,$F14,'Base de Datos'!$AA:$AA,"Abierta")</f>
@@ -44405,7 +44404,7 @@
       </c>
       <c r="K14" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C14,'Base de Datos'!$G:$G,$D14,'Base de Datos'!$H:$H,$E14,'Base de Datos'!$U:$U,$F14,'Base de Datos'!$AA:$AA,"Finalizada")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" s="29">
         <f>COUNTIFS('Base de Datos'!$F:$F,$C14,'Base de Datos'!$G:$G,$D14,'Base de Datos'!$H:$H,$E14,'Base de Datos'!$U:$U,$F14,'Base de Datos'!$AA:$AA,"Abierta",'Base de Datos'!$AC:$AC,"&lt;=10",'Base de Datos'!$AC:$AC,"&gt;0")</f>

--- a/TABLERO_PA_C.xlsx
+++ b/TABLERO_PA_C.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e2a95cfba4fb0187/Escritorio/Tableros de Control/2. Contraloría/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="479" documentId="13_ncr:1_{5037B3AD-B0A2-4521-8F49-D3B2F1605E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FE71772-2C62-4A59-A5D9-553FC6ECAD8A}"/>
+  <xr:revisionPtr revIDLastSave="496" documentId="13_ncr:1_{5037B3AD-B0A2-4521-8F49-D3B2F1605E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D9A7BB0-831B-468B-958E-712AFA3F124F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="10" xr2:uid="{E38B2051-8614-49B4-943E-B3707D980583}"/>
   </bookViews>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2577" uniqueCount="823">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2577" uniqueCount="824">
   <si>
     <t>No.</t>
   </si>
@@ -2688,81 +2688,85 @@
     <t>Se verifica la efectividad de la acción mediante la Resolución No. 0090 del 25/03/2026 de la Secretaría de Hacienda de Soacha (saneamiento de intereses moratorios) y el Recibo de Impuesto Predial No. 26982690 (Vigencias 2025-2026). Los soportes acreditan la depuración de la cartera y la actualización oficial del área del predio</t>
   </si>
   <si>
-    <t>DIRECCIÓN DE GESTIÓN FINANCIERA 
+    <t xml:space="preserve">DIRECCIÓN DE GESTIÓN FINANCIERA </t>
+  </si>
+  <si>
+    <t>DIRECCIÓN DE RECURSOS FÍSICOS Y NEGOCIOS</t>
+  </si>
+  <si>
+    <t>DIRECCIÓN DE GESTIÓN HUMANA</t>
+  </si>
+  <si>
+    <t>SUBGERENCIA JURÍDICA</t>
+  </si>
+  <si>
+    <t>DIRECCIÓN DE GESTIÓN FINANCIERA</t>
+  </si>
+  <si>
+    <t>SUBGERENCIA CORPORATIVA</t>
+  </si>
+  <si>
+    <t>DIRECCIÓN DE INFRAESTRUCTURA</t>
+  </si>
+  <si>
+    <t>SUBGERENCIA DE SERVICIOS OPERACIONALES E INFRAESTRUCTURA</t>
+  </si>
+  <si>
+    <t>DIRECCIÓN DE SERVICIO AL TRANSPORTADOR</t>
+  </si>
+  <si>
+    <t>DIRECCIÓN DE SEGURIDAD OPERACIONAL</t>
+  </si>
+  <si>
+    <t>SUB GERENCIA DE SERVICIOS OPERACIONALES E INFRAESTRUCTURA</t>
+  </si>
+  <si>
+    <t>SUBGERENCIA DE PLANEACIÓN Y PROYECTOS DIRECCIÓN DE GESTIÓN HUMANA</t>
+  </si>
+  <si>
+    <t>DIRECCIÓN DE GESTIÓN FINANCIERA/
 DIRECCIÓN DE RECURSOS FÍSICOS Y NEGOCIOS</t>
   </si>
   <si>
-    <t xml:space="preserve">DIRECCIÓN DE GESTIÓN FINANCIERA </t>
-  </si>
-  <si>
-    <t>DIRECCIÓN DE RECURSOS FÍSICOS Y NEGOCIOS</t>
-  </si>
-  <si>
-    <t>DIRECCIÓN DE GESTIÓN HUMANA</t>
-  </si>
-  <si>
-    <t>DIRECCIÓN DE RECURSOS FÍSICOS Y NEGOCIOS SUBGERENCIAJ URÍDICA</t>
-  </si>
-  <si>
-    <t>SUBGERENCIA JURÍDICA</t>
-  </si>
-  <si>
-    <t>DIRECCIÓN DE GESTIÓN FINANCIERA SUBGERENCIAJURÍDICA</t>
-  </si>
-  <si>
-    <t>DIRECCIÓN DE GESTIÓN FINANCIERA</t>
-  </si>
-  <si>
-    <t>SUBGERENCIA CORPORATIVA 
+    <t>DIRECCIÓN DE RECURSOS FÍSICOS Y NEGOCIOS/ SUBGERENCIAJ URÍDICA</t>
+  </si>
+  <si>
+    <t>DIRECCIÓN DE GESTIÓN FINANCIERA/ SUBGERENCIAJURÍDICA</t>
+  </si>
+  <si>
+    <t>SUBGERENCIA CORPORATIVA/
 DIRECCIÓN DE GESTIÓN FINANCIERA</t>
   </si>
   <si>
-    <t>SUBGERENCIA CORPORATIVA</t>
-  </si>
-  <si>
-    <t>DIRECCIÓN DE INFRAESTRUCTURA</t>
-  </si>
-  <si>
-    <t>SUBGERENCIA DE SERVICIOS OPERACIONALES E INFRAESTRUCTURA</t>
-  </si>
-  <si>
-    <t>SUBGERENCIA CORPORATIVA 
+    <t>DIRECCIÓN DE SERVICIO AL TRANSPORTADOR/ DIRECCIÓN DE RECURSOS TECNOLÓGICOS</t>
+  </si>
+  <si>
+    <t>DIRECCIÓN DE RECURSOS TECNOLÓGICOS/
+DIRECCIÓN DE GESTIÓN FINANCIERA</t>
+  </si>
+  <si>
+    <t>SUBGERENCIA CORPORATIVA/ 
 DIRECCIÓN DE RECURSOS TECNOLÓGICOS</t>
   </si>
   <si>
-    <t>DIRECCIÓN DE SERVICIO AL TRANSPORTADOR</t>
-  </si>
-  <si>
-    <t>DIRECCIÓN DE SEGURIDAD OPERACIONAL</t>
-  </si>
-  <si>
-    <t>SUBGERENCIA JURÍDICA 
+    <t>SUBGERENCIA CORPORATIVA/
+DIRECCIÓN DE RECURSOS TECNOLÓGICOS</t>
+  </si>
+  <si>
+    <t>SUBGERENCIA JURÍDICA/
 DIRECCIÓN DE GESTIÓN HUMANA</t>
   </si>
   <si>
-    <t>SUBGERENCIA DE PLANEACIÓN Y PROYECTOS DIRECCIÓN DE RECURSOS FÍSICOS Y NEGOCIOS</t>
-  </si>
-  <si>
-    <t>SUBGERENCIA CORPORATIVA 
-DIRECCIÓN DE GESTIÓN FINANCIERA 
+    <t>SUBGERENCIA DE PLANEACIÓN Y PROYECTOS/ DIRECCIÓN DE RECURSOS FÍSICOS Y NEGOCIOS</t>
+  </si>
+  <si>
+    <t>SUBGERENCIA CORPORATIVA/ 
+DIRECCIÓN DE GESTIÓN FINANCIERA/ 
 DIRECCIÓN DE RECURSOS TECNOLÓGICOS</t>
   </si>
   <si>
-    <t>SUB GERENCIA DE SERVICIOS OPERACIONALES E INFRAESTRUCTURA</t>
-  </si>
-  <si>
-    <t>SUBGERENCIA DE PLANEACIÓN Y PROYECTOS DIRECCIÓN DE GESTIÓN HUMANA</t>
-  </si>
-  <si>
-    <t>DIRECCIÓN DE SERVICIO AL TRANSPORTADOR DIRECCIÓN DE RECURSOS TECNOLÓGICOS</t>
-  </si>
-  <si>
-    <t>DIRECCIÓN DE RECURSOS TECNOLÓGICOS
-DIRECCIÓN DE GESTIÓN FINANCIERA</t>
-  </si>
-  <si>
-    <t>OFICINA DE AUDITORÍA INTERNA 
-SUBGERENCIA JURÍDICA 
+    <t>OFICINA DE AUDITORÍA INTERNA/ 
+SUBGERENCIA JURÍDICA/ 
 DIRECCIÓN DE GESTIÓN FINANCIERA</t>
   </si>
 </sst>
@@ -13949,7 +13953,7 @@
             <v>Auditoría Servicios Conexos (20250110018563)</v>
           </cell>
           <cell r="G51" t="str">
-            <v>DIRECCIÓN DE RECURSOS FÍSICOS Y NEGOCIOS
+            <v>DIRECCIÓN DE RECURSOS FÍSICOS Y NEGOCIOS/
 DIRECCIÓN DE SERVICIO AL CIUDADANO</v>
           </cell>
           <cell r="S51">
@@ -13964,9 +13968,9 @@
             <v>Auditoría Servicios Conexos (20250110018563)</v>
           </cell>
           <cell r="G52" t="str">
-            <v>DIRECCIÓN DE RECURSOS FÍSICOS Y NEGOCIOS
-DIRECCIÓN DE SERVICIO AL CIUDADANO
-SUB GERENCIA DE PLANEACIÓN Y PROYECTOS
+            <v>DIRECCIÓN DE RECURSOS FÍSICOS Y NEGOCIOS/
+DIRECCIÓN DE SERVICIO AL CIUDADANO/
+SUB GERENCIA DE PLANEACIÓN Y PROYECTOS/
 DIRECCIÓN DE GESTIÓN FINANCIERA</v>
           </cell>
           <cell r="S52"/>
@@ -14077,7 +14081,7 @@
             <v>Auditoría Servicios Conexos (20250110018563)</v>
           </cell>
           <cell r="G61" t="str">
-            <v>SUB GERENCIA CORPORATIVA
+            <v>SUB GERENCIA CORPORATIVA/
 SUB GERENCIA DE PLANEACIÓN Y PROYECTOS</v>
           </cell>
           <cell r="S61"/>
@@ -14178,7 +14182,7 @@
             <v>Auditoría al Programa de Seguridad Vial (20250110031663)</v>
           </cell>
           <cell r="G69" t="str">
-            <v>SUB GERENCIA DE SERVICIOS OPERACIONALES E INFRAESTRUCTURA
+            <v>SUB GERENCIA DE SERVICIOS OPERACIONALES E INFRAESTRUCTURA/
 DIRECCIÓN DE RECURSOS TECNOLÓGICOS</v>
           </cell>
           <cell r="S69">
@@ -14193,7 +14197,7 @@
             <v>Auditoría al Programa de Seguridad Vial (20250110031663)</v>
           </cell>
           <cell r="G70" t="str">
-            <v>SUB GERENCIA DE SERVICIOS OPERACIONALES E INFRAESTRUCTURA
+            <v>SUB GERENCIA DE SERVICIOS OPERACIONALES E INFRAESTRUCTURA/
 DIRECCIÓN DE SERVICIO AL TRANSPORTADOR</v>
           </cell>
           <cell r="S70">
@@ -14246,7 +14250,7 @@
             <v>Auditoría al Programa de Seguridad Vial (20250110031663)</v>
           </cell>
           <cell r="G74" t="str">
-            <v>SUB GERENCIA DE SERVICIOS OPERACIONALES E INFRAESTRUCTURA
+            <v>SUB GERENCIA DE SERVICIOS OPERACIONALES E INFRAESTRUCTURA/
 DIRECCIÓN DE RECURSOS TECNOLÓGICOS</v>
           </cell>
           <cell r="S74">
@@ -14487,7 +14491,7 @@
             <v>Servicio al Ciudadano (20250110042183)</v>
           </cell>
           <cell r="G93" t="str">
-            <v>DIRECCIÓN DE SERVICIO AL CIUDADANO
+            <v>DIRECCIÓN DE SERVICIO AL CIUDADANO/
 SUB GERENCIA DE PLANEACIÓN Y PROYECTOS</v>
           </cell>
           <cell r="S93"/>
@@ -14500,7 +14504,7 @@
             <v>Servicio al Ciudadano (20250110042183)</v>
           </cell>
           <cell r="G94" t="str">
-            <v>DIRECCIÓN DE SERVICIO AL CIUDADANO
+            <v>DIRECCIÓN DE SERVICIO AL CIUDADANO/
 SUB GERENCIA DE PLANEACIÓN Y PROYECTOS</v>
           </cell>
           <cell r="S94">
@@ -14673,8 +14677,8 @@
             <v>Auditoría al Cierre del Almacén (20250110045533)</v>
           </cell>
           <cell r="G107" t="str">
-            <v>SUB GERENCIA JURÍDICA
-SUB GERENCIA CORPORATIVA
+            <v>SUB GERENCIA JURÍDICA/
+SUB GERENCIA CORPORATIVA/
 SUB GERENCIA DE SERVICIOS OPERACIONALES E INFRAESTRUCTURA</v>
           </cell>
           <cell r="S107"/>
@@ -14785,7 +14789,7 @@
             <v>Auditoría Gobierno Corporativo, Transparencia y Conflicto de Intereses (20250110041653)</v>
           </cell>
           <cell r="G116" t="str">
-            <v>OFICIAL DE CUMPLIMIENTO
+            <v>OFICIAL DE CUMPLIMIENTO/
 DIRECCIÓN DE GESTIÓN HUMANA</v>
           </cell>
           <cell r="S116"/>
@@ -14798,7 +14802,7 @@
             <v>Auditoría Gobierno Corporativo, Transparencia y Conflicto de Intereses (20250110041653)</v>
           </cell>
           <cell r="G117" t="str">
-            <v>OFICIAL DE CUMPLIMIENTO
+            <v>OFICIAL DE CUMPLIMIENTO/
 DIRECCIÓN DE GESTIÓN HUMANA</v>
           </cell>
           <cell r="S117"/>
@@ -14811,7 +14815,7 @@
             <v>Auditoría Gobierno Corporativo, Transparencia y Conflicto de Intereses (20250110041653)</v>
           </cell>
           <cell r="G118" t="str">
-            <v>OFICIAL DE CUMPLIMIENTO
+            <v>OFICIAL DE CUMPLIMIENTO/
 DIRECCIÓN DE GESTIÓN HUMANA</v>
           </cell>
           <cell r="S118"/>
@@ -14824,7 +14828,7 @@
             <v>Auditoría Gobierno Corporativo, Transparencia y Conflicto de Intereses (20250110041653)</v>
           </cell>
           <cell r="G119" t="str">
-            <v>OFICIAL DE CUMPLIMIENTO
+            <v>OFICIAL DE CUMPLIMIENTO/
 DIRECCIÓN DE GESTIÓN HUMANA</v>
           </cell>
           <cell r="S119"/>
@@ -14897,7 +14901,7 @@
             <v>Auditoría Gobierno Corporativo, Transparencia y Conflicto de Intereses (20250110041653)</v>
           </cell>
           <cell r="G125" t="str">
-            <v>SUB GERENCIA JURÍDICA
+            <v>SUB GERENCIA JURÍDICA/
 SUB GERENCIA DE PLANEACIÓN Y PROYECTOS</v>
           </cell>
           <cell r="S125"/>
@@ -14910,7 +14914,7 @@
             <v>Auditoría Gobierno Corporativo, Transparencia y Conflicto de Intereses (20250110041653)</v>
           </cell>
           <cell r="G126" t="str">
-            <v>SUB GERENCIA JURÍDICA
+            <v>SUB GERENCIA JURÍDICA/
 SUB GERENCIA DE PLANEACIÓN Y PROYECTOS</v>
           </cell>
           <cell r="S126"/>
@@ -14923,7 +14927,7 @@
             <v>Auditoría Gobierno Corporativo, Transparencia y Conflicto de Intereses (20250110041653)</v>
           </cell>
           <cell r="G127" t="str">
-            <v>SUB GERENCIA JURÍDICA
+            <v>SUB GERENCIA JURÍDICA/
 SUB GERENCIA DE PLANEACIÓN Y PROYECTOS</v>
           </cell>
           <cell r="S127"/>
@@ -15278,7 +15282,7 @@
             <v xml:space="preserve">Migración de datos a la nube 20261200022073 </v>
           </cell>
           <cell r="G155" t="str">
-            <v>DIRECCIÓN DE RECURSOS TECNOLÓGICOS
+            <v>DIRECCIÓN DE RECURSOS TECNOLÓGICOS/
 SUB GERENCIA DE PLANEACIÓN Y PROYECTOS</v>
           </cell>
           <cell r="S155"/>
@@ -15303,7 +15307,7 @@
             <v xml:space="preserve">Migración de datos a la nube 20261200022073 </v>
           </cell>
           <cell r="G157" t="str">
-            <v>DIRECCIÓN DE RECURSOS TECNOLÓGICOS
+            <v>DIRECCIÓN DE RECURSOS TECNOLÓGICOS/
 SUB GERENCIA DE PLANEACIÓN Y PROYECTOS</v>
           </cell>
           <cell r="S157"/>
@@ -28574,21 +28578,7 @@
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CEA19F0D-D53E-4776-BB60-8DAF8AF7C40F}" name="Tabla2" displayName="Tabla2" ref="A1:AJ85" totalsRowShown="0" headerRowDxfId="299" dataDxfId="298" tableBorderDxfId="297">
-  <autoFilter ref="A1:AJ85" xr:uid="{CEA19F0D-D53E-4776-BB60-8DAF8AF7C40F}">
-    <filterColumn colId="20">
-      <filters>
-        <filter val="DIRECCIÓN DE RECURSOS FÍSICOS"/>
-        <filter val="DIRECCIÓN DE RECURSOS TECNOLÓGICOS_x000a_DIRECCIÓNDEGESTIÓNFINANCIERA"/>
-        <filter val="DIRECCIÓN DE SERVICIO AL TRANSPORTADOR DIRECCIÓN DE RECURSOST ECNOLÓGICOS"/>
-        <filter val="DIRECCIÓN DE SERVICIO ALTRANSPORTADOR"/>
-        <filter val="DIRECCIÓNDEGESTIÓNFINANCIERA"/>
-        <filter val="OFICINA DE AUDITORÍA INTERNA _x000a_SUBGERENCIA JURÍDICA _x000a_DIRECCIÓNFINANCIERA"/>
-        <filter val="SUBGERENCIA DE SERVICIOS PERACIONALES E INFRAESTRUCTURA"/>
-        <filter val="SUBGERENCIA PLANEACIÓN Y PROYECTOS"/>
-        <filter val="SUBGERENCIAJ URÍDICA"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AJ85" xr:uid="{CEA19F0D-D53E-4776-BB60-8DAF8AF7C40F}"/>
   <tableColumns count="36">
     <tableColumn id="1" xr3:uid="{7A8D3A5E-E004-426E-B403-310EC9C105F1}" name="No." dataDxfId="296"/>
     <tableColumn id="2" xr3:uid="{657020D6-E9B2-4900-BBA6-15C5F0ADC46D}" name="FECHA REPORTE DE LA INFORMACIÓN" dataDxfId="295"/>
@@ -29260,7 +29250,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="2" spans="1:36" ht="79.8" hidden="1">
+    <row r="2" spans="1:36" ht="79.8">
       <c r="A2" s="59">
         <v>117</v>
       </c>
@@ -29316,7 +29306,7 @@
         <v>100</v>
       </c>
       <c r="U2" s="60" t="s">
-        <v>800</v>
+        <v>812</v>
       </c>
       <c r="V2" s="138">
         <v>45957</v>
@@ -29365,7 +29355,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="3" spans="1:36" ht="125.4" hidden="1">
+    <row r="3" spans="1:36" ht="125.4">
       <c r="A3" s="59">
         <v>118</v>
       </c>
@@ -29421,7 +29411,7 @@
         <v>100</v>
       </c>
       <c r="U3" s="60" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="V3" s="138">
         <v>45957</v>
@@ -29474,7 +29464,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="4" spans="1:36" ht="125.4" hidden="1">
+    <row r="4" spans="1:36" ht="125.4">
       <c r="A4" s="59">
         <v>123</v>
       </c>
@@ -29530,7 +29520,7 @@
         <v>100</v>
       </c>
       <c r="U4" s="60" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="V4" s="137" t="s">
         <v>38</v>
@@ -29583,7 +29573,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:36" ht="125.4" hidden="1">
+    <row r="5" spans="1:36" ht="125.4">
       <c r="A5" s="59">
         <v>124</v>
       </c>
@@ -29639,7 +29629,7 @@
         <v>100</v>
       </c>
       <c r="U5" s="60" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="V5" s="137" t="s">
         <v>38</v>
@@ -29690,7 +29680,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:36" ht="136.80000000000001" hidden="1">
+    <row r="6" spans="1:36" ht="136.80000000000001">
       <c r="A6" s="59">
         <v>189</v>
       </c>
@@ -29746,7 +29736,7 @@
         <v>100</v>
       </c>
       <c r="U6" s="60" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="V6" s="137" t="s">
         <v>38</v>
@@ -29799,7 +29789,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="7" spans="1:36" ht="136.80000000000001" hidden="1">
+    <row r="7" spans="1:36" ht="136.80000000000001">
       <c r="A7" s="59">
         <v>190</v>
       </c>
@@ -29855,7 +29845,7 @@
         <v>100</v>
       </c>
       <c r="U7" s="60" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="V7" s="137" t="s">
         <v>38</v>
@@ -29908,7 +29898,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="8" spans="1:36" ht="136.80000000000001" hidden="1">
+    <row r="8" spans="1:36" ht="136.80000000000001">
       <c r="A8" s="59">
         <v>191</v>
       </c>
@@ -29964,7 +29954,7 @@
         <v>100</v>
       </c>
       <c r="U8" s="60" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="V8" s="137" t="s">
         <v>38</v>
@@ -30017,7 +30007,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="9" spans="1:36" ht="136.80000000000001" hidden="1">
+    <row r="9" spans="1:36" ht="136.80000000000001">
       <c r="A9" s="141">
         <v>193</v>
       </c>
@@ -30073,7 +30063,7 @@
         <v>100</v>
       </c>
       <c r="U9" s="75" t="s">
-        <v>804</v>
+        <v>813</v>
       </c>
       <c r="V9" s="142" t="s">
         <v>38</v>
@@ -30126,7 +30116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:36" ht="171" hidden="1">
+    <row r="10" spans="1:36" ht="171">
       <c r="A10" s="59">
         <v>196</v>
       </c>
@@ -30182,7 +30172,7 @@
         <v>100</v>
       </c>
       <c r="U10" s="60" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="V10" s="137" t="s">
         <v>38</v>
@@ -30235,7 +30225,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="11" spans="1:36" ht="171" hidden="1">
+    <row r="11" spans="1:36" ht="171">
       <c r="A11" s="59">
         <v>197</v>
       </c>
@@ -30291,7 +30281,7 @@
         <v>100</v>
       </c>
       <c r="U11" s="60" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="V11" s="137" t="s">
         <v>38</v>
@@ -30314,7 +30304,7 @@
       </c>
       <c r="AC11" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AD11" s="67">
         <f t="shared" ca="1" si="1"/>
@@ -30340,7 +30330,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="12" spans="1:36" ht="171" hidden="1">
+    <row r="12" spans="1:36" ht="171">
       <c r="A12" s="59">
         <v>198</v>
       </c>
@@ -30396,7 +30386,7 @@
         <v>100</v>
       </c>
       <c r="U12" s="60" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="V12" s="137" t="s">
         <v>38</v>
@@ -30419,7 +30409,7 @@
       </c>
       <c r="AC12" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AD12" s="67">
         <f t="shared" ca="1" si="1"/>
@@ -30445,7 +30435,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="13" spans="1:36" ht="91.2" hidden="1">
+    <row r="13" spans="1:36" ht="91.2">
       <c r="A13" s="59">
         <v>199</v>
       </c>
@@ -30501,7 +30491,7 @@
         <v>100</v>
       </c>
       <c r="U13" s="60" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="V13" s="137" t="s">
         <v>38</v>
@@ -30554,7 +30544,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="14" spans="1:36" ht="125.4" hidden="1">
+    <row r="14" spans="1:36" ht="125.4">
       <c r="A14" s="59">
         <v>200</v>
       </c>
@@ -30610,7 +30600,7 @@
         <v>100</v>
       </c>
       <c r="U14" s="60" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="V14" s="137" t="s">
         <v>38</v>
@@ -30719,7 +30709,7 @@
         <v>100</v>
       </c>
       <c r="U15" s="60" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="V15" s="137" t="s">
         <v>38</v>
@@ -30772,7 +30762,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:36" ht="159.6" hidden="1">
+    <row r="16" spans="1:36" ht="159.6">
       <c r="A16" s="59">
         <v>214</v>
       </c>
@@ -30828,7 +30818,7 @@
         <v>100</v>
       </c>
       <c r="U16" s="60" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="V16" s="137" t="s">
         <v>38</v>
@@ -30851,7 +30841,7 @@
       </c>
       <c r="AC16" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AD16" s="67">
         <f t="shared" ca="1" si="1"/>
@@ -30877,7 +30867,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="17" spans="1:36" ht="182.4" hidden="1">
+    <row r="17" spans="1:36" ht="182.4">
       <c r="A17" s="59">
         <v>215</v>
       </c>
@@ -30933,7 +30923,7 @@
         <v>100</v>
       </c>
       <c r="U17" s="60" t="s">
-        <v>806</v>
+        <v>814</v>
       </c>
       <c r="V17" s="137" t="s">
         <v>38</v>
@@ -30986,7 +30976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:36" ht="68.400000000000006" hidden="1">
+    <row r="18" spans="1:36" ht="68.400000000000006">
       <c r="A18" s="59">
         <v>221</v>
       </c>
@@ -31042,7 +31032,7 @@
         <v>100</v>
       </c>
       <c r="U18" s="60" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="V18" s="137" t="s">
         <v>38</v>
@@ -31095,7 +31085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:36" ht="114" hidden="1">
+    <row r="19" spans="1:36" ht="114">
       <c r="A19" s="59">
         <v>222</v>
       </c>
@@ -31151,7 +31141,7 @@
         <v>100</v>
       </c>
       <c r="U19" s="60" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="V19" s="137" t="s">
         <v>38</v>
@@ -31204,7 +31194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:36" ht="114" hidden="1">
+    <row r="20" spans="1:36" ht="114">
       <c r="A20" s="59">
         <v>223</v>
       </c>
@@ -31260,7 +31250,7 @@
         <v>100</v>
       </c>
       <c r="U20" s="60" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="V20" s="137" t="s">
         <v>38</v>
@@ -31313,7 +31303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:36" ht="91.2" hidden="1">
+    <row r="21" spans="1:36" ht="91.2">
       <c r="A21" s="141">
         <v>230</v>
       </c>
@@ -31369,7 +31359,7 @@
         <v>100</v>
       </c>
       <c r="U21" s="75" t="s">
-        <v>808</v>
+        <v>815</v>
       </c>
       <c r="V21" s="142" t="s">
         <v>38</v>
@@ -31418,7 +31408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:36" ht="91.2" hidden="1">
+    <row r="22" spans="1:36" ht="91.2">
       <c r="A22" s="141">
         <v>232</v>
       </c>
@@ -31474,7 +31464,7 @@
         <v>100</v>
       </c>
       <c r="U22" s="75" t="s">
-        <v>808</v>
+        <v>815</v>
       </c>
       <c r="V22" s="142" t="s">
         <v>38</v>
@@ -31523,7 +31513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:36" ht="91.2" hidden="1">
+    <row r="23" spans="1:36" ht="91.2">
       <c r="A23" s="141">
         <v>233</v>
       </c>
@@ -31579,7 +31569,7 @@
         <v>100</v>
       </c>
       <c r="U23" s="75" t="s">
-        <v>808</v>
+        <v>815</v>
       </c>
       <c r="V23" s="142" t="s">
         <v>38</v>
@@ -31684,7 +31674,7 @@
         <v>100</v>
       </c>
       <c r="U24" s="75" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="V24" s="142" t="s">
         <v>38</v>
@@ -31793,7 +31783,7 @@
         <v>100</v>
       </c>
       <c r="U25" s="60" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="V25" s="137" t="s">
         <v>38</v>
@@ -31846,7 +31836,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="26" spans="1:36" ht="136.80000000000001" hidden="1">
+    <row r="26" spans="1:36" ht="136.80000000000001">
       <c r="A26" s="59">
         <v>246</v>
       </c>
@@ -31902,7 +31892,7 @@
         <v>100</v>
       </c>
       <c r="U26" s="60" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="V26" s="137" t="s">
         <v>38</v>
@@ -31925,7 +31915,7 @@
       </c>
       <c r="AC26" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AD26" s="67">
         <f t="shared" ca="1" si="1"/>
@@ -31951,7 +31941,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="27" spans="1:36" ht="193.8" hidden="1">
+    <row r="27" spans="1:36" ht="193.8">
       <c r="A27" s="59">
         <v>247</v>
       </c>
@@ -32007,7 +31997,7 @@
         <v>100</v>
       </c>
       <c r="U27" s="60" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="V27" s="137" t="s">
         <v>38</v>
@@ -32030,7 +32020,7 @@
       </c>
       <c r="AC27" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AD27" s="67">
         <f t="shared" ca="1" si="1"/>
@@ -32056,7 +32046,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="28" spans="1:36" ht="91.2" hidden="1">
+    <row r="28" spans="1:36" ht="91.2">
       <c r="A28" s="59">
         <v>255</v>
       </c>
@@ -32112,7 +32102,7 @@
         <v>100</v>
       </c>
       <c r="U28" s="60" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="V28" s="137" t="s">
         <v>38</v>
@@ -32135,7 +32125,7 @@
       </c>
       <c r="AC28" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AD28" s="67">
         <f t="shared" ca="1" si="1"/>
@@ -32161,7 +32151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:36" ht="102.6" hidden="1">
+    <row r="29" spans="1:36" ht="102.6">
       <c r="A29" s="59">
         <v>256</v>
       </c>
@@ -32217,7 +32207,7 @@
         <v>100</v>
       </c>
       <c r="U29" s="60" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="V29" s="137" t="s">
         <v>38</v>
@@ -32240,7 +32230,7 @@
       </c>
       <c r="AC29" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AD29" s="67">
         <f t="shared" ca="1" si="1"/>
@@ -32266,7 +32256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:36" ht="91.2" hidden="1">
+    <row r="30" spans="1:36" ht="91.2">
       <c r="A30" s="151">
         <v>259</v>
       </c>
@@ -32322,7 +32312,7 @@
         <v>100</v>
       </c>
       <c r="U30" s="152" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="V30" s="153" t="s">
         <v>38</v>
@@ -32375,7 +32365,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="31" spans="1:36" ht="91.2" hidden="1">
+    <row r="31" spans="1:36" ht="91.2">
       <c r="A31" s="141">
         <v>260</v>
       </c>
@@ -32431,7 +32421,7 @@
         <v>100</v>
       </c>
       <c r="U31" s="75" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="V31" s="142" t="s">
         <v>38</v>
@@ -32484,7 +32474,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="32" spans="1:36" ht="136.80000000000001" hidden="1">
+    <row r="32" spans="1:36" ht="136.80000000000001">
       <c r="A32" s="141">
         <v>261</v>
       </c>
@@ -32540,7 +32530,7 @@
         <v>100</v>
       </c>
       <c r="U32" s="75" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="V32" s="142" t="s">
         <v>38</v>
@@ -32589,7 +32579,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="33" spans="1:36" ht="136.80000000000001" hidden="1">
+    <row r="33" spans="1:36" ht="136.80000000000001">
       <c r="A33" s="141">
         <v>262</v>
       </c>
@@ -32645,7 +32635,7 @@
         <v>100</v>
       </c>
       <c r="U33" s="75" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="V33" s="142" t="s">
         <v>38</v>
@@ -32698,7 +32688,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="34" spans="1:36" ht="136.80000000000001" hidden="1">
+    <row r="34" spans="1:36" ht="136.80000000000001">
       <c r="A34" s="59">
         <v>263</v>
       </c>
@@ -32754,7 +32744,7 @@
         <v>100</v>
       </c>
       <c r="U34" s="60" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="V34" s="137" t="s">
         <v>38</v>
@@ -32805,7 +32795,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="35" spans="1:36" ht="148.19999999999999" hidden="1">
+    <row r="35" spans="1:36" ht="148.19999999999999">
       <c r="A35" s="59">
         <v>281</v>
       </c>
@@ -32861,7 +32851,7 @@
         <v>100</v>
       </c>
       <c r="U35" s="60" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="V35" s="137" t="s">
         <v>38</v>
@@ -32914,7 +32904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:36" ht="136.80000000000001" hidden="1">
+    <row r="36" spans="1:36" ht="136.80000000000001">
       <c r="A36" s="59">
         <v>181</v>
       </c>
@@ -32970,7 +32960,7 @@
         <v>100</v>
       </c>
       <c r="U36" s="60" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="V36" s="137" t="s">
         <v>244</v>
@@ -33079,7 +33069,7 @@
         <v>100</v>
       </c>
       <c r="U37" s="60" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="V37" s="137" t="s">
         <v>244</v>
@@ -33130,7 +33120,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="38" spans="1:36" ht="125.4" hidden="1">
+    <row r="38" spans="1:36" ht="125.4">
       <c r="A38" s="59">
         <v>183</v>
       </c>
@@ -33186,7 +33176,7 @@
         <v>100</v>
       </c>
       <c r="U38" s="60" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="V38" s="137" t="s">
         <v>244</v>
@@ -33237,7 +33227,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="39" spans="1:36" ht="148.19999999999999" hidden="1">
+    <row r="39" spans="1:36" ht="148.19999999999999">
       <c r="A39" s="161">
         <v>189</v>
       </c>
@@ -33293,7 +33283,7 @@
         <v>100</v>
       </c>
       <c r="U39" s="75" t="s">
-        <v>812</v>
+        <v>818</v>
       </c>
       <c r="V39" s="142" t="s">
         <v>244</v>
@@ -33344,7 +33334,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="40" spans="1:36" ht="159.6" hidden="1">
+    <row r="40" spans="1:36" ht="159.6">
       <c r="A40" s="59">
         <v>190</v>
       </c>
@@ -33451,7 +33441,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="41" spans="1:36" ht="102.6" hidden="1">
+    <row r="41" spans="1:36" ht="102.6">
       <c r="A41" s="78">
         <v>191</v>
       </c>
@@ -33507,7 +33497,7 @@
         <v>100</v>
       </c>
       <c r="U41" s="60" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="V41" s="137" t="s">
         <v>244</v>
@@ -33560,7 +33550,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="42" spans="1:36" ht="125.4" hidden="1">
+    <row r="42" spans="1:36" ht="125.4">
       <c r="A42" s="59">
         <v>194</v>
       </c>
@@ -33616,7 +33606,7 @@
         <v>100</v>
       </c>
       <c r="U42" s="60" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="V42" s="137" t="s">
         <v>244</v>
@@ -33669,7 +33659,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="43" spans="1:36" ht="148.19999999999999" hidden="1">
+    <row r="43" spans="1:36" ht="148.19999999999999">
       <c r="A43" s="161">
         <v>195</v>
       </c>
@@ -33725,7 +33715,7 @@
         <v>100</v>
       </c>
       <c r="U43" s="75" t="s">
-        <v>812</v>
+        <v>819</v>
       </c>
       <c r="V43" s="142" t="s">
         <v>244</v>
@@ -33832,7 +33822,7 @@
         <v>100</v>
       </c>
       <c r="U44" s="60" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="V44" s="137" t="s">
         <v>244</v>
@@ -33883,7 +33873,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="45" spans="1:36" ht="125.4" hidden="1">
+    <row r="45" spans="1:36" ht="125.4">
       <c r="A45" s="83">
         <v>215</v>
       </c>
@@ -33939,7 +33929,7 @@
         <v>100</v>
       </c>
       <c r="U45" s="84" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="V45" s="139" t="s">
         <v>244</v>
@@ -33990,7 +33980,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="46" spans="1:36" ht="102.6" hidden="1">
+    <row r="46" spans="1:36" ht="102.6">
       <c r="A46" s="78">
         <v>216</v>
       </c>
@@ -34097,7 +34087,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="47" spans="1:36" ht="182.4" hidden="1">
+    <row r="47" spans="1:36" ht="182.4">
       <c r="A47" s="78">
         <v>217</v>
       </c>
@@ -34204,7 +34194,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="48" spans="1:36" ht="131.4" hidden="1" customHeight="1">
+    <row r="48" spans="1:36" ht="131.4" customHeight="1">
       <c r="A48" s="78">
         <v>218</v>
       </c>
@@ -34369,7 +34359,7 @@
         <v>100</v>
       </c>
       <c r="U49" s="60" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="V49" s="137" t="s">
         <v>244</v>
@@ -34476,7 +34466,7 @@
         <v>100</v>
       </c>
       <c r="U50" s="60" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="V50" s="137" t="s">
         <v>244</v>
@@ -34527,7 +34517,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="51" spans="1:36" ht="171" hidden="1">
+    <row r="51" spans="1:36" ht="171">
       <c r="A51" s="59">
         <v>223</v>
       </c>
@@ -34583,7 +34573,7 @@
         <v>100</v>
       </c>
       <c r="U51" s="60" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="V51" s="137" t="s">
         <v>244</v>
@@ -34634,7 +34624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:36" ht="125.4" hidden="1">
+    <row r="52" spans="1:36" ht="125.4">
       <c r="A52" s="59">
         <v>226</v>
       </c>
@@ -34741,7 +34731,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="53" spans="1:36" ht="125.4" hidden="1">
+    <row r="53" spans="1:36" ht="125.4">
       <c r="A53" s="59">
         <v>227</v>
       </c>
@@ -34848,7 +34838,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="54" spans="1:36" ht="193.8" hidden="1">
+    <row r="54" spans="1:36" ht="193.8">
       <c r="A54" s="59">
         <v>228</v>
       </c>
@@ -34955,7 +34945,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="55" spans="1:36" ht="125.4" hidden="1">
+    <row r="55" spans="1:36" ht="125.4">
       <c r="A55" s="78">
         <v>229</v>
       </c>
@@ -35062,7 +35052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:36" ht="136.80000000000001" hidden="1">
+    <row r="56" spans="1:36" ht="136.80000000000001">
       <c r="A56" s="78">
         <v>230</v>
       </c>
@@ -35169,7 +35159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:36" ht="114" hidden="1">
+    <row r="57" spans="1:36" ht="114">
       <c r="A57" s="59">
         <v>231</v>
       </c>
@@ -35225,7 +35215,7 @@
         <v>100</v>
       </c>
       <c r="U57" s="60" t="s">
-        <v>815</v>
+        <v>820</v>
       </c>
       <c r="V57" s="137" t="s">
         <v>244</v>
@@ -35276,7 +35266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:36" ht="171" hidden="1">
+    <row r="58" spans="1:36" ht="171">
       <c r="A58" s="78">
         <v>240</v>
       </c>
@@ -35383,7 +35373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:36" ht="205.2" hidden="1">
+    <row r="59" spans="1:36" ht="205.2">
       <c r="A59" s="59">
         <v>245</v>
       </c>
@@ -35490,7 +35480,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="60" spans="1:36" ht="68.400000000000006" hidden="1">
+    <row r="60" spans="1:36" ht="68.400000000000006">
       <c r="A60" s="78">
         <v>246</v>
       </c>
@@ -35597,7 +35587,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="61" spans="1:36" ht="148.19999999999999" hidden="1">
+    <row r="61" spans="1:36" ht="148.19999999999999">
       <c r="A61" s="78">
         <v>247</v>
       </c>
@@ -35653,7 +35643,7 @@
         <v>100</v>
       </c>
       <c r="U61" s="60" t="s">
-        <v>816</v>
+        <v>821</v>
       </c>
       <c r="V61" s="137" t="s">
         <v>244</v>
@@ -35704,7 +35694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:36" ht="228" hidden="1">
+    <row r="62" spans="1:36" ht="228">
       <c r="A62" s="59">
         <v>120</v>
       </c>
@@ -35815,7 +35805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:36" ht="262.2" hidden="1">
+    <row r="63" spans="1:36" ht="262.2">
       <c r="A63" s="78">
         <v>123</v>
       </c>
@@ -35875,7 +35865,7 @@
         <v>100</v>
       </c>
       <c r="U63" s="60" t="s">
-        <v>817</v>
+        <v>822</v>
       </c>
       <c r="V63" s="60" t="s">
         <v>455</v>
@@ -35986,7 +35976,7 @@
         <v>100</v>
       </c>
       <c r="U64" s="60" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="V64" s="60" t="s">
         <v>455</v>
@@ -36037,7 +36027,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:36" ht="171" hidden="1">
+    <row r="65" spans="1:36" ht="171">
       <c r="A65" s="59">
         <v>184</v>
       </c>
@@ -36097,7 +36087,7 @@
         <v>100</v>
       </c>
       <c r="U65" s="60" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="V65" s="60" t="s">
         <v>455</v>
@@ -36150,7 +36140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:36" ht="205.2" hidden="1">
+    <row r="66" spans="1:36" ht="205.2">
       <c r="A66" s="59">
         <v>186</v>
       </c>
@@ -36210,7 +36200,7 @@
         <v>100</v>
       </c>
       <c r="U66" s="60" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="V66" s="60" t="s">
         <v>446</v>
@@ -36263,7 +36253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:36" ht="171" hidden="1">
+    <row r="67" spans="1:36" ht="171">
       <c r="A67" s="59">
         <v>187</v>
       </c>
@@ -36323,7 +36313,7 @@
         <v>100</v>
       </c>
       <c r="U67" s="60" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="V67" s="60" t="s">
         <v>455</v>
@@ -36376,7 +36366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:36" ht="171" hidden="1">
+    <row r="68" spans="1:36" ht="171">
       <c r="A68" s="59">
         <v>188</v>
       </c>
@@ -36436,7 +36426,7 @@
         <v>100</v>
       </c>
       <c r="U68" s="60" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="V68" s="60" t="s">
         <v>455</v>
@@ -36600,7 +36590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:36" ht="228" hidden="1">
+    <row r="70" spans="1:36" ht="228">
       <c r="A70" s="59">
         <v>221</v>
       </c>
@@ -36660,7 +36650,7 @@
         <v>100</v>
       </c>
       <c r="U70" s="60" t="s">
-        <v>818</v>
+        <v>810</v>
       </c>
       <c r="V70" s="60" t="s">
         <v>500</v>
@@ -36711,7 +36701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:36" ht="239.4" hidden="1">
+    <row r="71" spans="1:36" ht="239.4">
       <c r="A71" s="59">
         <v>222</v>
       </c>
@@ -36771,7 +36761,7 @@
         <v>100</v>
       </c>
       <c r="U71" s="60" t="s">
-        <v>818</v>
+        <v>810</v>
       </c>
       <c r="V71" s="60" t="s">
         <v>500</v>
@@ -36822,7 +36812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:36" ht="228" hidden="1">
+    <row r="72" spans="1:36" ht="228">
       <c r="A72" s="78">
         <v>224</v>
       </c>
@@ -36882,7 +36872,7 @@
         <v>100</v>
       </c>
       <c r="U72" s="60" t="s">
-        <v>818</v>
+        <v>810</v>
       </c>
       <c r="V72" s="60" t="s">
         <v>500</v>
@@ -36933,7 +36923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:36" ht="239.4" hidden="1">
+    <row r="73" spans="1:36" ht="239.4">
       <c r="A73" s="59">
         <v>225</v>
       </c>
@@ -36993,7 +36983,7 @@
         <v>100</v>
       </c>
       <c r="U73" s="60" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="V73" s="60" t="s">
         <v>500</v>
@@ -37046,7 +37036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:36" ht="193.8" hidden="1">
+    <row r="74" spans="1:36" ht="193.8">
       <c r="A74" s="59">
         <v>232</v>
       </c>
@@ -37106,7 +37096,7 @@
         <v>100</v>
       </c>
       <c r="U74" s="60" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="V74" s="60" t="s">
         <v>500</v>
@@ -37159,7 +37149,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:36" ht="182.4" hidden="1">
+    <row r="75" spans="1:36" ht="182.4">
       <c r="A75" s="59">
         <v>233</v>
       </c>
@@ -37219,7 +37209,7 @@
         <v>100</v>
       </c>
       <c r="U75" s="60" t="s">
-        <v>819</v>
+        <v>811</v>
       </c>
       <c r="V75" s="60" t="s">
         <v>500</v>
@@ -37270,7 +37260,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="76" spans="1:36" ht="262.2" hidden="1">
+    <row r="76" spans="1:36" ht="262.2">
       <c r="A76" s="59">
         <v>234</v>
       </c>
@@ -37330,7 +37320,7 @@
         <v>100</v>
       </c>
       <c r="U76" s="60" t="s">
-        <v>819</v>
+        <v>811</v>
       </c>
       <c r="V76" s="60" t="s">
         <v>500</v>
@@ -37381,7 +37371,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="77" spans="1:36" ht="205.2" hidden="1">
+    <row r="77" spans="1:36" ht="205.2">
       <c r="A77" s="59">
         <v>235</v>
       </c>
@@ -37441,7 +37431,7 @@
         <v>100</v>
       </c>
       <c r="U77" s="60" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="V77" s="60" t="s">
         <v>500</v>
@@ -37494,7 +37484,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="78" spans="1:36" ht="262.2" hidden="1">
+    <row r="78" spans="1:36" ht="262.2">
       <c r="A78" s="59">
         <v>236</v>
       </c>
@@ -37554,7 +37544,7 @@
         <v>100</v>
       </c>
       <c r="U78" s="60" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="V78" s="60" t="s">
         <v>500</v>
@@ -37607,7 +37597,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="79" spans="1:36" ht="159.6" hidden="1">
+    <row r="79" spans="1:36" ht="159.6">
       <c r="A79" s="59">
         <v>237</v>
       </c>
@@ -37667,7 +37657,7 @@
         <v>100</v>
       </c>
       <c r="U79" s="60" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="V79" s="60" t="s">
         <v>500</v>
@@ -37780,7 +37770,7 @@
         <v>100</v>
       </c>
       <c r="U80" s="60" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="V80" s="60" t="s">
         <v>578</v>
@@ -37831,7 +37821,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="81" spans="1:36" ht="250.8" hidden="1">
+    <row r="81" spans="1:36" ht="250.8">
       <c r="A81" s="59">
         <v>239</v>
       </c>
@@ -37891,7 +37881,7 @@
         <v>100</v>
       </c>
       <c r="U81" s="60" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="V81" s="60" t="s">
         <v>578</v>
@@ -37942,7 +37932,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="82" spans="1:36" ht="125.4" hidden="1">
+    <row r="82" spans="1:36" ht="125.4">
       <c r="A82" s="59">
         <v>241</v>
       </c>
@@ -38002,7 +37992,7 @@
         <v>100</v>
       </c>
       <c r="U82" s="60" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="V82" s="60" t="s">
         <v>592</v>
@@ -38053,7 +38043,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="83" spans="1:36" ht="114" hidden="1">
+    <row r="83" spans="1:36" ht="114">
       <c r="A83" s="59">
         <v>242</v>
       </c>
@@ -38113,7 +38103,7 @@
         <v>100</v>
       </c>
       <c r="U83" s="60" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="V83" s="60" t="s">
         <v>592</v>
@@ -38164,7 +38154,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="84" spans="1:36" ht="228" hidden="1">
+    <row r="84" spans="1:36" ht="228">
       <c r="A84" s="59">
         <v>243</v>
       </c>
@@ -38224,7 +38214,7 @@
         <v>100</v>
       </c>
       <c r="U84" s="60" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="V84" s="60" t="s">
         <v>592</v>
@@ -38275,7 +38265,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="85" spans="1:36" ht="205.2" hidden="1">
+    <row r="85" spans="1:36" ht="205.2">
       <c r="A85" s="59">
         <v>244</v>
       </c>
@@ -38335,7 +38325,7 @@
         <v>100</v>
       </c>
       <c r="U85" s="60" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="V85" s="60" t="s">
         <v>592</v>

--- a/TABLERO_PA_C.xlsx
+++ b/TABLERO_PA_C.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e2a95cfba4fb0187/Escritorio/Tableros de Control/2. Contraloría/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="496" documentId="13_ncr:1_{5037B3AD-B0A2-4521-8F49-D3B2F1605E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D9A7BB0-831B-468B-958E-712AFA3F124F}"/>
+  <xr:revisionPtr revIDLastSave="501" documentId="13_ncr:1_{5037B3AD-B0A2-4521-8F49-D3B2F1605E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A526515-513D-45E4-AB52-F132E910C74D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="10" xr2:uid="{E38B2051-8614-49B4-943E-B3707D980583}"/>
   </bookViews>
@@ -2721,9 +2721,6 @@
     <t>SUB GERENCIA DE SERVICIOS OPERACIONALES E INFRAESTRUCTURA</t>
   </si>
   <si>
-    <t>SUBGERENCIA DE PLANEACIÓN Y PROYECTOS DIRECCIÓN DE GESTIÓN HUMANA</t>
-  </si>
-  <si>
     <t>DIRECCIÓN DE GESTIÓN FINANCIERA/
 DIRECCIÓN DE RECURSOS FÍSICOS Y NEGOCIOS</t>
   </si>
@@ -2768,6 +2765,9 @@
     <t>OFICINA DE AUDITORÍA INTERNA/ 
 SUBGERENCIA JURÍDICA/ 
 DIRECCIÓN DE GESTIÓN FINANCIERA</t>
+  </si>
+  <si>
+    <t>SUBGERENCIA DE PLANEACIÓN Y PROYECTOS/ DIRECCIÓN DE GESTIÓN HUMANA</t>
   </si>
 </sst>
 </file>
@@ -5458,6 +5458,21 @@
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="3" tint="0.499984740745262"/>
@@ -5564,21 +5579,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
@@ -20576,6 +20576,129 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B6C7AB91-8822-4E2E-BE9B-A9578BEEAA20}" name="TablaDinámica3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:G7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="19">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+    <i i="3">
+      <x v="3"/>
+    </i>
+    <i i="4">
+      <x v="4"/>
+    </i>
+    <i i="5">
+      <x v="5"/>
+    </i>
+  </colItems>
+  <dataFields count="6">
+    <dataField name="Cuenta de No. Hallazgo" fld="2" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Total Planes de acción" fld="5" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Abiertos" fld="6" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Vencidos" fld="7" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Finalizados" fld="8" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Auditoría" fld="1" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="5">
+    <format dxfId="240">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="239">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="238">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0"/>
+    </format>
+    <format dxfId="237">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="236">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="4">
+            <x v="0"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5E7F1577-F431-4B0C-B786-3FF0F4829E0F}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A9:E35" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
@@ -20769,255 +20892,6 @@
     <dataField name="Suma de Finalizados" fld="8" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="20">
-    <format dxfId="255">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="254">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="253">
-      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0"/>
-    </format>
-    <format dxfId="252">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="251">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="250">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="249">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="248">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="247">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="14"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="246">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="19"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="245">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="20"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="244">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="23"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="243">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="25"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="242">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="42"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="241">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="43"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="240">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="44"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="239">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="46"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="238">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="47"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="237">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="50"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="236">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="12"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B6C7AB91-8822-4E2E-BE9B-A9578BEEAA20}" name="TablaDinámica3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:G7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="19">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-    <i i="2">
-      <x v="2"/>
-    </i>
-    <i i="3">
-      <x v="3"/>
-    </i>
-    <i i="4">
-      <x v="4"/>
-    </i>
-    <i i="5">
-      <x v="5"/>
-    </i>
-  </colItems>
-  <dataFields count="6">
-    <dataField name="Cuenta de No. Hallazgo" fld="2" subtotal="count" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Total Planes de acción" fld="5" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Abiertos" fld="6" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Vencidos" fld="7" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Finalizados" fld="8" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Auditoría" fld="1" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="5">
     <format dxfId="260">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
@@ -21031,13 +20905,139 @@
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
     <format dxfId="256">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
-          <reference field="4294967294" count="4">
-            <x v="0"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="255">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="254">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="253">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="252">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="14"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="251">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="19"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="250">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="20"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="249">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="23"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="248">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="25"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="247">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="42"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="246">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="43"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="245">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="44"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="244">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="46"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="243">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="47"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="242">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="50"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="241">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="12"/>
           </reference>
         </references>
       </pivotArea>
@@ -27862,255 +27862,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A9C7B425-127F-4B5F-B2E3-C2AB4F050E7C}" name="TablaDinámica3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A12:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="19">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Suma de Total Planes de acción" fld="5" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="1">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="0">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{53017CE7-FCFE-4C73-9C32-3A18A27FC23C}" name="TablaDinámica7" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
-  <location ref="F13:G16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="19">
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="54">
-        <item m="1" x="25"/>
-        <item m="1" x="26"/>
-        <item m="1" x="31"/>
-        <item m="1" x="28"/>
-        <item m="1" x="36"/>
-        <item m="1" x="42"/>
-        <item m="1" x="27"/>
-        <item m="1" x="29"/>
-        <item m="1" x="38"/>
-        <item m="1" x="43"/>
-        <item m="1" x="41"/>
-        <item m="1" x="34"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item x="11"/>
-        <item x="16"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="12"/>
-        <item x="17"/>
-        <item x="15"/>
-        <item x="9"/>
-        <item m="1" x="48"/>
-        <item x="21"/>
-        <item m="1" x="46"/>
-        <item m="1" x="52"/>
-        <item m="1" x="49"/>
-        <item m="1" x="50"/>
-        <item m="1" x="35"/>
-        <item m="1" x="32"/>
-        <item m="1" x="47"/>
-        <item m="1" x="39"/>
-        <item m="1" x="40"/>
-        <item m="1" x="45"/>
-        <item m="1" x="51"/>
-        <item m="1" x="37"/>
-        <item m="1" x="33"/>
-        <item m="1" x="30"/>
-        <item m="1" x="44"/>
-        <item x="10"/>
-        <item x="7"/>
-        <item x="13"/>
-        <item x="20"/>
-        <item x="14"/>
-        <item x="24"/>
-        <item x="19"/>
-        <item x="8"/>
-        <item x="5"/>
-        <item x="18"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="-2"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-    <i i="2">
-      <x v="2"/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="3">
-    <dataField name="Suma de Abiertos" fld="6" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Vencidos" fld="7" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Finalizados" fld="8" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="5">
-    <chartFormat chart="4" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="3">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="4">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="5">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DD0BBB6E-FA08-4903-950F-5C10965A7D8D}" name="TablaDinámica6" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A26:B31" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
@@ -28235,10 +27986,10 @@
     <dataField name="Suma de Finalizados" fld="8" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="3">
+    <format dxfId="1">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="2">
+    <format dxfId="0">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
   </formats>
@@ -28254,7 +28005,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3B3AE9AA-616F-416E-8D70-C9530CA01C24}" name="TablaDinámica4" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A19:B23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
@@ -28305,13 +28056,262 @@
     <dataField name="Suma de Alerta 30" fld="11" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
+    <format dxfId="3">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="2">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A9C7B425-127F-4B5F-B2E3-C2AB4F050E7C}" name="TablaDinámica3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A12:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="19">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Suma de Total Planes de acción" fld="5" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="2">
     <format dxfId="5">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
     <format dxfId="4">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0"/>
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{53017CE7-FCFE-4C73-9C32-3A18A27FC23C}" name="TablaDinámica7" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+  <location ref="F13:G16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="19">
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="54">
+        <item m="1" x="25"/>
+        <item m="1" x="26"/>
+        <item m="1" x="31"/>
+        <item m="1" x="28"/>
+        <item m="1" x="36"/>
+        <item m="1" x="42"/>
+        <item m="1" x="27"/>
+        <item m="1" x="29"/>
+        <item m="1" x="38"/>
+        <item m="1" x="43"/>
+        <item m="1" x="41"/>
+        <item m="1" x="34"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="11"/>
+        <item x="16"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="12"/>
+        <item x="17"/>
+        <item x="15"/>
+        <item x="9"/>
+        <item m="1" x="48"/>
+        <item x="21"/>
+        <item m="1" x="46"/>
+        <item m="1" x="52"/>
+        <item m="1" x="49"/>
+        <item m="1" x="50"/>
+        <item m="1" x="35"/>
+        <item m="1" x="32"/>
+        <item m="1" x="47"/>
+        <item m="1" x="39"/>
+        <item m="1" x="40"/>
+        <item m="1" x="45"/>
+        <item m="1" x="51"/>
+        <item m="1" x="37"/>
+        <item m="1" x="33"/>
+        <item m="1" x="30"/>
+        <item m="1" x="44"/>
+        <item x="10"/>
+        <item x="7"/>
+        <item x="13"/>
+        <item x="20"/>
+        <item x="14"/>
+        <item x="24"/>
+        <item x="19"/>
+        <item x="8"/>
+        <item x="5"/>
+        <item x="18"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="-2"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="3">
+    <dataField name="Suma de Abiertos" fld="6" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Vencidos" fld="7" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Finalizados" fld="8" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="5">
+    <chartFormat chart="4" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -29306,7 +29306,7 @@
         <v>100</v>
       </c>
       <c r="U2" s="60" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="V2" s="138">
         <v>45957</v>
@@ -30063,7 +30063,7 @@
         <v>100</v>
       </c>
       <c r="U9" s="75" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="V9" s="142" t="s">
         <v>38</v>
@@ -30304,7 +30304,7 @@
       </c>
       <c r="AC11" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD11" s="67">
         <f t="shared" ca="1" si="1"/>
@@ -30409,7 +30409,7 @@
       </c>
       <c r="AC12" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD12" s="67">
         <f t="shared" ca="1" si="1"/>
@@ -30841,7 +30841,7 @@
       </c>
       <c r="AC16" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD16" s="67">
         <f t="shared" ca="1" si="1"/>
@@ -30923,7 +30923,7 @@
         <v>100</v>
       </c>
       <c r="U17" s="60" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="V17" s="137" t="s">
         <v>38</v>
@@ -31359,7 +31359,7 @@
         <v>100</v>
       </c>
       <c r="U21" s="75" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="V21" s="142" t="s">
         <v>38</v>
@@ -31464,7 +31464,7 @@
         <v>100</v>
       </c>
       <c r="U22" s="75" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="V22" s="142" t="s">
         <v>38</v>
@@ -31569,7 +31569,7 @@
         <v>100</v>
       </c>
       <c r="U23" s="75" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="V23" s="142" t="s">
         <v>38</v>
@@ -31783,7 +31783,7 @@
         <v>100</v>
       </c>
       <c r="U25" s="60" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="V25" s="137" t="s">
         <v>38</v>
@@ -31915,7 +31915,7 @@
       </c>
       <c r="AC26" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD26" s="67">
         <f t="shared" ca="1" si="1"/>
@@ -32020,7 +32020,7 @@
       </c>
       <c r="AC27" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD27" s="67">
         <f t="shared" ca="1" si="1"/>
@@ -32125,7 +32125,7 @@
       </c>
       <c r="AC28" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD28" s="67">
         <f t="shared" ca="1" si="1"/>
@@ -32230,7 +32230,7 @@
       </c>
       <c r="AC29" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD29" s="67">
         <f t="shared" ca="1" si="1"/>
@@ -33069,7 +33069,7 @@
         <v>100</v>
       </c>
       <c r="U37" s="60" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="V37" s="137" t="s">
         <v>244</v>
@@ -33283,7 +33283,7 @@
         <v>100</v>
       </c>
       <c r="U39" s="75" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="V39" s="142" t="s">
         <v>244</v>
@@ -33715,7 +33715,7 @@
         <v>100</v>
       </c>
       <c r="U43" s="75" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="V43" s="142" t="s">
         <v>244</v>
@@ -35215,7 +35215,7 @@
         <v>100</v>
       </c>
       <c r="U57" s="60" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="V57" s="137" t="s">
         <v>244</v>
@@ -35643,7 +35643,7 @@
         <v>100</v>
       </c>
       <c r="U61" s="60" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="V61" s="137" t="s">
         <v>244</v>
@@ -35865,7 +35865,7 @@
         <v>100</v>
       </c>
       <c r="U63" s="60" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="V63" s="60" t="s">
         <v>455</v>
@@ -35976,7 +35976,7 @@
         <v>100</v>
       </c>
       <c r="U64" s="60" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="V64" s="60" t="s">
         <v>455</v>
@@ -37209,7 +37209,7 @@
         <v>100</v>
       </c>
       <c r="U75" s="60" t="s">
-        <v>811</v>
+        <v>823</v>
       </c>
       <c r="V75" s="60" t="s">
         <v>500</v>
@@ -37320,7 +37320,7 @@
         <v>100</v>
       </c>
       <c r="U76" s="60" t="s">
-        <v>811</v>
+        <v>823</v>
       </c>
       <c r="V76" s="60" t="s">
         <v>500</v>

--- a/TABLERO_PA_C.xlsx
+++ b/TABLERO_PA_C.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e2a95cfba4fb0187/Escritorio/Tableros de Control/2. Contraloría/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="501" documentId="13_ncr:1_{5037B3AD-B0A2-4521-8F49-D3B2F1605E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A526515-513D-45E4-AB52-F132E910C74D}"/>
+  <xr:revisionPtr revIDLastSave="504" documentId="13_ncr:1_{5037B3AD-B0A2-4521-8F49-D3B2F1605E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4562E260-FA7B-4D19-9AF9-18F4BA06ED79}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="10" xr2:uid="{E38B2051-8614-49B4-943E-B3707D980583}"/>
   </bookViews>
@@ -2725,9 +2725,6 @@
 DIRECCIÓN DE RECURSOS FÍSICOS Y NEGOCIOS</t>
   </si>
   <si>
-    <t>DIRECCIÓN DE RECURSOS FÍSICOS Y NEGOCIOS/ SUBGERENCIAJ URÍDICA</t>
-  </si>
-  <si>
     <t>DIRECCIÓN DE GESTIÓN FINANCIERA/ SUBGERENCIAJURÍDICA</t>
   </si>
   <si>
@@ -2768,6 +2765,9 @@
   </si>
   <si>
     <t>SUBGERENCIA DE PLANEACIÓN Y PROYECTOS/ DIRECCIÓN DE GESTIÓN HUMANA</t>
+  </si>
+  <si>
+    <t>DIRECCIÓN DE RECURSOS FÍSICOS Y NEGOCIOS/ SUBGERENCIA JURÍDICA</t>
   </si>
 </sst>
 </file>
@@ -5458,21 +5458,6 @@
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="3" tint="0.499984740745262"/>
@@ -5579,6 +5564,21 @@
     </dxf>
     <dxf>
       <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
@@ -20576,129 +20576,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B6C7AB91-8822-4E2E-BE9B-A9578BEEAA20}" name="TablaDinámica3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:G7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="19">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-    <i i="2">
-      <x v="2"/>
-    </i>
-    <i i="3">
-      <x v="3"/>
-    </i>
-    <i i="4">
-      <x v="4"/>
-    </i>
-    <i i="5">
-      <x v="5"/>
-    </i>
-  </colItems>
-  <dataFields count="6">
-    <dataField name="Cuenta de No. Hallazgo" fld="2" subtotal="count" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Total Planes de acción" fld="5" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Abiertos" fld="6" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Vencidos" fld="7" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Finalizados" fld="8" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Auditoría" fld="1" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="5">
-    <format dxfId="240">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="239">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="238">
-      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0"/>
-    </format>
-    <format dxfId="237">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="236">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="4">
-            <x v="0"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5E7F1577-F431-4B0C-B786-3FF0F4829E0F}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A9:E35" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
@@ -20892,6 +20769,255 @@
     <dataField name="Suma de Finalizados" fld="8" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="20">
+    <format dxfId="255">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="254">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="253">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0"/>
+    </format>
+    <format dxfId="252">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="251">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="250">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="249">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="248">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="247">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="14"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="246">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="19"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="245">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="20"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="244">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="23"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="243">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="25"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="242">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="42"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="241">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="43"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="240">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="44"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="239">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="46"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="238">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="47"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="237">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="50"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="236">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="12"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B6C7AB91-8822-4E2E-BE9B-A9578BEEAA20}" name="TablaDinámica3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:G7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="19">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+    <i i="3">
+      <x v="3"/>
+    </i>
+    <i i="4">
+      <x v="4"/>
+    </i>
+    <i i="5">
+      <x v="5"/>
+    </i>
+  </colItems>
+  <dataFields count="6">
+    <dataField name="Cuenta de No. Hallazgo" fld="2" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Total Planes de acción" fld="5" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Abiertos" fld="6" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Vencidos" fld="7" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Finalizados" fld="8" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Auditoría" fld="1" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="5">
     <format dxfId="260">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
@@ -20905,139 +21031,13 @@
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
     <format dxfId="256">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="3" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="255">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="254">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="253">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="252">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="14"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="251">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="19"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="250">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="20"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="249">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="23"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="248">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="25"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="247">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="42"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="246">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="43"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="245">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="44"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="244">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="46"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="243">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="47"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="242">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="50"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="241">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="12"/>
+          <reference field="4294967294" count="4">
+            <x v="0"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
           </reference>
         </references>
       </pivotArea>
@@ -27862,6 +27862,255 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A9C7B425-127F-4B5F-B2E3-C2AB4F050E7C}" name="TablaDinámica3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A12:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="19">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Suma de Total Planes de acción" fld="5" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="1">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="0">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{53017CE7-FCFE-4C73-9C32-3A18A27FC23C}" name="TablaDinámica7" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+  <location ref="F13:G16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="19">
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="54">
+        <item m="1" x="25"/>
+        <item m="1" x="26"/>
+        <item m="1" x="31"/>
+        <item m="1" x="28"/>
+        <item m="1" x="36"/>
+        <item m="1" x="42"/>
+        <item m="1" x="27"/>
+        <item m="1" x="29"/>
+        <item m="1" x="38"/>
+        <item m="1" x="43"/>
+        <item m="1" x="41"/>
+        <item m="1" x="34"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="11"/>
+        <item x="16"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="12"/>
+        <item x="17"/>
+        <item x="15"/>
+        <item x="9"/>
+        <item m="1" x="48"/>
+        <item x="21"/>
+        <item m="1" x="46"/>
+        <item m="1" x="52"/>
+        <item m="1" x="49"/>
+        <item m="1" x="50"/>
+        <item m="1" x="35"/>
+        <item m="1" x="32"/>
+        <item m="1" x="47"/>
+        <item m="1" x="39"/>
+        <item m="1" x="40"/>
+        <item m="1" x="45"/>
+        <item m="1" x="51"/>
+        <item m="1" x="37"/>
+        <item m="1" x="33"/>
+        <item m="1" x="30"/>
+        <item m="1" x="44"/>
+        <item x="10"/>
+        <item x="7"/>
+        <item x="13"/>
+        <item x="20"/>
+        <item x="14"/>
+        <item x="24"/>
+        <item x="19"/>
+        <item x="8"/>
+        <item x="5"/>
+        <item x="18"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="-2"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="3">
+    <dataField name="Suma de Abiertos" fld="6" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Vencidos" fld="7" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Finalizados" fld="8" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="5">
+    <chartFormat chart="4" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DD0BBB6E-FA08-4903-950F-5C10965A7D8D}" name="TablaDinámica6" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A26:B31" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
@@ -27986,10 +28235,10 @@
     <dataField name="Suma de Finalizados" fld="8" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="1">
+    <format dxfId="3">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="0">
+    <format dxfId="2">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
   </formats>
@@ -28005,7 +28254,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3B3AE9AA-616F-416E-8D70-C9530CA01C24}" name="TablaDinámica4" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A19:B23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
@@ -28056,262 +28305,13 @@
     <dataField name="Suma de Alerta 30" fld="11" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="3">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="2">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A9C7B425-127F-4B5F-B2E3-C2AB4F050E7C}" name="TablaDinámica3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A12:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="19">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Suma de Total Planes de acción" fld="5" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="2">
     <format dxfId="5">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
     <format dxfId="4">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
   </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{53017CE7-FCFE-4C73-9C32-3A18A27FC23C}" name="TablaDinámica7" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
-  <location ref="F13:G16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="19">
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="54">
-        <item m="1" x="25"/>
-        <item m="1" x="26"/>
-        <item m="1" x="31"/>
-        <item m="1" x="28"/>
-        <item m="1" x="36"/>
-        <item m="1" x="42"/>
-        <item m="1" x="27"/>
-        <item m="1" x="29"/>
-        <item m="1" x="38"/>
-        <item m="1" x="43"/>
-        <item m="1" x="41"/>
-        <item m="1" x="34"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item x="11"/>
-        <item x="16"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="12"/>
-        <item x="17"/>
-        <item x="15"/>
-        <item x="9"/>
-        <item m="1" x="48"/>
-        <item x="21"/>
-        <item m="1" x="46"/>
-        <item m="1" x="52"/>
-        <item m="1" x="49"/>
-        <item m="1" x="50"/>
-        <item m="1" x="35"/>
-        <item m="1" x="32"/>
-        <item m="1" x="47"/>
-        <item m="1" x="39"/>
-        <item m="1" x="40"/>
-        <item m="1" x="45"/>
-        <item m="1" x="51"/>
-        <item m="1" x="37"/>
-        <item m="1" x="33"/>
-        <item m="1" x="30"/>
-        <item m="1" x="44"/>
-        <item x="10"/>
-        <item x="7"/>
-        <item x="13"/>
-        <item x="20"/>
-        <item x="14"/>
-        <item x="24"/>
-        <item x="19"/>
-        <item x="8"/>
-        <item x="5"/>
-        <item x="18"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="-2"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-    <i i="2">
-      <x v="2"/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="3">
-    <dataField name="Suma de Abiertos" fld="6" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Vencidos" fld="7" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Finalizados" fld="8" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="5">
-    <chartFormat chart="4" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="3">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="4">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="5">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -28578,7 +28578,15 @@
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CEA19F0D-D53E-4776-BB60-8DAF8AF7C40F}" name="Tabla2" displayName="Tabla2" ref="A1:AJ85" totalsRowShown="0" headerRowDxfId="299" dataDxfId="298" tableBorderDxfId="297">
-  <autoFilter ref="A1:AJ85" xr:uid="{CEA19F0D-D53E-4776-BB60-8DAF8AF7C40F}"/>
+  <autoFilter ref="A1:AJ85" xr:uid="{CEA19F0D-D53E-4776-BB60-8DAF8AF7C40F}">
+    <filterColumn colId="20">
+      <filters>
+        <filter val="DIRECCIÓN DE RECURSOS FÍSICOS Y NEGOCIOS/ SUBGERENCIAJ URÍDICA"/>
+        <filter val="SUBGERENCIA JURÍDICA"/>
+        <filter val="SUBGERENCIA JURÍDICA/_x000a_DIRECCIÓN DE GESTIÓN HUMANA"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="36">
     <tableColumn id="1" xr3:uid="{7A8D3A5E-E004-426E-B403-310EC9C105F1}" name="No." dataDxfId="296"/>
     <tableColumn id="2" xr3:uid="{657020D6-E9B2-4900-BBA6-15C5F0ADC46D}" name="FECHA REPORTE DE LA INFORMACIÓN" dataDxfId="295"/>
@@ -29250,7 +29258,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="2" spans="1:36" ht="79.8">
+    <row r="2" spans="1:36" ht="79.8" hidden="1">
       <c r="A2" s="59">
         <v>117</v>
       </c>
@@ -29355,7 +29363,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="3" spans="1:36" ht="125.4">
+    <row r="3" spans="1:36" ht="125.4" hidden="1">
       <c r="A3" s="59">
         <v>118</v>
       </c>
@@ -29464,7 +29472,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="4" spans="1:36" ht="125.4">
+    <row r="4" spans="1:36" ht="125.4" hidden="1">
       <c r="A4" s="59">
         <v>123</v>
       </c>
@@ -29573,7 +29581,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:36" ht="125.4">
+    <row r="5" spans="1:36" ht="125.4" hidden="1">
       <c r="A5" s="59">
         <v>124</v>
       </c>
@@ -29680,7 +29688,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:36" ht="136.80000000000001">
+    <row r="6" spans="1:36" ht="136.80000000000001" hidden="1">
       <c r="A6" s="59">
         <v>189</v>
       </c>
@@ -29789,7 +29797,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="7" spans="1:36" ht="136.80000000000001">
+    <row r="7" spans="1:36" ht="136.80000000000001" hidden="1">
       <c r="A7" s="59">
         <v>190</v>
       </c>
@@ -29898,7 +29906,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="8" spans="1:36" ht="136.80000000000001">
+    <row r="8" spans="1:36" ht="136.80000000000001" hidden="1">
       <c r="A8" s="59">
         <v>191</v>
       </c>
@@ -30063,7 +30071,7 @@
         <v>100</v>
       </c>
       <c r="U9" s="75" t="s">
-        <v>812</v>
+        <v>823</v>
       </c>
       <c r="V9" s="142" t="s">
         <v>38</v>
@@ -30116,7 +30124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:36" ht="171">
+    <row r="10" spans="1:36" ht="171" hidden="1">
       <c r="A10" s="59">
         <v>196</v>
       </c>
@@ -30225,7 +30233,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="11" spans="1:36" ht="171">
+    <row r="11" spans="1:36" ht="171" hidden="1">
       <c r="A11" s="59">
         <v>197</v>
       </c>
@@ -30435,7 +30443,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="13" spans="1:36" ht="91.2">
+    <row r="13" spans="1:36" ht="91.2" hidden="1">
       <c r="A13" s="59">
         <v>199</v>
       </c>
@@ -30544,7 +30552,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="14" spans="1:36" ht="125.4">
+    <row r="14" spans="1:36" ht="125.4" hidden="1">
       <c r="A14" s="59">
         <v>200</v>
       </c>
@@ -30653,7 +30661,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="15" spans="1:36" ht="159.6">
+    <row r="15" spans="1:36" ht="159.6" hidden="1">
       <c r="A15" s="59">
         <v>213</v>
       </c>
@@ -30867,7 +30875,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="17" spans="1:36" ht="182.4">
+    <row r="17" spans="1:36" ht="182.4" hidden="1">
       <c r="A17" s="59">
         <v>215</v>
       </c>
@@ -30923,7 +30931,7 @@
         <v>100</v>
       </c>
       <c r="U17" s="60" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="V17" s="137" t="s">
         <v>38</v>
@@ -30976,7 +30984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:36" ht="68.400000000000006">
+    <row r="18" spans="1:36" ht="68.400000000000006" hidden="1">
       <c r="A18" s="59">
         <v>221</v>
       </c>
@@ -31085,7 +31093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:36" ht="114">
+    <row r="19" spans="1:36" ht="114" hidden="1">
       <c r="A19" s="59">
         <v>222</v>
       </c>
@@ -31194,7 +31202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:36" ht="114">
+    <row r="20" spans="1:36" ht="114" hidden="1">
       <c r="A20" s="59">
         <v>223</v>
       </c>
@@ -31303,7 +31311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:36" ht="91.2">
+    <row r="21" spans="1:36" ht="91.2" hidden="1">
       <c r="A21" s="141">
         <v>230</v>
       </c>
@@ -31359,7 +31367,7 @@
         <v>100</v>
       </c>
       <c r="U21" s="75" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="V21" s="142" t="s">
         <v>38</v>
@@ -31408,7 +31416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:36" ht="91.2">
+    <row r="22" spans="1:36" ht="91.2" hidden="1">
       <c r="A22" s="141">
         <v>232</v>
       </c>
@@ -31464,7 +31472,7 @@
         <v>100</v>
       </c>
       <c r="U22" s="75" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="V22" s="142" t="s">
         <v>38</v>
@@ -31513,7 +31521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:36" ht="91.2">
+    <row r="23" spans="1:36" ht="91.2" hidden="1">
       <c r="A23" s="141">
         <v>233</v>
       </c>
@@ -31569,7 +31577,7 @@
         <v>100</v>
       </c>
       <c r="U23" s="75" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="V23" s="142" t="s">
         <v>38</v>
@@ -31618,7 +31626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:36" ht="148.19999999999999">
+    <row r="24" spans="1:36" ht="148.19999999999999" hidden="1">
       <c r="A24" s="141">
         <v>244</v>
       </c>
@@ -31727,7 +31735,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="25" spans="1:36" ht="193.8">
+    <row r="25" spans="1:36" ht="193.8" hidden="1">
       <c r="A25" s="59">
         <v>245</v>
       </c>
@@ -31783,7 +31791,7 @@
         <v>100</v>
       </c>
       <c r="U25" s="60" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="V25" s="137" t="s">
         <v>38</v>
@@ -31836,7 +31844,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="26" spans="1:36" ht="136.80000000000001">
+    <row r="26" spans="1:36" ht="136.80000000000001" hidden="1">
       <c r="A26" s="59">
         <v>246</v>
       </c>
@@ -31941,7 +31949,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="27" spans="1:36" ht="193.8">
+    <row r="27" spans="1:36" ht="193.8" hidden="1">
       <c r="A27" s="59">
         <v>247</v>
       </c>
@@ -32046,7 +32054,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="28" spans="1:36" ht="91.2">
+    <row r="28" spans="1:36" ht="91.2" hidden="1">
       <c r="A28" s="59">
         <v>255</v>
       </c>
@@ -32256,7 +32264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:36" ht="91.2">
+    <row r="30" spans="1:36" ht="91.2" hidden="1">
       <c r="A30" s="151">
         <v>259</v>
       </c>
@@ -32474,7 +32482,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="32" spans="1:36" ht="136.80000000000001">
+    <row r="32" spans="1:36" ht="136.80000000000001" hidden="1">
       <c r="A32" s="141">
         <v>261</v>
       </c>
@@ -32579,7 +32587,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="33" spans="1:36" ht="136.80000000000001">
+    <row r="33" spans="1:36" ht="136.80000000000001" hidden="1">
       <c r="A33" s="141">
         <v>262</v>
       </c>
@@ -32688,7 +32696,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="34" spans="1:36" ht="136.80000000000001">
+    <row r="34" spans="1:36" ht="136.80000000000001" hidden="1">
       <c r="A34" s="59">
         <v>263</v>
       </c>
@@ -32795,7 +32803,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="35" spans="1:36" ht="148.19999999999999">
+    <row r="35" spans="1:36" ht="148.19999999999999" hidden="1">
       <c r="A35" s="59">
         <v>281</v>
       </c>
@@ -32904,7 +32912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:36" ht="136.80000000000001">
+    <row r="36" spans="1:36" ht="136.80000000000001" hidden="1">
       <c r="A36" s="59">
         <v>181</v>
       </c>
@@ -33013,7 +33021,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="37" spans="1:36" ht="91.2">
+    <row r="37" spans="1:36" ht="91.2" hidden="1">
       <c r="A37" s="59">
         <v>182</v>
       </c>
@@ -33069,7 +33077,7 @@
         <v>100</v>
       </c>
       <c r="U37" s="60" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="V37" s="137" t="s">
         <v>244</v>
@@ -33120,7 +33128,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="38" spans="1:36" ht="125.4">
+    <row r="38" spans="1:36" ht="125.4" hidden="1">
       <c r="A38" s="59">
         <v>183</v>
       </c>
@@ -33227,7 +33235,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="39" spans="1:36" ht="148.19999999999999">
+    <row r="39" spans="1:36" ht="148.19999999999999" hidden="1">
       <c r="A39" s="161">
         <v>189</v>
       </c>
@@ -33283,7 +33291,7 @@
         <v>100</v>
       </c>
       <c r="U39" s="75" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="V39" s="142" t="s">
         <v>244</v>
@@ -33334,7 +33342,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="40" spans="1:36" ht="159.6">
+    <row r="40" spans="1:36" ht="159.6" hidden="1">
       <c r="A40" s="59">
         <v>190</v>
       </c>
@@ -33441,7 +33449,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="41" spans="1:36" ht="102.6">
+    <row r="41" spans="1:36" ht="102.6" hidden="1">
       <c r="A41" s="78">
         <v>191</v>
       </c>
@@ -33550,7 +33558,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="42" spans="1:36" ht="125.4">
+    <row r="42" spans="1:36" ht="125.4" hidden="1">
       <c r="A42" s="59">
         <v>194</v>
       </c>
@@ -33659,7 +33667,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="43" spans="1:36" ht="148.19999999999999">
+    <row r="43" spans="1:36" ht="148.19999999999999" hidden="1">
       <c r="A43" s="161">
         <v>195</v>
       </c>
@@ -33715,7 +33723,7 @@
         <v>100</v>
       </c>
       <c r="U43" s="75" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="V43" s="142" t="s">
         <v>244</v>
@@ -33766,7 +33774,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="44" spans="1:36" ht="216.6">
+    <row r="44" spans="1:36" ht="216.6" hidden="1">
       <c r="A44" s="59">
         <v>214</v>
       </c>
@@ -33873,7 +33881,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="45" spans="1:36" ht="125.4">
+    <row r="45" spans="1:36" ht="125.4" hidden="1">
       <c r="A45" s="83">
         <v>215</v>
       </c>
@@ -33980,7 +33988,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="46" spans="1:36" ht="102.6">
+    <row r="46" spans="1:36" ht="102.6" hidden="1">
       <c r="A46" s="78">
         <v>216</v>
       </c>
@@ -34087,7 +34095,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="47" spans="1:36" ht="182.4">
+    <row r="47" spans="1:36" ht="182.4" hidden="1">
       <c r="A47" s="78">
         <v>217</v>
       </c>
@@ -34194,7 +34202,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="48" spans="1:36" ht="131.4" customHeight="1">
+    <row r="48" spans="1:36" ht="131.4" hidden="1" customHeight="1">
       <c r="A48" s="78">
         <v>218</v>
       </c>
@@ -34303,7 +34311,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="49" spans="1:36" ht="171">
+    <row r="49" spans="1:36" ht="171" hidden="1">
       <c r="A49" s="59">
         <v>219</v>
       </c>
@@ -34410,7 +34418,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="50" spans="1:36" ht="205.2">
+    <row r="50" spans="1:36" ht="205.2" hidden="1">
       <c r="A50" s="59">
         <v>220</v>
       </c>
@@ -34517,7 +34525,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="51" spans="1:36" ht="171">
+    <row r="51" spans="1:36" ht="171" hidden="1">
       <c r="A51" s="59">
         <v>223</v>
       </c>
@@ -34624,7 +34632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:36" ht="125.4">
+    <row r="52" spans="1:36" ht="125.4" hidden="1">
       <c r="A52" s="59">
         <v>226</v>
       </c>
@@ -34731,7 +34739,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="53" spans="1:36" ht="125.4">
+    <row r="53" spans="1:36" ht="125.4" hidden="1">
       <c r="A53" s="59">
         <v>227</v>
       </c>
@@ -34838,7 +34846,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="54" spans="1:36" ht="193.8">
+    <row r="54" spans="1:36" ht="193.8" hidden="1">
       <c r="A54" s="59">
         <v>228</v>
       </c>
@@ -34945,7 +34953,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="55" spans="1:36" ht="125.4">
+    <row r="55" spans="1:36" ht="125.4" hidden="1">
       <c r="A55" s="78">
         <v>229</v>
       </c>
@@ -35052,7 +35060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:36" ht="136.80000000000001">
+    <row r="56" spans="1:36" ht="136.80000000000001" hidden="1">
       <c r="A56" s="78">
         <v>230</v>
       </c>
@@ -35215,7 +35223,7 @@
         <v>100</v>
       </c>
       <c r="U57" s="60" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="V57" s="137" t="s">
         <v>244</v>
@@ -35266,7 +35274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:36" ht="171">
+    <row r="58" spans="1:36" ht="171" hidden="1">
       <c r="A58" s="78">
         <v>240</v>
       </c>
@@ -35373,7 +35381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:36" ht="205.2">
+    <row r="59" spans="1:36" ht="205.2" hidden="1">
       <c r="A59" s="59">
         <v>245</v>
       </c>
@@ -35480,7 +35488,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="60" spans="1:36" ht="68.400000000000006">
+    <row r="60" spans="1:36" ht="68.400000000000006" hidden="1">
       <c r="A60" s="78">
         <v>246</v>
       </c>
@@ -35587,7 +35595,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="61" spans="1:36" ht="148.19999999999999">
+    <row r="61" spans="1:36" ht="148.19999999999999" hidden="1">
       <c r="A61" s="78">
         <v>247</v>
       </c>
@@ -35643,7 +35651,7 @@
         <v>100</v>
       </c>
       <c r="U61" s="60" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="V61" s="137" t="s">
         <v>244</v>
@@ -35694,7 +35702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:36" ht="228">
+    <row r="62" spans="1:36" ht="228" hidden="1">
       <c r="A62" s="59">
         <v>120</v>
       </c>
@@ -35805,7 +35813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:36" ht="262.2">
+    <row r="63" spans="1:36" ht="262.2" hidden="1">
       <c r="A63" s="78">
         <v>123</v>
       </c>
@@ -35865,7 +35873,7 @@
         <v>100</v>
       </c>
       <c r="U63" s="60" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="V63" s="60" t="s">
         <v>455</v>
@@ -35916,7 +35924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:36" ht="273.60000000000002">
+    <row r="64" spans="1:36" ht="273.60000000000002" hidden="1">
       <c r="A64" s="59">
         <v>125</v>
       </c>
@@ -35976,7 +35984,7 @@
         <v>100</v>
       </c>
       <c r="U64" s="60" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="V64" s="60" t="s">
         <v>455</v>
@@ -36027,7 +36035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:36" ht="171">
+    <row r="65" spans="1:36" ht="171" hidden="1">
       <c r="A65" s="59">
         <v>184</v>
       </c>
@@ -36140,7 +36148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:36" ht="205.2">
+    <row r="66" spans="1:36" ht="205.2" hidden="1">
       <c r="A66" s="59">
         <v>186</v>
       </c>
@@ -36253,7 +36261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:36" ht="171">
+    <row r="67" spans="1:36" ht="171" hidden="1">
       <c r="A67" s="59">
         <v>187</v>
       </c>
@@ -36366,7 +36374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:36" ht="171">
+    <row r="68" spans="1:36" ht="171" hidden="1">
       <c r="A68" s="59">
         <v>188</v>
       </c>
@@ -36479,7 +36487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:36" ht="193.8">
+    <row r="69" spans="1:36" ht="193.8" hidden="1">
       <c r="A69" s="59">
         <v>213</v>
       </c>
@@ -36590,7 +36598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:36" ht="228">
+    <row r="70" spans="1:36" ht="228" hidden="1">
       <c r="A70" s="59">
         <v>221</v>
       </c>
@@ -36701,7 +36709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:36" ht="239.4">
+    <row r="71" spans="1:36" ht="239.4" hidden="1">
       <c r="A71" s="59">
         <v>222</v>
       </c>
@@ -36812,7 +36820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:36" ht="228">
+    <row r="72" spans="1:36" ht="228" hidden="1">
       <c r="A72" s="78">
         <v>224</v>
       </c>
@@ -36923,7 +36931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:36" ht="239.4">
+    <row r="73" spans="1:36" ht="239.4" hidden="1">
       <c r="A73" s="59">
         <v>225</v>
       </c>
@@ -37036,7 +37044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:36" ht="193.8">
+    <row r="74" spans="1:36" ht="193.8" hidden="1">
       <c r="A74" s="59">
         <v>232</v>
       </c>
@@ -37149,7 +37157,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:36" ht="182.4">
+    <row r="75" spans="1:36" ht="182.4" hidden="1">
       <c r="A75" s="59">
         <v>233</v>
       </c>
@@ -37209,7 +37217,7 @@
         <v>100</v>
       </c>
       <c r="U75" s="60" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="V75" s="60" t="s">
         <v>500</v>
@@ -37260,7 +37268,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="76" spans="1:36" ht="262.2">
+    <row r="76" spans="1:36" ht="262.2" hidden="1">
       <c r="A76" s="59">
         <v>234</v>
       </c>
@@ -37320,7 +37328,7 @@
         <v>100</v>
       </c>
       <c r="U76" s="60" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="V76" s="60" t="s">
         <v>500</v>
@@ -37371,7 +37379,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="77" spans="1:36" ht="205.2">
+    <row r="77" spans="1:36" ht="205.2" hidden="1">
       <c r="A77" s="59">
         <v>235</v>
       </c>
@@ -37484,7 +37492,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="78" spans="1:36" ht="262.2">
+    <row r="78" spans="1:36" ht="262.2" hidden="1">
       <c r="A78" s="59">
         <v>236</v>
       </c>
@@ -37597,7 +37605,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="79" spans="1:36" ht="159.6">
+    <row r="79" spans="1:36" ht="159.6" hidden="1">
       <c r="A79" s="59">
         <v>237</v>
       </c>
@@ -37821,7 +37829,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="81" spans="1:36" ht="250.8">
+    <row r="81" spans="1:36" ht="250.8" hidden="1">
       <c r="A81" s="59">
         <v>239</v>
       </c>

--- a/TABLERO_PA_C.xlsx
+++ b/TABLERO_PA_C.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e2a95cfba4fb0187/Escritorio/Tableros de Control/2. Contraloría/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="504" documentId="13_ncr:1_{5037B3AD-B0A2-4521-8F49-D3B2F1605E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4562E260-FA7B-4D19-9AF9-18F4BA06ED79}"/>
+  <xr:revisionPtr revIDLastSave="531" documentId="13_ncr:1_{5037B3AD-B0A2-4521-8F49-D3B2F1605E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB263BA1-7E00-42DC-B7D8-8FC96CE532F1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="10" xr2:uid="{E38B2051-8614-49B4-943E-B3707D980583}"/>
   </bookViews>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2577" uniqueCount="824">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2576" uniqueCount="823">
   <si>
     <t>No.</t>
   </si>
@@ -2069,13 +2069,7 @@
     <t>Cuenta de ESTADO</t>
   </si>
   <si>
-    <t>Se adjuntan los soportes que sustentan el registro contable del lote soacha</t>
-  </si>
-  <si>
     <t>Fecha cierre x Auditoría</t>
-  </si>
-  <si>
-    <t>Se adjunta trazabilidad lote soacha</t>
   </si>
   <si>
     <t>Se actualzian los Procedimeintos MANTENIMIENTO PREVENTIVO CORRECTIVO FTI-PR08, Y DEL PLAN DE MANTENIMENTO CORRECTIVO Y PREVENTIVO FTI-PL01 DE LA TTSA, referncuiando la infraestructura del control de tiempos de permanencia</t>
@@ -2448,9 +2442,6 @@
     <t>Se implementa el Procedimiento Trámite de Incapacidades CÓDIGO: GTS-PR22, el cual establece los lineamientos para el trámite de reconocimiento, liquidación, pago, cobro y conciliación de las incapacidades y licencias del personal de la Terminal de Transporte S.A.</t>
   </si>
   <si>
-    <t xml:space="preserve">Se adjunta el informe </t>
-  </si>
-  <si>
     <t>Ene</t>
   </si>
   <si>
@@ -2682,9 +2673,6 @@
     <t>0.5</t>
   </si>
   <si>
-    <t>Se implementa el Manual Gestión Inmobiliaria Código: GIM-MN01, con el fin de proporcionar al personal involucrado en el proces, una guía que regule su accionar en las actividades administrativas y de control inherentes a los bienes inmuebles de la TTSA.</t>
-  </si>
-  <si>
     <t>Se verifica la efectividad de la acción mediante la Resolución No. 0090 del 25/03/2026 de la Secretaría de Hacienda de Soacha (saneamiento de intereses moratorios) y el Recibo de Impuesto Predial No. 26982690 (Vigencias 2025-2026). Los soportes acreditan la depuración de la cartera y la actualización oficial del área del predio</t>
   </si>
   <si>
@@ -2768,6 +2756,15 @@
   </si>
   <si>
     <t>DIRECCIÓN DE RECURSOS FÍSICOS Y NEGOCIOS/ SUBGERENCIA JURÍDICA</t>
+  </si>
+  <si>
+    <t>Se implementa el Manual Gestión Inmobiliaria Código: GIM-MN01, con el fin de proporcionar al personal involucrado en el proceso, una guía que regule su accionar en las actividades administrativas y de control inherentes a los bienes inmuebles de la TTSA.</t>
+  </si>
+  <si>
+    <t>Se elaboró un informe de ajuste contable y cumplimiento del activo denominado "Lote Soacha"</t>
+  </si>
+  <si>
+    <t>Se presenta el informe final del supervisor</t>
   </si>
 </sst>
 </file>
@@ -3287,7 +3284,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="235">
+  <cellXfs count="242">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3937,6 +3934,25 @@
     <xf numFmtId="0" fontId="17" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="19" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -14655,7 +14671,9 @@
           <cell r="G105" t="str">
             <v>SUB GERENCIA CORPORATIVA</v>
           </cell>
-          <cell r="S105"/>
+          <cell r="S105">
+            <v>46304</v>
+          </cell>
         </row>
         <row r="106">
           <cell r="A106" t="str">
@@ -14693,7 +14711,9 @@
           <cell r="G108" t="str">
             <v>SUB GERENCIA CORPORATIVA</v>
           </cell>
-          <cell r="S108"/>
+          <cell r="S108">
+            <v>46304</v>
+          </cell>
         </row>
         <row r="109">
           <cell r="A109" t="str">
@@ -14719,7 +14739,9 @@
           <cell r="G110" t="str">
             <v>SUB GERENCIA DE PLANEACIÓN Y PROYECTOS</v>
           </cell>
-          <cell r="S110"/>
+          <cell r="S110">
+            <v>46302</v>
+          </cell>
         </row>
         <row r="111">
           <cell r="A111" t="str">
@@ -14731,7 +14753,9 @@
           <cell r="G111" t="str">
             <v>SUB GERENCIA DE PLANEACIÓN Y PROYECTOS</v>
           </cell>
-          <cell r="S111"/>
+          <cell r="S111">
+            <v>46302</v>
+          </cell>
         </row>
         <row r="112">
           <cell r="A112" t="str">
@@ -14743,7 +14767,9 @@
           <cell r="G112" t="str">
             <v>SUB GERENCIA DE PLANEACIÓN Y PROYECTOS</v>
           </cell>
-          <cell r="S112"/>
+          <cell r="S112">
+            <v>46302</v>
+          </cell>
         </row>
         <row r="113">
           <cell r="A113" t="str">
@@ -14755,7 +14781,9 @@
           <cell r="G113" t="str">
             <v>SUB GERENCIA DE PLANEACIÓN Y PROYECTOS</v>
           </cell>
-          <cell r="S113"/>
+          <cell r="S113">
+            <v>46302</v>
+          </cell>
         </row>
         <row r="114">
           <cell r="A114" t="str">
@@ -14767,7 +14795,9 @@
           <cell r="G114" t="str">
             <v>SUB GERENCIA DE PLANEACIÓN Y PROYECTOS</v>
           </cell>
-          <cell r="S114"/>
+          <cell r="S114">
+            <v>46302</v>
+          </cell>
         </row>
         <row r="115">
           <cell r="A115" t="str">
@@ -14779,7 +14809,9 @@
           <cell r="G115" t="str">
             <v>SUB GERENCIA DE PLANEACIÓN Y PROYECTOS</v>
           </cell>
-          <cell r="S115"/>
+          <cell r="S115">
+            <v>46302</v>
+          </cell>
         </row>
         <row r="116">
           <cell r="A116" t="str">
@@ -28578,15 +28610,7 @@
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CEA19F0D-D53E-4776-BB60-8DAF8AF7C40F}" name="Tabla2" displayName="Tabla2" ref="A1:AJ85" totalsRowShown="0" headerRowDxfId="299" dataDxfId="298" tableBorderDxfId="297">
-  <autoFilter ref="A1:AJ85" xr:uid="{CEA19F0D-D53E-4776-BB60-8DAF8AF7C40F}">
-    <filterColumn colId="20">
-      <filters>
-        <filter val="DIRECCIÓN DE RECURSOS FÍSICOS Y NEGOCIOS/ SUBGERENCIAJ URÍDICA"/>
-        <filter val="SUBGERENCIA JURÍDICA"/>
-        <filter val="SUBGERENCIA JURÍDICA/_x000a_DIRECCIÓN DE GESTIÓN HUMANA"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AJ85" xr:uid="{CEA19F0D-D53E-4776-BB60-8DAF8AF7C40F}"/>
   <tableColumns count="36">
     <tableColumn id="1" xr3:uid="{7A8D3A5E-E004-426E-B403-310EC9C105F1}" name="No." dataDxfId="296"/>
     <tableColumn id="2" xr3:uid="{657020D6-E9B2-4900-BBA6-15C5F0ADC46D}" name="FECHA REPORTE DE LA INFORMACIÓN" dataDxfId="295"/>
@@ -29219,7 +29243,7 @@
         <v>21</v>
       </c>
       <c r="X1" s="210" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="Y1" s="211" t="s">
         <v>22</v>
@@ -29252,13 +29276,13 @@
         <v>638</v>
       </c>
       <c r="AI1" s="213" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="AJ1" s="226" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="2" spans="1:36" ht="79.8" hidden="1">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="2" spans="1:36" ht="79.8">
       <c r="A2" s="59">
         <v>117</v>
       </c>
@@ -29314,7 +29338,7 @@
         <v>100</v>
       </c>
       <c r="U2" s="60" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="V2" s="138">
         <v>45957</v>
@@ -29363,7 +29387,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="3" spans="1:36" ht="125.4" hidden="1">
+    <row r="3" spans="1:36" ht="125.4">
       <c r="A3" s="59">
         <v>118</v>
       </c>
@@ -29419,7 +29443,7 @@
         <v>100</v>
       </c>
       <c r="U3" s="60" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="V3" s="138">
         <v>45957</v>
@@ -29434,7 +29458,7 @@
         <v>41</v>
       </c>
       <c r="Z3" s="126" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="AA3" s="134" t="s">
         <v>55</v>
@@ -29472,7 +29496,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="4" spans="1:36" ht="125.4" hidden="1">
+    <row r="4" spans="1:36" ht="125.4">
       <c r="A4" s="59">
         <v>123</v>
       </c>
@@ -29528,7 +29552,7 @@
         <v>100</v>
       </c>
       <c r="U4" s="60" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="V4" s="137" t="s">
         <v>38</v>
@@ -29581,7 +29605,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:36" ht="125.4" hidden="1">
+    <row r="5" spans="1:36" ht="125.4">
       <c r="A5" s="59">
         <v>124</v>
       </c>
@@ -29637,7 +29661,7 @@
         <v>100</v>
       </c>
       <c r="U5" s="60" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="V5" s="137" t="s">
         <v>38</v>
@@ -29688,7 +29712,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:36" ht="136.80000000000001" hidden="1">
+    <row r="6" spans="1:36" ht="136.80000000000001">
       <c r="A6" s="59">
         <v>189</v>
       </c>
@@ -29744,7 +29768,7 @@
         <v>100</v>
       </c>
       <c r="U6" s="60" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="V6" s="137" t="s">
         <v>38</v>
@@ -29759,7 +29783,7 @@
         <v>41</v>
       </c>
       <c r="Z6" s="129" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="AA6" s="64" t="s">
         <v>55</v>
@@ -29797,7 +29821,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="7" spans="1:36" ht="136.80000000000001" hidden="1">
+    <row r="7" spans="1:36" ht="136.80000000000001">
       <c r="A7" s="59">
         <v>190</v>
       </c>
@@ -29853,7 +29877,7 @@
         <v>100</v>
       </c>
       <c r="U7" s="60" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="V7" s="137" t="s">
         <v>38</v>
@@ -29906,7 +29930,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="8" spans="1:36" ht="136.80000000000001" hidden="1">
+    <row r="8" spans="1:36" ht="136.80000000000001">
       <c r="A8" s="59">
         <v>191</v>
       </c>
@@ -29962,7 +29986,7 @@
         <v>100</v>
       </c>
       <c r="U8" s="60" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="V8" s="137" t="s">
         <v>38</v>
@@ -30071,7 +30095,7 @@
         <v>100</v>
       </c>
       <c r="U9" s="75" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="V9" s="142" t="s">
         <v>38</v>
@@ -30086,7 +30110,7 @@
         <v>41</v>
       </c>
       <c r="Z9" s="144" t="s">
-        <v>798</v>
+        <v>820</v>
       </c>
       <c r="AA9" s="145" t="s">
         <v>55</v>
@@ -30124,7 +30148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:36" ht="171" hidden="1">
+    <row r="10" spans="1:36" ht="171">
       <c r="A10" s="59">
         <v>196</v>
       </c>
@@ -30180,7 +30204,7 @@
         <v>100</v>
       </c>
       <c r="U10" s="60" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="V10" s="137" t="s">
         <v>38</v>
@@ -30195,7 +30219,7 @@
         <v>41</v>
       </c>
       <c r="Z10" s="129" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="AA10" s="64" t="s">
         <v>55</v>
@@ -30233,108 +30257,108 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="11" spans="1:36" ht="171" hidden="1">
-      <c r="A11" s="59">
+    <row r="11" spans="1:36" s="235" customFormat="1" ht="171">
+      <c r="A11" s="229">
         <v>197</v>
       </c>
-      <c r="B11" s="60" t="s">
+      <c r="B11" s="74" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="60" t="s">
+      <c r="C11" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="60" t="s">
+      <c r="D11" s="74" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="60" t="s">
+      <c r="E11" s="74" t="s">
         <v>29</v>
       </c>
-      <c r="F11" s="60">
+      <c r="F11" s="74">
         <v>2025</v>
       </c>
-      <c r="G11" s="60">
+      <c r="G11" s="74">
         <v>90</v>
       </c>
-      <c r="H11" s="60" t="s">
+      <c r="H11" s="74" t="s">
         <v>88</v>
       </c>
-      <c r="I11" s="60">
+      <c r="I11" s="74">
         <v>2</v>
       </c>
-      <c r="J11" s="61" t="s">
+      <c r="J11" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="K11" s="62"/>
-      <c r="L11" s="60" t="s">
+      <c r="K11" s="77"/>
+      <c r="L11" s="74" t="s">
         <v>32</v>
       </c>
-      <c r="M11" s="60"/>
-      <c r="N11" s="60"/>
-      <c r="O11" s="60" t="s">
+      <c r="M11" s="74"/>
+      <c r="N11" s="74"/>
+      <c r="O11" s="74" t="s">
         <v>89</v>
       </c>
-      <c r="P11" s="60" t="s">
+      <c r="P11" s="74" t="s">
         <v>90</v>
       </c>
-      <c r="Q11" s="96" t="s">
+      <c r="Q11" s="74" t="s">
         <v>95</v>
       </c>
-      <c r="R11" s="60" t="s">
+      <c r="R11" s="74" t="s">
         <v>96</v>
       </c>
-      <c r="S11" s="60" t="s">
+      <c r="S11" s="74" t="s">
         <v>97</v>
       </c>
-      <c r="T11" s="60">
+      <c r="T11" s="74">
         <v>100</v>
       </c>
-      <c r="U11" s="60" t="s">
-        <v>800</v>
-      </c>
-      <c r="V11" s="137" t="s">
+      <c r="U11" s="74" t="s">
+        <v>796</v>
+      </c>
+      <c r="V11" s="217" t="s">
         <v>38</v>
       </c>
-      <c r="W11" s="137" t="s">
+      <c r="W11" s="217" t="s">
         <v>86</v>
       </c>
-      <c r="X11" s="60" t="s">
+      <c r="X11" s="74" t="s">
         <v>40</v>
       </c>
-      <c r="Y11" s="60" t="s">
+      <c r="Y11" s="74" t="s">
         <v>41</v>
       </c>
-      <c r="Z11" s="129"/>
-      <c r="AA11" s="64" t="s">
+      <c r="Z11" s="230"/>
+      <c r="AA11" s="134" t="s">
         <v>42</v>
       </c>
-      <c r="AB11" s="97" t="s">
+      <c r="AB11" s="231" t="s">
         <v>98</v>
       </c>
-      <c r="AC11" s="66">
+      <c r="AC11" s="232">
         <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AD11" s="67">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="233">
         <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
-      <c r="AE11" s="67">
+      <c r="AE11" s="233">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="AF11" s="67">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="233">
         <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
-      <c r="AG11" s="67">
+      <c r="AG11" s="233">
         <f t="shared" ca="1" si="4"/>
         <v>0</v>
       </c>
-      <c r="AH11" s="94" t="s">
+      <c r="AH11" s="234" t="s">
         <v>639</v>
       </c>
-      <c r="AI11" s="67"/>
-      <c r="AJ11" s="67">
+      <c r="AI11" s="233"/>
+      <c r="AJ11" s="233">
         <v>0.33</v>
       </c>
     </row>
@@ -30394,7 +30418,7 @@
         <v>100</v>
       </c>
       <c r="U12" s="60" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="V12" s="137" t="s">
         <v>38</v>
@@ -30417,7 +30441,7 @@
       </c>
       <c r="AC12" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AD12" s="67">
         <f t="shared" ca="1" si="1"/>
@@ -30425,7 +30449,7 @@
       </c>
       <c r="AE12" s="67">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF12" s="67">
         <f t="shared" ca="1" si="3"/>
@@ -30443,7 +30467,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="13" spans="1:36" ht="91.2" hidden="1">
+    <row r="13" spans="1:36" ht="91.2">
       <c r="A13" s="59">
         <v>199</v>
       </c>
@@ -30499,7 +30523,7 @@
         <v>100</v>
       </c>
       <c r="U13" s="60" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="V13" s="137" t="s">
         <v>38</v>
@@ -30514,7 +30538,7 @@
         <v>41</v>
       </c>
       <c r="Z13" s="129" t="s">
-        <v>655</v>
+        <v>821</v>
       </c>
       <c r="AA13" s="64" t="s">
         <v>55</v>
@@ -30552,7 +30576,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="14" spans="1:36" ht="125.4" hidden="1">
+    <row r="14" spans="1:36" ht="125.4">
       <c r="A14" s="59">
         <v>200</v>
       </c>
@@ -30608,7 +30632,7 @@
         <v>100</v>
       </c>
       <c r="U14" s="60" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="V14" s="137" t="s">
         <v>38</v>
@@ -30623,7 +30647,7 @@
         <v>41</v>
       </c>
       <c r="Z14" s="129" t="s">
-        <v>657</v>
+        <v>821</v>
       </c>
       <c r="AA14" s="64" t="s">
         <v>55</v>
@@ -30661,7 +30685,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="15" spans="1:36" ht="159.6" hidden="1">
+    <row r="15" spans="1:36" ht="159.6">
       <c r="A15" s="59">
         <v>213</v>
       </c>
@@ -30717,7 +30741,7 @@
         <v>100</v>
       </c>
       <c r="U15" s="60" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="V15" s="137" t="s">
         <v>38</v>
@@ -30732,7 +30756,7 @@
         <v>41</v>
       </c>
       <c r="Z15" s="129" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="AA15" s="64" t="s">
         <v>55</v>
@@ -30826,13 +30850,13 @@
         <v>100</v>
       </c>
       <c r="U16" s="60" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="V16" s="137" t="s">
         <v>38</v>
       </c>
-      <c r="W16" s="137" t="s">
-        <v>86</v>
+      <c r="W16" s="138">
+        <v>46308</v>
       </c>
       <c r="X16" s="60" t="s">
         <v>40</v>
@@ -30847,25 +30871,25 @@
       <c r="AB16" s="97" t="s">
         <v>126</v>
       </c>
-      <c r="AC16" s="66">
+      <c r="AC16" s="66" t="e">
         <f t="shared" ca="1" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="AD16" s="67">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AD16" s="67" t="e">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AE16" s="67">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AE16" s="67" t="e">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="AF16" s="67">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AF16" s="67" t="e">
         <f t="shared" ca="1" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AG16" s="67">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AG16" s="67" t="e">
         <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="AH16" s="94" t="s">
         <v>653</v>
@@ -30875,7 +30899,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="17" spans="1:36" ht="182.4" hidden="1">
+    <row r="17" spans="1:36" ht="182.4">
       <c r="A17" s="59">
         <v>215</v>
       </c>
@@ -30931,7 +30955,7 @@
         <v>100</v>
       </c>
       <c r="U17" s="60" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="V17" s="137" t="s">
         <v>38</v>
@@ -30946,7 +30970,7 @@
         <v>41</v>
       </c>
       <c r="Z17" s="129" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="AA17" s="134" t="s">
         <v>55</v>
@@ -30984,7 +31008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:36" ht="68.400000000000006" hidden="1">
+    <row r="18" spans="1:36" ht="68.400000000000006">
       <c r="A18" s="59">
         <v>221</v>
       </c>
@@ -31040,7 +31064,7 @@
         <v>100</v>
       </c>
       <c r="U18" s="60" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="V18" s="137" t="s">
         <v>38</v>
@@ -31055,7 +31079,7 @@
         <v>41</v>
       </c>
       <c r="Z18" s="129" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="AA18" s="64" t="s">
         <v>55</v>
@@ -31093,7 +31117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:36" ht="114" hidden="1">
+    <row r="19" spans="1:36" ht="114">
       <c r="A19" s="59">
         <v>222</v>
       </c>
@@ -31149,7 +31173,7 @@
         <v>100</v>
       </c>
       <c r="U19" s="60" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="V19" s="137" t="s">
         <v>38</v>
@@ -31164,12 +31188,12 @@
         <v>41</v>
       </c>
       <c r="Z19" s="129" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="AA19" s="64" t="s">
         <v>55</v>
       </c>
-      <c r="AB19" s="65" t="s">
+      <c r="AB19" s="97" t="s">
         <v>147</v>
       </c>
       <c r="AC19" s="66" t="str">
@@ -31202,7 +31226,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:36" ht="114" hidden="1">
+    <row r="20" spans="1:36" ht="114">
       <c r="A20" s="59">
         <v>223</v>
       </c>
@@ -31258,7 +31282,7 @@
         <v>100</v>
       </c>
       <c r="U20" s="60" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="V20" s="137" t="s">
         <v>38</v>
@@ -31273,7 +31297,7 @@
         <v>41</v>
       </c>
       <c r="Z20" s="129" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="AA20" s="64" t="s">
         <v>55</v>
@@ -31311,7 +31335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:36" ht="91.2" hidden="1">
+    <row r="21" spans="1:36" ht="91.2">
       <c r="A21" s="141">
         <v>230</v>
       </c>
@@ -31367,13 +31391,13 @@
         <v>100</v>
       </c>
       <c r="U21" s="75" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="V21" s="142" t="s">
         <v>38</v>
       </c>
       <c r="W21" s="143" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="X21" s="75" t="s">
         <v>40</v>
@@ -31416,7 +31440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:36" ht="91.2" hidden="1">
+    <row r="22" spans="1:36" ht="91.2">
       <c r="A22" s="141">
         <v>232</v>
       </c>
@@ -31472,7 +31496,7 @@
         <v>100</v>
       </c>
       <c r="U22" s="75" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="V22" s="142" t="s">
         <v>38</v>
@@ -31521,7 +31545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:36" ht="91.2" hidden="1">
+    <row r="23" spans="1:36" ht="91.2">
       <c r="A23" s="141">
         <v>233</v>
       </c>
@@ -31577,7 +31601,7 @@
         <v>100</v>
       </c>
       <c r="U23" s="75" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="V23" s="142" t="s">
         <v>38</v>
@@ -31626,7 +31650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:36" ht="148.19999999999999" hidden="1">
+    <row r="24" spans="1:36" ht="148.19999999999999">
       <c r="A24" s="141">
         <v>244</v>
       </c>
@@ -31682,7 +31706,7 @@
         <v>100</v>
       </c>
       <c r="U24" s="75" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="V24" s="142" t="s">
         <v>38</v>
@@ -31697,7 +31721,7 @@
         <v>41</v>
       </c>
       <c r="Z24" s="144" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="AA24" s="145" t="s">
         <v>55</v>
@@ -31729,13 +31753,13 @@
         <v>651</v>
       </c>
       <c r="AI24" s="220">
-        <v>46022</v>
+        <v>46219</v>
       </c>
       <c r="AJ24" s="67">
         <v>0.5</v>
       </c>
     </row>
-    <row r="25" spans="1:36" ht="193.8" hidden="1">
+    <row r="25" spans="1:36" ht="193.8">
       <c r="A25" s="59">
         <v>245</v>
       </c>
@@ -31791,7 +31815,7 @@
         <v>100</v>
       </c>
       <c r="U25" s="60" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="V25" s="137" t="s">
         <v>38</v>
@@ -31806,7 +31830,7 @@
         <v>41</v>
       </c>
       <c r="Z25" s="99" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="AA25" s="64" t="s">
         <v>55</v>
@@ -31844,7 +31868,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="26" spans="1:36" ht="136.80000000000001" hidden="1">
+    <row r="26" spans="1:36" ht="136.80000000000001">
       <c r="A26" s="59">
         <v>246</v>
       </c>
@@ -31900,7 +31924,7 @@
         <v>100</v>
       </c>
       <c r="U26" s="60" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="V26" s="137" t="s">
         <v>38</v>
@@ -31923,7 +31947,7 @@
       </c>
       <c r="AC26" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AD26" s="67">
         <f t="shared" ca="1" si="1"/>
@@ -31931,7 +31955,7 @@
       </c>
       <c r="AE26" s="67">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF26" s="67">
         <f t="shared" ca="1" si="3"/>
@@ -31946,10 +31970,10 @@
       </c>
       <c r="AI26" s="67"/>
       <c r="AJ26" s="67" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="27" spans="1:36" ht="193.8" hidden="1">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="27" spans="1:36" ht="193.8">
       <c r="A27" s="59">
         <v>247</v>
       </c>
@@ -32005,7 +32029,7 @@
         <v>100</v>
       </c>
       <c r="U27" s="60" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="V27" s="137" t="s">
         <v>38</v>
@@ -32028,7 +32052,7 @@
       </c>
       <c r="AC27" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AD27" s="67">
         <f t="shared" ca="1" si="1"/>
@@ -32036,7 +32060,7 @@
       </c>
       <c r="AE27" s="67">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF27" s="67">
         <f t="shared" ca="1" si="3"/>
@@ -32051,10 +32075,10 @@
       </c>
       <c r="AI27" s="67"/>
       <c r="AJ27" s="67" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="28" spans="1:36" ht="91.2" hidden="1">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="28" spans="1:36" ht="91.2">
       <c r="A28" s="59">
         <v>255</v>
       </c>
@@ -32110,7 +32134,7 @@
         <v>100</v>
       </c>
       <c r="U28" s="60" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="V28" s="137" t="s">
         <v>38</v>
@@ -32133,7 +32157,7 @@
       </c>
       <c r="AC28" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AD28" s="67">
         <f t="shared" ca="1" si="1"/>
@@ -32141,7 +32165,7 @@
       </c>
       <c r="AE28" s="67">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF28" s="67">
         <f t="shared" ca="1" si="3"/>
@@ -32215,7 +32239,7 @@
         <v>100</v>
       </c>
       <c r="U29" s="60" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="V29" s="137" t="s">
         <v>38</v>
@@ -32238,7 +32262,7 @@
       </c>
       <c r="AC29" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AD29" s="67">
         <f t="shared" ca="1" si="1"/>
@@ -32246,7 +32270,7 @@
       </c>
       <c r="AE29" s="67">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF29" s="67">
         <f t="shared" ca="1" si="3"/>
@@ -32264,7 +32288,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:36" ht="91.2" hidden="1">
+    <row r="30" spans="1:36" ht="91.2">
       <c r="A30" s="151">
         <v>259</v>
       </c>
@@ -32320,7 +32344,7 @@
         <v>100</v>
       </c>
       <c r="U30" s="152" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="V30" s="153" t="s">
         <v>38</v>
@@ -32335,7 +32359,7 @@
         <v>41</v>
       </c>
       <c r="Z30" s="154" t="s">
-        <v>726</v>
+        <v>822</v>
       </c>
       <c r="AA30" s="155" t="s">
         <v>55</v>
@@ -32429,7 +32453,7 @@
         <v>100</v>
       </c>
       <c r="U31" s="75" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="V31" s="142" t="s">
         <v>38</v>
@@ -32444,7 +32468,7 @@
         <v>41</v>
       </c>
       <c r="Z31" s="160" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="AA31" s="145" t="s">
         <v>55</v>
@@ -32482,7 +32506,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="32" spans="1:36" ht="136.80000000000001" hidden="1">
+    <row r="32" spans="1:36" ht="136.80000000000001">
       <c r="A32" s="141">
         <v>261</v>
       </c>
@@ -32538,7 +32562,7 @@
         <v>100</v>
       </c>
       <c r="U32" s="75" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="V32" s="142" t="s">
         <v>38</v>
@@ -32587,7 +32611,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="33" spans="1:36" ht="136.80000000000001" hidden="1">
+    <row r="33" spans="1:36" ht="136.80000000000001">
       <c r="A33" s="141">
         <v>262</v>
       </c>
@@ -32643,7 +32667,7 @@
         <v>100</v>
       </c>
       <c r="U33" s="75" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="V33" s="142" t="s">
         <v>38</v>
@@ -32658,7 +32682,7 @@
         <v>41</v>
       </c>
       <c r="Z33" s="160" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="AA33" s="145" t="s">
         <v>55</v>
@@ -32696,7 +32720,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="34" spans="1:36" ht="136.80000000000001" hidden="1">
+    <row r="34" spans="1:36" ht="136.80000000000001">
       <c r="A34" s="59">
         <v>263</v>
       </c>
@@ -32752,7 +32776,7 @@
         <v>100</v>
       </c>
       <c r="U34" s="60" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="V34" s="137" t="s">
         <v>38</v>
@@ -32803,7 +32827,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="35" spans="1:36" ht="148.19999999999999" hidden="1">
+    <row r="35" spans="1:36" ht="148.19999999999999">
       <c r="A35" s="59">
         <v>281</v>
       </c>
@@ -32859,7 +32883,7 @@
         <v>100</v>
       </c>
       <c r="U35" s="60" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="V35" s="137" t="s">
         <v>38</v>
@@ -32874,7 +32898,7 @@
         <v>41</v>
       </c>
       <c r="Z35" s="99" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="AA35" s="64" t="s">
         <v>55</v>
@@ -32912,7 +32936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:36" ht="136.80000000000001" hidden="1">
+    <row r="36" spans="1:36" ht="136.80000000000001">
       <c r="A36" s="59">
         <v>181</v>
       </c>
@@ -32968,7 +32992,7 @@
         <v>100</v>
       </c>
       <c r="U36" s="60" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="V36" s="137" t="s">
         <v>244</v>
@@ -33021,7 +33045,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="37" spans="1:36" ht="91.2" hidden="1">
+    <row r="37" spans="1:36" ht="91.2">
       <c r="A37" s="59">
         <v>182</v>
       </c>
@@ -33077,7 +33101,7 @@
         <v>100</v>
       </c>
       <c r="U37" s="60" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="V37" s="137" t="s">
         <v>244</v>
@@ -33128,7 +33152,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="38" spans="1:36" ht="125.4" hidden="1">
+    <row r="38" spans="1:36" ht="125.4">
       <c r="A38" s="59">
         <v>183</v>
       </c>
@@ -33184,7 +33208,7 @@
         <v>100</v>
       </c>
       <c r="U38" s="60" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="V38" s="137" t="s">
         <v>244</v>
@@ -33235,7 +33259,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="39" spans="1:36" ht="148.19999999999999" hidden="1">
+    <row r="39" spans="1:36" ht="148.19999999999999">
       <c r="A39" s="161">
         <v>189</v>
       </c>
@@ -33291,7 +33315,7 @@
         <v>100</v>
       </c>
       <c r="U39" s="75" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="V39" s="142" t="s">
         <v>244</v>
@@ -33342,7 +33366,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="40" spans="1:36" ht="159.6" hidden="1">
+    <row r="40" spans="1:36" ht="159.6">
       <c r="A40" s="59">
         <v>190</v>
       </c>
@@ -33449,7 +33473,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="41" spans="1:36" ht="102.6" hidden="1">
+    <row r="41" spans="1:36" ht="102.6">
       <c r="A41" s="78">
         <v>191</v>
       </c>
@@ -33505,7 +33529,7 @@
         <v>100</v>
       </c>
       <c r="U41" s="60" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="V41" s="137" t="s">
         <v>244</v>
@@ -33558,7 +33582,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="42" spans="1:36" ht="125.4" hidden="1">
+    <row r="42" spans="1:36" ht="125.4">
       <c r="A42" s="59">
         <v>194</v>
       </c>
@@ -33614,7 +33638,7 @@
         <v>100</v>
       </c>
       <c r="U42" s="60" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="V42" s="137" t="s">
         <v>244</v>
@@ -33667,7 +33691,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="43" spans="1:36" ht="148.19999999999999" hidden="1">
+    <row r="43" spans="1:36" ht="148.19999999999999">
       <c r="A43" s="161">
         <v>195</v>
       </c>
@@ -33723,7 +33747,7 @@
         <v>100</v>
       </c>
       <c r="U43" s="75" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="V43" s="142" t="s">
         <v>244</v>
@@ -33774,7 +33798,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="44" spans="1:36" ht="216.6" hidden="1">
+    <row r="44" spans="1:36" ht="216.6">
       <c r="A44" s="59">
         <v>214</v>
       </c>
@@ -33830,7 +33854,7 @@
         <v>100</v>
       </c>
       <c r="U44" s="60" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="V44" s="137" t="s">
         <v>244</v>
@@ -33881,7 +33905,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="45" spans="1:36" ht="125.4" hidden="1">
+    <row r="45" spans="1:36" ht="125.4">
       <c r="A45" s="83">
         <v>215</v>
       </c>
@@ -33937,7 +33961,7 @@
         <v>100</v>
       </c>
       <c r="U45" s="84" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="V45" s="139" t="s">
         <v>244</v>
@@ -33988,7 +34012,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="46" spans="1:36" ht="102.6" hidden="1">
+    <row r="46" spans="1:36" ht="102.6">
       <c r="A46" s="78">
         <v>216</v>
       </c>
@@ -34095,7 +34119,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="47" spans="1:36" ht="182.4" hidden="1">
+    <row r="47" spans="1:36" ht="182.4">
       <c r="A47" s="78">
         <v>217</v>
       </c>
@@ -34202,7 +34226,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="48" spans="1:36" ht="131.4" hidden="1" customHeight="1">
+    <row r="48" spans="1:36" ht="131.4" customHeight="1">
       <c r="A48" s="78">
         <v>218</v>
       </c>
@@ -34273,7 +34297,7 @@
         <v>41</v>
       </c>
       <c r="Z48" s="129" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="AA48" s="64" t="s">
         <v>55</v>
@@ -34311,7 +34335,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="49" spans="1:36" ht="171" hidden="1">
+    <row r="49" spans="1:36" ht="171">
       <c r="A49" s="59">
         <v>219</v>
       </c>
@@ -34367,7 +34391,7 @@
         <v>100</v>
       </c>
       <c r="U49" s="60" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="V49" s="137" t="s">
         <v>244</v>
@@ -34418,7 +34442,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="50" spans="1:36" ht="205.2" hidden="1">
+    <row r="50" spans="1:36" ht="205.2">
       <c r="A50" s="59">
         <v>220</v>
       </c>
@@ -34474,7 +34498,7 @@
         <v>100</v>
       </c>
       <c r="U50" s="60" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="V50" s="137" t="s">
         <v>244</v>
@@ -34525,7 +34549,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="51" spans="1:36" ht="171" hidden="1">
+    <row r="51" spans="1:36" ht="171">
       <c r="A51" s="59">
         <v>223</v>
       </c>
@@ -34581,7 +34605,7 @@
         <v>100</v>
       </c>
       <c r="U51" s="60" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="V51" s="137" t="s">
         <v>244</v>
@@ -34632,7 +34656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:36" ht="125.4" hidden="1">
+    <row r="52" spans="1:36" ht="125.4">
       <c r="A52" s="59">
         <v>226</v>
       </c>
@@ -34739,7 +34763,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="53" spans="1:36" ht="125.4" hidden="1">
+    <row r="53" spans="1:36" ht="125.4">
       <c r="A53" s="59">
         <v>227</v>
       </c>
@@ -34846,7 +34870,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="54" spans="1:36" ht="193.8" hidden="1">
+    <row r="54" spans="1:36" ht="193.8">
       <c r="A54" s="59">
         <v>228</v>
       </c>
@@ -34953,7 +34977,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="55" spans="1:36" ht="125.4" hidden="1">
+    <row r="55" spans="1:36" ht="125.4">
       <c r="A55" s="78">
         <v>229</v>
       </c>
@@ -35060,7 +35084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:36" ht="136.80000000000001" hidden="1">
+    <row r="56" spans="1:36" ht="136.80000000000001">
       <c r="A56" s="78">
         <v>230</v>
       </c>
@@ -35223,7 +35247,7 @@
         <v>100</v>
       </c>
       <c r="U57" s="60" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="V57" s="137" t="s">
         <v>244</v>
@@ -35274,7 +35298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:36" ht="171" hidden="1">
+    <row r="58" spans="1:36" ht="171">
       <c r="A58" s="78">
         <v>240</v>
       </c>
@@ -35381,7 +35405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:36" ht="205.2" hidden="1">
+    <row r="59" spans="1:36" ht="205.2">
       <c r="A59" s="59">
         <v>245</v>
       </c>
@@ -35488,7 +35512,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="60" spans="1:36" ht="68.400000000000006" hidden="1">
+    <row r="60" spans="1:36" ht="68.400000000000006">
       <c r="A60" s="78">
         <v>246</v>
       </c>
@@ -35595,7 +35619,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="61" spans="1:36" ht="148.19999999999999" hidden="1">
+    <row r="61" spans="1:36" ht="148.19999999999999">
       <c r="A61" s="78">
         <v>247</v>
       </c>
@@ -35651,7 +35675,7 @@
         <v>100</v>
       </c>
       <c r="U61" s="60" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="V61" s="137" t="s">
         <v>244</v>
@@ -35702,7 +35726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:36" ht="228" hidden="1">
+    <row r="62" spans="1:36" ht="228">
       <c r="A62" s="59">
         <v>120</v>
       </c>
@@ -35813,7 +35837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:36" ht="262.2" hidden="1">
+    <row r="63" spans="1:36" ht="262.2">
       <c r="A63" s="78">
         <v>123</v>
       </c>
@@ -35873,7 +35897,7 @@
         <v>100</v>
       </c>
       <c r="U63" s="60" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="V63" s="60" t="s">
         <v>455</v>
@@ -35924,7 +35948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:36" ht="273.60000000000002" hidden="1">
+    <row r="64" spans="1:36" ht="273.60000000000002">
       <c r="A64" s="59">
         <v>125</v>
       </c>
@@ -35984,7 +36008,7 @@
         <v>100</v>
       </c>
       <c r="U64" s="60" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="V64" s="60" t="s">
         <v>455</v>
@@ -36035,7 +36059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:36" ht="171" hidden="1">
+    <row r="65" spans="1:36" ht="171">
       <c r="A65" s="59">
         <v>184</v>
       </c>
@@ -36095,7 +36119,7 @@
         <v>100</v>
       </c>
       <c r="U65" s="60" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="V65" s="60" t="s">
         <v>455</v>
@@ -36148,7 +36172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:36" ht="205.2" hidden="1">
+    <row r="66" spans="1:36" ht="205.2">
       <c r="A66" s="59">
         <v>186</v>
       </c>
@@ -36208,7 +36232,7 @@
         <v>100</v>
       </c>
       <c r="U66" s="60" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="V66" s="60" t="s">
         <v>446</v>
@@ -36261,7 +36285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:36" ht="171" hidden="1">
+    <row r="67" spans="1:36" ht="171">
       <c r="A67" s="59">
         <v>187</v>
       </c>
@@ -36321,7 +36345,7 @@
         <v>100</v>
       </c>
       <c r="U67" s="60" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="V67" s="60" t="s">
         <v>455</v>
@@ -36374,7 +36398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:36" ht="171" hidden="1">
+    <row r="68" spans="1:36" ht="171">
       <c r="A68" s="59">
         <v>188</v>
       </c>
@@ -36434,7 +36458,7 @@
         <v>100</v>
       </c>
       <c r="U68" s="60" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="V68" s="60" t="s">
         <v>455</v>
@@ -36487,7 +36511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:36" ht="193.8" hidden="1">
+    <row r="69" spans="1:36" ht="193.8">
       <c r="A69" s="59">
         <v>213</v>
       </c>
@@ -36598,7 +36622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:36" ht="228" hidden="1">
+    <row r="70" spans="1:36" ht="228">
       <c r="A70" s="59">
         <v>221</v>
       </c>
@@ -36658,7 +36682,7 @@
         <v>100</v>
       </c>
       <c r="U70" s="60" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="V70" s="60" t="s">
         <v>500</v>
@@ -36709,7 +36733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:36" ht="239.4" hidden="1">
+    <row r="71" spans="1:36" ht="239.4">
       <c r="A71" s="59">
         <v>222</v>
       </c>
@@ -36769,7 +36793,7 @@
         <v>100</v>
       </c>
       <c r="U71" s="60" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="V71" s="60" t="s">
         <v>500</v>
@@ -36820,7 +36844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:36" ht="228" hidden="1">
+    <row r="72" spans="1:36" ht="228">
       <c r="A72" s="78">
         <v>224</v>
       </c>
@@ -36880,7 +36904,7 @@
         <v>100</v>
       </c>
       <c r="U72" s="60" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="V72" s="60" t="s">
         <v>500</v>
@@ -36931,7 +36955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:36" ht="239.4" hidden="1">
+    <row r="73" spans="1:36" ht="239.4">
       <c r="A73" s="59">
         <v>225</v>
       </c>
@@ -36991,7 +37015,7 @@
         <v>100</v>
       </c>
       <c r="U73" s="60" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="V73" s="60" t="s">
         <v>500</v>
@@ -37044,7 +37068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:36" ht="193.8" hidden="1">
+    <row r="74" spans="1:36" ht="193.8">
       <c r="A74" s="59">
         <v>232</v>
       </c>
@@ -37104,7 +37128,7 @@
         <v>100</v>
       </c>
       <c r="U74" s="60" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="V74" s="60" t="s">
         <v>500</v>
@@ -37157,7 +37181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:36" ht="182.4" hidden="1">
+    <row r="75" spans="1:36" ht="182.4">
       <c r="A75" s="59">
         <v>233</v>
       </c>
@@ -37217,7 +37241,7 @@
         <v>100</v>
       </c>
       <c r="U75" s="60" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="V75" s="60" t="s">
         <v>500</v>
@@ -37268,7 +37292,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="76" spans="1:36" ht="262.2" hidden="1">
+    <row r="76" spans="1:36" ht="262.2">
       <c r="A76" s="59">
         <v>234</v>
       </c>
@@ -37328,7 +37352,7 @@
         <v>100</v>
       </c>
       <c r="U76" s="60" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="V76" s="60" t="s">
         <v>500</v>
@@ -37379,7 +37403,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="77" spans="1:36" ht="205.2" hidden="1">
+    <row r="77" spans="1:36" ht="205.2">
       <c r="A77" s="59">
         <v>235</v>
       </c>
@@ -37439,7 +37463,7 @@
         <v>100</v>
       </c>
       <c r="U77" s="60" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="V77" s="60" t="s">
         <v>500</v>
@@ -37492,7 +37516,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="78" spans="1:36" ht="262.2" hidden="1">
+    <row r="78" spans="1:36" ht="262.2">
       <c r="A78" s="59">
         <v>236</v>
       </c>
@@ -37552,7 +37576,7 @@
         <v>100</v>
       </c>
       <c r="U78" s="60" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="V78" s="60" t="s">
         <v>500</v>
@@ -37605,7 +37629,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="79" spans="1:36" ht="159.6" hidden="1">
+    <row r="79" spans="1:36" ht="159.6">
       <c r="A79" s="59">
         <v>237</v>
       </c>
@@ -37665,7 +37689,7 @@
         <v>100</v>
       </c>
       <c r="U79" s="60" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="V79" s="60" t="s">
         <v>500</v>
@@ -37778,7 +37802,7 @@
         <v>100</v>
       </c>
       <c r="U80" s="60" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="V80" s="60" t="s">
         <v>578</v>
@@ -37829,7 +37853,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="81" spans="1:36" ht="250.8" hidden="1">
+    <row r="81" spans="1:36" ht="250.8">
       <c r="A81" s="59">
         <v>239</v>
       </c>
@@ -37889,7 +37913,7 @@
         <v>100</v>
       </c>
       <c r="U81" s="60" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="V81" s="60" t="s">
         <v>578</v>
@@ -38000,7 +38024,7 @@
         <v>100</v>
       </c>
       <c r="U82" s="60" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="V82" s="60" t="s">
         <v>592</v>
@@ -38111,7 +38135,7 @@
         <v>100</v>
       </c>
       <c r="U83" s="60" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="V83" s="60" t="s">
         <v>592</v>
@@ -38222,7 +38246,7 @@
         <v>100</v>
       </c>
       <c r="U84" s="60" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="V84" s="60" t="s">
         <v>592</v>
@@ -38333,7 +38357,7 @@
         <v>100</v>
       </c>
       <c r="U85" s="60" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="V85" s="60" t="s">
         <v>592</v>
@@ -38537,46 +38561,46 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="20" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="C1" s="20" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="43.2">
       <c r="A2" s="206" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="B2" s="166" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="C2" s="207" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="28.8">
       <c r="A3" s="206" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="B3" s="166" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="C3" s="207" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="43.2">
       <c r="A4" s="206" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="B4" s="166" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="C4" s="208" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -39105,35 +39129,35 @@
   <sheetData>
     <row r="2" spans="3:10">
       <c r="C2" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="D2" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="E2" s="121">
         <v>0.25</v>
       </c>
       <c r="F2" t="s">
+        <v>702</v>
+      </c>
+      <c r="I2" t="s">
         <v>704</v>
-      </c>
-      <c r="I2" t="s">
-        <v>706</v>
       </c>
     </row>
     <row r="4" spans="3:10">
       <c r="C4" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="6" spans="3:10">
       <c r="C6" t="s">
+        <v>705</v>
+      </c>
+      <c r="H6" s="122" t="s">
         <v>707</v>
       </c>
-      <c r="H6" s="122" t="s">
-        <v>709</v>
-      </c>
       <c r="I6" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="J6" s="123">
         <v>85141264</v>
@@ -39141,15 +39165,15 @@
     </row>
     <row r="8" spans="3:10">
       <c r="C8" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
     <row r="10" spans="3:10">
       <c r="C10" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="F10" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
   </sheetData>
@@ -39188,14 +39212,14 @@
     <row r="1" spans="3:14" s="102" customFormat="1" ht="3.6" customHeight="1"/>
     <row r="4" spans="3:14">
       <c r="C4" s="103" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="D4" s="104"/>
       <c r="E4" s="104"/>
     </row>
     <row r="5" spans="3:14">
       <c r="C5" s="16" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="D5" s="16"/>
       <c r="E5" s="16"/>
@@ -39206,13 +39230,13 @@
       <c r="E6" s="16"/>
     </row>
     <row r="7" spans="3:14" ht="76.2" customHeight="1">
-      <c r="C7" s="233" t="s">
-        <v>686</v>
-      </c>
-      <c r="D7" s="233"/>
-      <c r="E7" s="233"/>
-      <c r="F7" s="233"/>
-      <c r="G7" s="233"/>
+      <c r="C7" s="240" t="s">
+        <v>684</v>
+      </c>
+      <c r="D7" s="240"/>
+      <c r="E7" s="240"/>
+      <c r="F7" s="240"/>
+      <c r="G7" s="240"/>
     </row>
     <row r="8" spans="3:14">
       <c r="C8" s="105" t="s">
@@ -39237,7 +39261,7 @@
         <v>15</v>
       </c>
       <c r="J8" s="111" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="K8" s="105" t="s">
         <v>20</v>
@@ -39275,7 +39299,7 @@
         <v>118</v>
       </c>
       <c r="J9" s="118" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="K9" s="99" t="s">
         <v>38</v>
@@ -39313,7 +39337,7 @@
         <v>137</v>
       </c>
       <c r="J10" s="118" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="K10" s="99" t="s">
         <v>38</v>
@@ -39351,7 +39375,7 @@
         <v>144</v>
       </c>
       <c r="J11" s="118" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="K11" s="99" t="s">
         <v>38</v>
@@ -39389,7 +39413,7 @@
         <v>137</v>
       </c>
       <c r="J12" s="119" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="K12" s="115" t="s">
         <v>38</v>
@@ -39442,14 +39466,14 @@
     </row>
     <row r="15" spans="3:14">
       <c r="C15" s="103" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="D15" s="104"/>
       <c r="E15" s="104"/>
     </row>
     <row r="16" spans="3:14">
       <c r="C16" s="16" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="D16" s="16"/>
       <c r="E16" s="16"/>
@@ -39460,13 +39484,13 @@
       <c r="E17" s="16"/>
     </row>
     <row r="18" spans="3:14" ht="85.2" customHeight="1">
-      <c r="C18" s="234" t="s">
-        <v>690</v>
-      </c>
-      <c r="D18" s="234"/>
-      <c r="E18" s="234"/>
-      <c r="F18" s="234"/>
-      <c r="G18" s="234"/>
+      <c r="C18" s="241" t="s">
+        <v>688</v>
+      </c>
+      <c r="D18" s="241"/>
+      <c r="E18" s="241"/>
+      <c r="F18" s="241"/>
+      <c r="G18" s="241"/>
     </row>
     <row r="19" spans="3:14">
       <c r="C19" s="108" t="s">
@@ -39491,7 +39515,7 @@
         <v>15</v>
       </c>
       <c r="J19" s="106" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="K19" s="108" t="s">
         <v>20</v>
@@ -39529,7 +39553,7 @@
         <v>260</v>
       </c>
       <c r="J20" s="127" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="K20" s="112" t="s">
         <v>244</v>
@@ -39567,7 +39591,7 @@
         <v>288</v>
       </c>
       <c r="J21" s="113" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="K21" s="112" t="s">
         <v>244</v>
@@ -39584,22 +39608,22 @@
     </row>
     <row r="22" spans="3:14" ht="74.400000000000006" customHeight="1">
       <c r="J22" s="125" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="24" spans="3:14">
       <c r="C24" s="103" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="D24" s="104"/>
       <c r="E24" s="104"/>
       <c r="J24" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
     </row>
     <row r="25" spans="3:14">
       <c r="C25" s="16" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="D25" s="16"/>
       <c r="E25" s="16"/>
@@ -39609,19 +39633,19 @@
       <c r="D26" s="16"/>
       <c r="E26" s="16"/>
       <c r="J26" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
     </row>
     <row r="27" spans="3:14" ht="58.2" customHeight="1">
-      <c r="C27" s="233" t="s">
-        <v>694</v>
-      </c>
-      <c r="D27" s="233"/>
-      <c r="E27" s="233"/>
-      <c r="F27" s="233"/>
-      <c r="G27" s="233"/>
+      <c r="C27" s="240" t="s">
+        <v>692</v>
+      </c>
+      <c r="D27" s="240"/>
+      <c r="E27" s="240"/>
+      <c r="F27" s="240"/>
+      <c r="G27" s="240"/>
       <c r="J27" s="203" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
     </row>
     <row r="28" spans="3:14">
@@ -39647,7 +39671,7 @@
         <v>15</v>
       </c>
       <c r="J28" s="111" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="K28" s="105" t="s">
         <v>20</v>
@@ -39685,7 +39709,7 @@
         <v>316</v>
       </c>
       <c r="J29" s="113" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="K29" s="112" t="s">
         <v>244</v>
@@ -39702,14 +39726,14 @@
     </row>
     <row r="32" spans="3:14">
       <c r="C32" s="103" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="D32" s="104"/>
       <c r="E32" s="104"/>
     </row>
     <row r="33" spans="3:14">
       <c r="C33" s="16" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="D33" s="16"/>
       <c r="E33" s="16"/>
@@ -39720,13 +39744,13 @@
       <c r="E34" s="16"/>
     </row>
     <row r="35" spans="3:14" ht="71.400000000000006" customHeight="1">
-      <c r="C35" s="233" t="s">
-        <v>700</v>
-      </c>
-      <c r="D35" s="233"/>
-      <c r="E35" s="233"/>
-      <c r="F35" s="233"/>
-      <c r="G35" s="233"/>
+      <c r="C35" s="240" t="s">
+        <v>698</v>
+      </c>
+      <c r="D35" s="240"/>
+      <c r="E35" s="240"/>
+      <c r="F35" s="240"/>
+      <c r="G35" s="240"/>
     </row>
     <row r="36" spans="3:14" ht="26.4" customHeight="1">
       <c r="C36" s="105" t="s">
@@ -39751,7 +39775,7 @@
         <v>15</v>
       </c>
       <c r="J36" s="111" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="K36" s="105" t="s">
         <v>20</v>
@@ -39789,7 +39813,7 @@
         <v>65</v>
       </c>
       <c r="J37" s="120" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="K37" s="112" t="s">
         <v>38</v>
@@ -39806,14 +39830,14 @@
     </row>
     <row r="40" spans="3:14">
       <c r="C40" s="103" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="D40" s="104"/>
       <c r="E40" s="104"/>
     </row>
     <row r="41" spans="3:14">
       <c r="C41" s="16" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="D41" s="16"/>
       <c r="E41" s="16"/>
@@ -39824,13 +39848,13 @@
       <c r="E42" s="16"/>
     </row>
     <row r="43" spans="3:14" ht="108.6" customHeight="1">
-      <c r="C43" s="233" t="s">
-        <v>713</v>
-      </c>
-      <c r="D43" s="233"/>
-      <c r="E43" s="233"/>
-      <c r="F43" s="233"/>
-      <c r="G43" s="233"/>
+      <c r="C43" s="240" t="s">
+        <v>711</v>
+      </c>
+      <c r="D43" s="240"/>
+      <c r="E43" s="240"/>
+      <c r="F43" s="240"/>
+      <c r="G43" s="240"/>
     </row>
     <row r="45" spans="3:14">
       <c r="C45" s="108" t="s">
@@ -39855,7 +39879,7 @@
         <v>15</v>
       </c>
       <c r="J45" s="124" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="K45" s="108" t="s">
         <v>20</v>
@@ -39893,7 +39917,7 @@
         <v>171</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="K46" s="112" t="s">
         <v>38</v>
@@ -39910,14 +39934,14 @@
     </row>
     <row r="49" spans="3:14">
       <c r="C49" s="103" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="D49" s="104"/>
       <c r="E49" s="104"/>
     </row>
     <row r="50" spans="3:14">
       <c r="C50" s="16" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="D50" s="16"/>
       <c r="E50" s="16"/>
@@ -39927,17 +39951,17 @@
       <c r="D51" s="16"/>
       <c r="E51" s="16"/>
       <c r="L51" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
     </row>
     <row r="52" spans="3:14" ht="70.8" customHeight="1">
-      <c r="C52" s="233" t="s">
-        <v>718</v>
-      </c>
-      <c r="D52" s="233"/>
-      <c r="E52" s="233"/>
-      <c r="F52" s="233"/>
-      <c r="G52" s="233"/>
+      <c r="C52" s="240" t="s">
+        <v>716</v>
+      </c>
+      <c r="D52" s="240"/>
+      <c r="E52" s="240"/>
+      <c r="F52" s="240"/>
+      <c r="G52" s="240"/>
     </row>
     <row r="54" spans="3:14">
       <c r="C54" s="105" t="s">
@@ -39962,7 +39986,7 @@
         <v>15</v>
       </c>
       <c r="J54" s="111" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="K54" s="105" t="s">
         <v>20</v>
@@ -40564,7 +40588,7 @@
         <v>623</v>
       </c>
       <c r="B3" s="46" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="C3" s="46" t="s">
         <v>628</v>
@@ -40579,7 +40603,7 @@
         <v>627</v>
       </c>
       <c r="G3" s="46" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -40700,7 +40724,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="192" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B10" s="205">
         <v>15</v>
@@ -40717,7 +40741,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="187" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="B11" s="204">
         <v>1</v>
@@ -40734,7 +40758,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="187" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B12" s="204">
         <v>1</v>
@@ -40751,7 +40775,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="39" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B13" s="46">
         <v>10</v>
@@ -40768,7 +40792,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="39" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="B14" s="46">
         <v>2</v>
@@ -40785,7 +40809,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="39" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B15" s="46">
         <v>2</v>
@@ -40802,7 +40826,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="39" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B16" s="46">
         <v>4</v>
@@ -40819,7 +40843,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="187" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="B17" s="204">
         <v>1</v>
@@ -40836,7 +40860,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="187" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B18" s="204">
         <v>1</v>
@@ -40853,7 +40877,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="39" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B19" s="46">
         <v>1</v>
@@ -40870,7 +40894,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="39" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B20" s="46">
         <v>2</v>
@@ -40887,7 +40911,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="187" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B21" s="204">
         <v>1</v>
@@ -40904,7 +40928,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="187" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B22" s="204">
         <v>1</v>
@@ -40921,7 +40945,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="39" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B23" s="46">
         <v>3</v>
@@ -40938,7 +40962,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="187" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B24" s="204">
         <v>3</v>
@@ -40955,7 +40979,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="187" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B25" s="204">
         <v>2</v>
@@ -40972,7 +40996,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="187" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="B26" s="204">
         <v>1</v>
@@ -40989,7 +41013,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="39" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="B27" s="46">
         <v>13</v>
@@ -41006,7 +41030,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="187" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B28" s="204">
         <v>2</v>
@@ -41023,7 +41047,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="187" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="B29" s="204">
         <v>1</v>
@@ -41040,7 +41064,7 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="39" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B30" s="46">
         <v>2</v>
@@ -41057,7 +41081,7 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="39" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B31" s="46">
         <v>10</v>
@@ -41074,7 +41098,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="187" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="B32" s="204">
         <v>1</v>
@@ -41091,7 +41115,7 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="39" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B33" s="46">
         <v>1</v>
@@ -41108,7 +41132,7 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="39" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B34" s="46">
         <v>3</v>
@@ -41172,10 +41196,10 @@
     </row>
     <row r="3" spans="3:15" ht="13.2">
       <c r="C3" s="176" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="K3" s="176" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
     </row>
     <row r="5" spans="3:15" ht="27" customHeight="1">
@@ -41183,37 +41207,37 @@
         <v>610</v>
       </c>
       <c r="D5" s="184" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="E5" s="184" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="F5" s="179" t="s">
+        <v>732</v>
+      </c>
+      <c r="G5" s="179" t="s">
+        <v>733</v>
+      </c>
+      <c r="H5" s="180" t="s">
+        <v>734</v>
+      </c>
+      <c r="I5" s="180" t="s">
         <v>735</v>
       </c>
-      <c r="G5" s="179" t="s">
-        <v>736</v>
-      </c>
-      <c r="H5" s="180" t="s">
-        <v>737</v>
-      </c>
-      <c r="I5" s="180" t="s">
-        <v>738</v>
-      </c>
       <c r="K5" s="178" t="s">
+        <v>731</v>
+      </c>
+      <c r="L5" s="179" t="s">
+        <v>732</v>
+      </c>
+      <c r="M5" s="179" t="s">
+        <v>733</v>
+      </c>
+      <c r="N5" s="180" t="s">
         <v>734</v>
       </c>
-      <c r="L5" s="179" t="s">
+      <c r="O5" s="180" t="s">
         <v>735</v>
-      </c>
-      <c r="M5" s="179" t="s">
-        <v>736</v>
-      </c>
-      <c r="N5" s="180" t="s">
-        <v>737</v>
-      </c>
-      <c r="O5" s="180" t="s">
-        <v>738</v>
       </c>
     </row>
     <row r="6" spans="3:15">
@@ -41243,7 +41267,7 @@
         <v>24</v>
       </c>
       <c r="K6" s="182" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="L6" s="183">
         <f>+GETPIVOTDATA("Suma de Total Planes de acción",'Calculos 2'!$A$9,"Responsable ","DIRECCIÓNDEGESTIÓNFINANCIERA")</f>
@@ -41289,7 +41313,7 @@
         <v>24</v>
       </c>
       <c r="K7" s="182" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="L7" s="183">
         <f>+GETPIVOTDATA("Suma de Total Planes de acción",'Calculos 2'!$A$9,"Responsable ","DIRECCIÓNDEGESTIÓNHUMANA")</f>
@@ -41335,7 +41359,7 @@
         <v>19</v>
       </c>
       <c r="K8" s="182" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="L8" s="183">
         <f>+GETPIVOTDATA("Suma de Total Planes de acción",'Calculos 2'!$A$9,"Responsable ","DIRECCIÓNDEINFRAESTRUCTURA")</f>
@@ -41355,11 +41379,11 @@
       </c>
     </row>
     <row r="9" spans="3:15" ht="12">
-      <c r="C9" s="229" t="s">
-        <v>752</v>
-      </c>
-      <c r="D9" s="229"/>
-      <c r="E9" s="229"/>
+      <c r="C9" s="236" t="s">
+        <v>749</v>
+      </c>
+      <c r="D9" s="236"/>
+      <c r="E9" s="236"/>
       <c r="F9" s="185">
         <f>SUM(F6:F8)</f>
         <v>84</v>
@@ -41377,7 +41401,7 @@
         <v>67</v>
       </c>
       <c r="K9" s="182" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="L9" s="183">
         <f>+GETPIVOTDATA("Suma de Total Planes de acción",'Calculos 2'!$A$9,"Responsable ","DIRECCIÓNDERECURSOSFÍSICOS")+GETPIVOTDATA("Suma de Total Planes de acción",'Calculos 2'!$A$9,"Responsable ","DIRECCIÓNDERECURSOSFÍSICOSYNEGOCIOS")</f>
@@ -41398,7 +41422,7 @@
     </row>
     <row r="10" spans="3:15">
       <c r="K10" s="182" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="L10" s="183">
         <f>+GETPIVOTDATA("Suma de Total Planes de acción",'Calculos 2'!$A$9,"Responsable ","DIRECCIÓNDESEGURIDADOPERACIONAL")</f>
@@ -41419,7 +41443,7 @@
     </row>
     <row r="11" spans="3:15">
       <c r="K11" s="182" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="L11" s="183">
         <f>+GETPIVOTDATA("Suma de Total Planes de acción",'Calculos 2'!$A$9,"Responsable ","DIRECCIÓNDESERVICIOALTRANSPORTADOR")</f>
@@ -41442,7 +41466,7 @@
       <c r="I12" s="19"/>
       <c r="J12" s="19"/>
       <c r="K12" s="182" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="L12" s="183">
         <f>+GETPIVOTDATA("Suma de Total Planes de acción",'Calculos 2'!$A$9,"Responsable ","SUBGERENCIACORPORATIVA")</f>
@@ -41463,7 +41487,7 @@
     </row>
     <row r="13" spans="3:15">
       <c r="K13" s="182" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="L13" s="183">
         <f>+GETPIVOTDATA("Suma de Total Planes de acción",'Calculos 2'!$A$9,"Responsable ","SUBGERENCIADEPLANEACIÓNYPROYECTOS")+GETPIVOTDATA("Suma de Total Planes de acción",'Calculos 2'!$A$9,"Responsable ","SUBGERENCIAPLANEACIÓNYPROYECTOS")+GETPIVOTDATA("Suma de Total Planes de acción",'Calculos 2'!$A$9,"Responsable ","SUBGERENCIAPLANEACIÓNYPROYECTOS(ZPP)")</f>
@@ -41488,7 +41512,7 @@
       <c r="F14" s="167"/>
       <c r="G14" s="167"/>
       <c r="K14" s="182" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="L14" s="183">
         <f>+GETPIVOTDATA("Suma de Total Planes de acción",'Calculos 2'!$A$9,"Responsable ","SUBGERENCIADESERVICIOSOPERACIONALESEINFRAESTRUCTURA")</f>
@@ -41513,7 +41537,7 @@
       <c r="F15" s="167"/>
       <c r="G15" s="167"/>
       <c r="K15" s="182" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="L15" s="183">
         <f>+GETPIVOTDATA("Suma de Total Planes de acción",'Calculos 2'!$A$9,"Responsable ","SUBGERENCIAJURÍDICA")</f>
@@ -41538,7 +41562,7 @@
       <c r="F16" s="167"/>
       <c r="G16" s="167"/>
       <c r="K16" s="185" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="L16" s="185">
         <f>SUM(L6:L15)</f>
@@ -41569,29 +41593,29 @@
       <c r="F18" s="167"/>
       <c r="G18" s="167"/>
       <c r="K18" s="176" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
     </row>
     <row r="20" spans="4:15" ht="24">
       <c r="K20" s="178" t="s">
+        <v>731</v>
+      </c>
+      <c r="L20" s="179" t="s">
+        <v>732</v>
+      </c>
+      <c r="M20" s="179" t="s">
+        <v>733</v>
+      </c>
+      <c r="N20" s="180" t="s">
         <v>734</v>
       </c>
-      <c r="L20" s="179" t="s">
+      <c r="O20" s="180" t="s">
         <v>735</v>
-      </c>
-      <c r="M20" s="179" t="s">
-        <v>736</v>
-      </c>
-      <c r="N20" s="180" t="s">
-        <v>737</v>
-      </c>
-      <c r="O20" s="180" t="s">
-        <v>738</v>
       </c>
     </row>
     <row r="21" spans="4:15" ht="22.8">
       <c r="K21" s="188" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="L21" s="29">
         <f>+GETPIVOTDATA("Suma de Total Planes de acción",'Calculos 2'!$A$9,"Responsable ","DIRECCIÓNDEGESTIÓNFINANCIERA/DIRECCIÓNDERECURSOSFÍSICOSYNEGOCIOS")</f>
@@ -41612,7 +41636,7 @@
     </row>
     <row r="22" spans="4:15" ht="22.8">
       <c r="K22" s="188" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="L22" s="29">
         <f>+GETPIVOTDATA("Suma de Total Planes de acción",'Calculos 2'!$A$9,"Responsable ","DIRECCIÓNDEGESTIÓNFINANCIERA/SUBGERENCIAJURÍDICA")</f>
@@ -41633,7 +41657,7 @@
     </row>
     <row r="23" spans="4:15" ht="22.8">
       <c r="K23" s="188" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="L23" s="29">
         <f>+GETPIVOTDATA("Suma de Total Planes de acción",'Calculos 2'!$A$9,"Responsable ","DIRECCIÓNDERECURSOSFÍSICOSYNEGOCIOS/SUBGERENCIAJURÍDICA")</f>
@@ -41654,7 +41678,7 @@
     </row>
     <row r="24" spans="4:15" ht="22.8">
       <c r="K24" s="188" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="L24" s="29">
         <f>+GETPIVOTDATA("Suma de Total Planes de acción",'Calculos 2'!$A$9,"Responsable ","DIRECCIÓNDERECURSOSTECNOLÓGICOS
@@ -41679,7 +41703,7 @@
     </row>
     <row r="25" spans="4:15" ht="22.8">
       <c r="K25" s="188" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="L25" s="29">
         <f>+GETPIVOTDATA("Suma de Total Planes de acción",'Calculos 2'!$A$9,"Responsable ","DIRECCIÓNDESERVICIOALTRANSPORTADOR/DIRECCIÓNDERECURSOSTECNOLÓGICOS")</f>
@@ -41700,7 +41724,7 @@
     </row>
     <row r="26" spans="4:15" ht="34.200000000000003">
       <c r="K26" s="188" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="L26" s="29">
         <f>+GETPIVOTDATA("Suma de Total Planes de acción",'Calculos 2'!$A$9,"Responsable ","OFICINADEAUDITORÍAINTERNASUBGERENCIAJURÍDICADIRECCIÓNFINANCIERA")</f>
@@ -41721,7 +41745,7 @@
     </row>
     <row r="27" spans="4:15" ht="22.8">
       <c r="K27" s="188" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="L27" s="29">
         <f>+GETPIVOTDATA("Suma de Total Planes de acción",'Calculos 2'!$A$9,"Responsable ","SUBGERENCIACORPORATIVA/DIRECCIÓNDEGESTIÓNFINANCIERA")</f>
@@ -41742,7 +41766,7 @@
     </row>
     <row r="28" spans="4:15" ht="22.8">
       <c r="K28" s="188" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="L28" s="29">
         <f>+GETPIVOTDATA("Suma de Total Planes de acción",'Calculos 2'!$A$9,"Responsable ","SUBGERENCIACORPORATIVA/DIRECCIÓNDERECURSOSTECNOLÓGICOS")</f>
@@ -41763,7 +41787,7 @@
     </row>
     <row r="29" spans="4:15" ht="34.200000000000003">
       <c r="K29" s="188" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="L29" s="29">
         <f>+GETPIVOTDATA("Suma de Total Planes de acción",'Calculos 2'!$A$9,"Responsable ","SUBGERENCIACORPORATIVADIRECCIÓNDEGESTIÓNFINANCIERADIRECCIÓNDERECURSOSTECNOLÓGICOS")</f>
@@ -41784,7 +41808,7 @@
     </row>
     <row r="30" spans="4:15" ht="22.8">
       <c r="K30" s="188" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="L30" s="29">
         <f>+GETPIVOTDATA("Suma de Total Planes de acción",'Calculos 2'!$A$9,"Responsable ","SUBGERENCIADEPLANEACIÓNYPROYECTOSDIRECCIÓNDEGESTIÓNHUMANA")</f>
@@ -41805,7 +41829,7 @@
     </row>
     <row r="31" spans="4:15" ht="22.8">
       <c r="K31" s="188" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="L31" s="29">
         <f>+GETPIVOTDATA("Suma de Total Planes de acción",'Calculos 2'!$A$9,"Responsable ","SUBGERENCIADEPLANEACIÓNYPROYECTOSDIRECCIÓNDERECURSOSFÍSICOSYNEGOCIOS")</f>
@@ -41826,7 +41850,7 @@
     </row>
     <row r="32" spans="4:15" ht="22.8">
       <c r="K32" s="188" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="L32" s="29">
         <f>+GETPIVOTDATA("Suma de Total Planes de acción",'Calculos 2'!$A$9,"Responsable ","SUBGERENCIAJURÍDICADIRECCIÓNDEGESTIÓNHUMANA")</f>
@@ -41847,7 +41871,7 @@
     </row>
     <row r="33" spans="11:19" ht="12">
       <c r="K33" s="185" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="L33" s="185">
         <f>SUM(L21:L32)</f>
@@ -41868,7 +41892,7 @@
     </row>
     <row r="36" spans="11:19">
       <c r="K36" s="177" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="L36" s="30"/>
       <c r="M36" s="30"/>
@@ -41889,29 +41913,29 @@
       <c r="S37" s="177"/>
     </row>
     <row r="38" spans="11:19" ht="24">
-      <c r="K38" s="230" t="s">
+      <c r="K38" s="237" t="s">
+        <v>732</v>
+      </c>
+      <c r="L38" s="179" t="s">
+        <v>732</v>
+      </c>
+      <c r="M38" s="179" t="s">
+        <v>733</v>
+      </c>
+      <c r="N38" s="180" t="s">
+        <v>734</v>
+      </c>
+      <c r="O38" s="180" t="s">
         <v>735</v>
-      </c>
-      <c r="L38" s="179" t="s">
-        <v>735</v>
-      </c>
-      <c r="M38" s="179" t="s">
-        <v>736</v>
-      </c>
-      <c r="N38" s="180" t="s">
-        <v>737</v>
-      </c>
-      <c r="O38" s="180" t="s">
-        <v>738</v>
       </c>
       <c r="P38" s="189"/>
       <c r="Q38" s="189" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="S38" s="177"/>
     </row>
     <row r="39" spans="11:19" ht="12">
-      <c r="K39" s="231"/>
+      <c r="K39" s="238"/>
       <c r="L39" s="190">
         <f>+L16+L33</f>
         <v>84</v>
@@ -42059,7 +42083,7 @@
         <v>35</v>
       </c>
       <c r="F5" s="166" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="G5" s="165" t="s">
         <v>39</v>
@@ -42093,7 +42117,7 @@
         <v>83</v>
       </c>
       <c r="F6" s="166" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="G6" s="165" t="s">
         <v>86</v>
@@ -42127,7 +42151,7 @@
         <v>99</v>
       </c>
       <c r="F7" s="166" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="G7" s="165" t="s">
         <v>86</v>
@@ -42157,7 +42181,7 @@
         <v>91</v>
       </c>
       <c r="F8" s="166" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="G8" s="165" t="s">
         <v>86</v>
@@ -42187,7 +42211,7 @@
         <v>95</v>
       </c>
       <c r="F9" s="166" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G9" s="165" t="s">
         <v>86</v>
@@ -42221,7 +42245,7 @@
         <v>123</v>
       </c>
       <c r="F10" s="166" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="G10" s="165" t="s">
         <v>86</v>
@@ -42255,7 +42279,7 @@
         <v>182</v>
       </c>
       <c r="F11" s="166" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="G11" s="165" t="s">
         <v>86</v>
@@ -42276,7 +42300,7 @@
         <v>0</v>
       </c>
       <c r="T11" s="186" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="57.6">
@@ -42288,7 +42312,7 @@
         <v>186</v>
       </c>
       <c r="F12" s="166" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="G12" s="165" t="s">
         <v>86</v>
@@ -42322,7 +42346,7 @@
         <v>193</v>
       </c>
       <c r="F13" s="166" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="G13" s="165" t="s">
         <v>86</v>
@@ -42356,7 +42380,7 @@
         <v>200</v>
       </c>
       <c r="F14" s="166" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="G14" s="165" t="s">
         <v>86</v>
@@ -42390,7 +42414,7 @@
         <v>232</v>
       </c>
       <c r="F15" s="166" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="G15" s="165" t="s">
         <v>39</v>
@@ -42670,10 +42694,10 @@
   <sheetData>
     <row r="2" spans="2:9" s="199" customFormat="1">
       <c r="B2" s="198" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="C2" s="198" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="D2" s="198" t="s">
         <v>7</v>
@@ -42691,7 +42715,7 @@
         <v>21</v>
       </c>
       <c r="I2" s="193" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
     </row>
     <row r="3" spans="2:9" ht="61.2">
@@ -42711,7 +42735,7 @@
         <v>260</v>
       </c>
       <c r="G3" s="195" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="H3" s="196" t="s">
         <v>263</v>
@@ -42737,7 +42761,7 @@
         <v>288</v>
       </c>
       <c r="G4" s="195" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="H4" s="196" t="s">
         <v>263</v>
@@ -42763,7 +42787,7 @@
         <v>155</v>
       </c>
       <c r="G5" s="195" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H5" s="197">
         <v>46142</v>
@@ -42789,7 +42813,7 @@
         <v>155</v>
       </c>
       <c r="G6" s="195" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H6" s="196" t="s">
         <v>158</v>
@@ -42815,7 +42839,7 @@
         <v>155</v>
       </c>
       <c r="G7" s="195" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H7" s="196" t="s">
         <v>158</v>
@@ -42841,7 +42865,7 @@
         <v>171</v>
       </c>
       <c r="G8" s="195" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="H8" s="196" t="s">
         <v>77</v>
@@ -42867,7 +42891,7 @@
         <v>211</v>
       </c>
       <c r="G9" s="195" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="H9" s="196" t="s">
         <v>121</v>
@@ -42893,7 +42917,7 @@
         <v>218</v>
       </c>
       <c r="G10" s="195" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="H10" s="196" t="s">
         <v>158</v>
@@ -42919,7 +42943,7 @@
         <v>222</v>
       </c>
       <c r="G11" s="195" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="H11" s="196" t="s">
         <v>158</v>
@@ -42963,10 +42987,10 @@
   <sheetData>
     <row r="2" spans="2:9" s="25" customFormat="1">
       <c r="B2" s="193" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="C2" s="193" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="D2" s="193" t="s">
         <v>7</v>
@@ -42984,7 +43008,7 @@
         <v>21</v>
       </c>
       <c r="I2" s="193" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
     </row>
     <row r="3" spans="2:9" ht="61.2">
@@ -43004,7 +43028,7 @@
         <v>35</v>
       </c>
       <c r="G3" s="202" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="H3" s="196" t="s">
         <v>39</v>
@@ -43030,7 +43054,7 @@
         <v>83</v>
       </c>
       <c r="G4" s="202" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H4" s="196" t="s">
         <v>86</v>
@@ -43056,7 +43080,7 @@
         <v>99</v>
       </c>
       <c r="G5" s="202" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="H5" s="196" t="s">
         <v>86</v>
@@ -43082,7 +43106,7 @@
         <v>91</v>
       </c>
       <c r="G6" s="202" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="H6" s="196" t="s">
         <v>86</v>
@@ -43108,7 +43132,7 @@
         <v>95</v>
       </c>
       <c r="G7" s="202" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="H7" s="196" t="s">
         <v>86</v>
@@ -43134,7 +43158,7 @@
         <v>123</v>
       </c>
       <c r="G8" s="202" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="H8" s="196" t="s">
         <v>86</v>
@@ -43160,7 +43184,7 @@
         <v>182</v>
       </c>
       <c r="G9" s="202" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="H9" s="196" t="s">
         <v>86</v>
@@ -43186,7 +43210,7 @@
         <v>186</v>
       </c>
       <c r="G10" s="202" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="H10" s="196" t="s">
         <v>86</v>
@@ -43212,7 +43236,7 @@
         <v>193</v>
       </c>
       <c r="G11" s="202" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="H11" s="196" t="s">
         <v>86</v>
@@ -43238,7 +43262,7 @@
         <v>200</v>
       </c>
       <c r="G12" s="202" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="H12" s="196" t="s">
         <v>86</v>
@@ -43264,7 +43288,7 @@
         <v>232</v>
       </c>
       <c r="G13" s="202" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="H13" s="196" t="s">
         <v>39</v>
@@ -43348,7 +43372,7 @@
         <v>260</v>
       </c>
       <c r="G3" s="172" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="H3" s="28" t="s">
         <v>263</v>
@@ -43371,7 +43395,7 @@
         <v>288</v>
       </c>
       <c r="G4" s="172" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="H4" s="28" t="s">
         <v>263</v>
@@ -43394,7 +43418,7 @@
         <v>155</v>
       </c>
       <c r="G5" s="172" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H5" s="173">
         <v>46142</v>
@@ -43415,7 +43439,7 @@
         <v>155</v>
       </c>
       <c r="G6" s="172" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H6" s="28" t="s">
         <v>158</v>
@@ -43436,7 +43460,7 @@
         <v>155</v>
       </c>
       <c r="G7" s="172" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="H7" s="28" t="s">
         <v>158</v>
@@ -43457,7 +43481,7 @@
         <v>171</v>
       </c>
       <c r="G8" s="172" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="H8" s="28" t="s">
         <v>77</v>
@@ -43478,7 +43502,7 @@
         <v>211</v>
       </c>
       <c r="G9" s="172" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="H9" s="28" t="s">
         <v>121</v>
@@ -43492,14 +43516,14 @@
       <c r="D10" s="28" t="s">
         <v>215</v>
       </c>
-      <c r="E10" s="232" t="s">
+      <c r="E10" s="239" t="s">
         <v>216</v>
       </c>
       <c r="F10" s="171" t="s">
         <v>218</v>
       </c>
       <c r="G10" s="172" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="H10" s="28" t="s">
         <v>158</v>
@@ -43513,12 +43537,12 @@
       <c r="D11" s="28" t="s">
         <v>215</v>
       </c>
-      <c r="E11" s="232"/>
+      <c r="E11" s="239"/>
       <c r="F11" s="171" t="s">
         <v>222</v>
       </c>
       <c r="G11" s="172" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="H11" s="28" t="s">
         <v>158</v>
@@ -43613,22 +43637,22 @@
         <v>636</v>
       </c>
       <c r="P3" s="174" t="s">
+        <v>724</v>
+      </c>
+      <c r="Q3" s="174" t="s">
+        <v>725</v>
+      </c>
+      <c r="R3" s="174" t="s">
+        <v>729</v>
+      </c>
+      <c r="S3" s="174" t="s">
+        <v>726</v>
+      </c>
+      <c r="T3" s="174" t="s">
         <v>727</v>
       </c>
-      <c r="Q3" s="174" t="s">
+      <c r="U3" s="174" t="s">
         <v>728</v>
-      </c>
-      <c r="R3" s="174" t="s">
-        <v>732</v>
-      </c>
-      <c r="S3" s="174" t="s">
-        <v>729</v>
-      </c>
-      <c r="T3" s="174" t="s">
-        <v>730</v>
-      </c>
-      <c r="U3" s="174" t="s">
-        <v>731</v>
       </c>
     </row>
     <row r="4" spans="1:21">
@@ -43642,7 +43666,7 @@
         <v>30</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="G4" s="28">
         <f>IF(COUNTIFS($C$4:C4, C4, $D$4:D4, D4, $E$4:E4, E4)=1, 1, 0)</f>
@@ -43716,7 +43740,7 @@
         <v>30</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G5" s="28">
         <f>IF(COUNTIFS($C$4:C5, C5, $D$4:D5, D5, $E$4:E5, E5)=1, 1, 0)</f>
@@ -43790,7 +43814,7 @@
         <v>48</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="G6" s="28">
         <f>IF(COUNTIFS($C$4:C6, C6, $D$4:D6, D6, $E$4:E6, E6)=1, 1, 0)</f>
@@ -43864,7 +43888,7 @@
         <v>62</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="G7" s="28">
         <f>IF(COUNTIFS($C$4:C7, C7, $D$4:D7, D7, $E$4:E7, E7)=1, 1, 0)</f>
@@ -43938,7 +43962,7 @@
         <v>80</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="G8" s="28">
         <f>IF(COUNTIFS($C$4:C8, C8, $D$4:D8, D8, $E$4:E8, E8)=1, 1, 0)</f>
@@ -44012,7 +44036,7 @@
         <v>88</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="G9" s="28">
         <f>IF(COUNTIFS($C$4:C9, C9, $D$4:D9, D9, $E$4:E9, E9)=1, 1, 0)</f>
@@ -44086,7 +44110,7 @@
         <v>88</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G10" s="28">
         <f>IF(COUNTIFS($C$4:C10, C10, $D$4:D10, D10, $E$4:E10, E10)=1, 1, 0)</f>
@@ -44160,7 +44184,7 @@
         <v>88</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="G11" s="28">
         <f>IF(COUNTIFS($C$4:C11, C11, $D$4:D11, D11, $E$4:E11, E11)=1, 1, 0)</f>
@@ -44234,7 +44258,7 @@
         <v>103</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="G12" s="28">
         <f>IF(COUNTIFS($C$4:C12, C12, $D$4:D12, D12, $E$4:E12, E12)=1, 1, 0)</f>
@@ -44308,7 +44332,7 @@
         <v>103</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G13" s="28">
         <f>IF(COUNTIFS($C$4:C13, C13, $D$4:D13, D13, $E$4:E13, E13)=1, 1, 0)</f>
@@ -44382,7 +44406,7 @@
         <v>115</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G14" s="28">
         <f>IF(COUNTIFS($C$4:C14, C14, $D$4:D14, D14, $E$4:E14, E14)=1, 1, 0)</f>
@@ -44456,7 +44480,7 @@
         <v>115</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="G15" s="28">
         <f>IF(COUNTIFS($C$4:C15, C15, $D$4:D15, D15, $E$4:E15, E15)=1, 1, 0)</f>
@@ -44530,7 +44554,7 @@
         <v>127</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="G16" s="28">
         <f>IF(COUNTIFS($C$4:C16, C16, $D$4:D16, D16, $E$4:E16, E16)=1, 1, 0)</f>
@@ -44604,7 +44628,7 @@
         <v>134</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G17" s="28">
         <f>IF(COUNTIFS($C$4:C17, C17, $D$4:D17, D17, $E$4:E17, E17)=1, 1, 0)</f>
@@ -44678,7 +44702,7 @@
         <v>141</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G18" s="28">
         <f>IF(COUNTIFS($C$4:C18, C18, $D$4:D18, D18, $E$4:E18, E18)=1, 1, 0)</f>
@@ -44752,7 +44776,7 @@
         <v>148</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G19" s="28">
         <f>IF(COUNTIFS($C$4:C19, C19, $D$4:D19, D19, $E$4:E19, E19)=1, 1, 0)</f>
@@ -44826,7 +44850,7 @@
         <v>152</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="G20" s="28">
         <f>IF(COUNTIFS($C$4:C20, C20, $D$4:D20, D20, $E$4:E20, E20)=1, 1, 0)</f>
@@ -44900,7 +44924,7 @@
         <v>160</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="G21" s="28">
         <f>IF(COUNTIFS($C$4:C21, C21, $D$4:D21, D21, $E$4:E21, E21)=1, 1, 0)</f>
@@ -44974,7 +44998,7 @@
         <v>164</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="G22" s="28">
         <f>IF(COUNTIFS($C$4:C22, C22, $D$4:D22, D22, $E$4:E22, E22)=1, 1, 0)</f>
@@ -45048,7 +45072,7 @@
         <v>168</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="G23" s="28">
         <f>IF(COUNTIFS($C$4:C23, C23, $D$4:D23, D23, $E$4:E23, E23)=1, 1, 0)</f>
@@ -45122,7 +45146,7 @@
         <v>168</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="G24" s="28">
         <f>IF(COUNTIFS($C$4:C24, C24, $D$4:D24, D24, $E$4:E24, E24)=1, 1, 0)</f>
@@ -45196,7 +45220,7 @@
         <v>179</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="G25" s="28">
         <f>IF(COUNTIFS($C$4:C25, C25, $D$4:D25, D25, $E$4:E25, E25)=1, 1, 0)</f>
@@ -45274,7 +45298,7 @@
         <v>190</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="G26" s="28">
         <f>IF(COUNTIFS($C$4:C26, C26, $D$4:D26, D26, $E$4:E26, E26)=1, 1, 0)</f>
@@ -45348,7 +45372,7 @@
         <v>197</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="G27" s="28">
         <f>IF(COUNTIFS($C$4:C27, C27, $D$4:D27, D27, $E$4:E27, E27)=1, 1, 0)</f>
@@ -45422,7 +45446,7 @@
         <v>204</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="G28" s="28">
         <f>IF(COUNTIFS($C$4:C28, C28, $D$4:D28, D28, $E$4:E28, E28)=1, 1, 0)</f>
@@ -45496,7 +45520,7 @@
         <v>204</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="G29" s="28">
         <f>IF(COUNTIFS($C$4:C29, C29, $D$4:D29, D29, $E$4:E29, E29)=1, 1, 0)</f>
@@ -45570,7 +45594,7 @@
         <v>215</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G30" s="28">
         <f>IF(COUNTIFS($C$4:C30, C30, $D$4:D30, D30, $E$4:E30, E30)=1, 1, 0)</f>
@@ -45644,7 +45668,7 @@
         <v>215</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="G31" s="28">
         <f>IF(COUNTIFS($C$4:C31, C31, $D$4:D31, D31, $E$4:E31, E31)=1, 1, 0)</f>
@@ -45718,7 +45742,7 @@
         <v>229</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="G32" s="28">
         <f>IF(COUNTIFS($C$4:C32, C32, $D$4:D32, D32, $E$4:E32, E32)=1, 1, 0)</f>
@@ -45792,7 +45816,7 @@
         <v>237</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G33" s="28">
         <f>IF(COUNTIFS($C$4:C33, C33, $D$4:D33, D33, $E$4:E33, E33)=1, 1, 0)</f>
@@ -45866,7 +45890,7 @@
         <v>237</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="G34" s="28">
         <f>IF(COUNTIFS($C$4:C34, C34, $D$4:D34, D34, $E$4:E34, E34)=1, 1, 0)</f>
@@ -45940,7 +45964,7 @@
         <v>237</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="G35" s="28">
         <f>IF(COUNTIFS($C$4:C35, C35, $D$4:D35, D35, $E$4:E35, E35)=1, 1, 0)</f>
@@ -46014,7 +46038,7 @@
         <v>257</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="G36" s="28">
         <f>IF(COUNTIFS($C$4:C36, C36, $D$4:D36, D36, $E$4:E36, E36)=1, 1, 0)</f>
@@ -46088,7 +46112,7 @@
         <v>257</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="G37" s="28">
         <f>IF(COUNTIFS($C$4:C37, C37, $D$4:D37, D37, $E$4:E37, E37)=1, 1, 0)</f>
@@ -46162,7 +46186,7 @@
         <v>257</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="G38" s="28">
         <f>IF(COUNTIFS($C$4:C38, C38, $D$4:D38, D38, $E$4:E38, E38)=1, 1, 0)</f>
@@ -46236,7 +46260,7 @@
         <v>279</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G39" s="28">
         <f>IF(COUNTIFS($C$4:C39, C39, $D$4:D39, D39, $E$4:E39, E39)=1, 1, 0)</f>
@@ -46310,7 +46334,7 @@
         <v>279</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="G40" s="28">
         <f>IF(COUNTIFS($C$4:C40, C40, $D$4:D40, D40, $E$4:E40, E40)=1, 1, 0)</f>
@@ -46384,7 +46408,7 @@
         <v>290</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="G41" s="28">
         <f>IF(COUNTIFS($C$4:C41, C41, $D$4:D41, D41, $E$4:E41, E41)=1, 1, 0)</f>
@@ -46458,7 +46482,7 @@
         <v>302</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="G42" s="28">
         <f>IF(COUNTIFS($C$4:C42, C42, $D$4:D42, D42, $E$4:E42, E42)=1, 1, 0)</f>
@@ -46532,7 +46556,7 @@
         <v>168</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="G43" s="28">
         <f>IF(COUNTIFS($C$4:C43, C43, $D$4:D43, D43, $E$4:E43, E43)=1, 1, 0)</f>
@@ -46606,7 +46630,7 @@
         <v>179</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="G44" s="28">
         <f>IF(COUNTIFS($C$4:C44, C44, $D$4:D44, D44, $E$4:E44, E44)=1, 1, 0)</f>
@@ -46680,7 +46704,7 @@
         <v>190</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="G45" s="28">
         <f>IF(COUNTIFS($C$4:C45, C45, $D$4:D45, D45, $E$4:E45, E45)=1, 1, 0)</f>
@@ -46754,7 +46778,7 @@
         <v>197</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="G46" s="28">
         <f>IF(COUNTIFS($C$4:C46, C46, $D$4:D46, D46, $E$4:E46, E46)=1, 1, 0)</f>
@@ -46828,7 +46852,7 @@
         <v>204</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="G47" s="28">
         <f>IF(COUNTIFS($C$4:C47, C47, $D$4:D47, D47, $E$4:E47, E47)=1, 1, 0)</f>
@@ -46902,7 +46926,7 @@
         <v>215</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="G48" s="28">
         <f>IF(COUNTIFS($C$4:C48, C48, $D$4:D48, D48, $E$4:E48, E48)=1, 1, 0)</f>
@@ -46976,7 +47000,7 @@
         <v>370</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="G49" s="28">
         <f>IF(COUNTIFS($C$4:C49, C49, $D$4:D49, D49, $E$4:E49, E49)=1, 1, 0)</f>
@@ -47050,7 +47074,7 @@
         <v>378</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="G50" s="28">
         <f>IF(COUNTIFS($C$4:C50, C50, $D$4:D50, D50, $E$4:E50, E50)=1, 1, 0)</f>
@@ -47124,7 +47148,7 @@
         <v>389</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="G51" s="28">
         <f>IF(COUNTIFS($C$4:C51, C51, $D$4:D51, D51, $E$4:E51, E51)=1, 1, 0)</f>
@@ -47198,7 +47222,7 @@
         <v>440</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="G52" s="28">
         <f>IF(COUNTIFS($C$4:C52, C52, $D$4:D52, D52, $E$4:E52, E52)=1, 1, 0)</f>
@@ -47272,7 +47296,7 @@
         <v>449</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="G53" s="28">
         <f>IF(COUNTIFS($C$4:C53, C53, $D$4:D53, D53, $E$4:E53, E53)=1, 1, 0)</f>
@@ -47346,7 +47370,7 @@
         <v>458</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="G54" s="28">
         <f>IF(COUNTIFS($C$4:C54, C54, $D$4:D54, D54, $E$4:E54, E54)=1, 1, 0)</f>
@@ -47420,7 +47444,7 @@
         <v>62</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G55" s="28">
         <f>IF(COUNTIFS($C$4:C55, C55, $D$4:D55, D55, $E$4:E55, E55)=1, 1, 0)</f>
@@ -47494,7 +47518,7 @@
         <v>80</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G56" s="28">
         <f>IF(COUNTIFS($C$4:C56, C56, $D$4:D56, D56, $E$4:E56, E56)=1, 1, 0)</f>
@@ -47568,7 +47592,7 @@
         <v>88</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G57" s="28">
         <f>IF(COUNTIFS($C$4:C57, C57, $D$4:D57, D57, $E$4:E57, E57)=1, 1, 0)</f>
@@ -47642,7 +47666,7 @@
         <v>103</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G58" s="100">
         <f>IF(COUNTIFS($C$4:C75, C58, $D$4:D75, D58, $E$4:E75, E58)=1, 1, 0)</f>
@@ -47716,7 +47740,7 @@
         <v>494</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="G59" s="28">
         <f>IF(COUNTIFS($C$4:C59, C59, $D$4:D59, D59, $E$4:E59, E59)=1, 1, 0)</f>
@@ -47790,7 +47814,7 @@
         <v>168</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="G60" s="28">
         <f>IF(COUNTIFS($C$4:C60, C60, $D$4:D60, D60, $E$4:E60, E60)=1, 1, 0)</f>
@@ -47864,7 +47888,7 @@
         <v>179</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="G61" s="28">
         <f>IF(COUNTIFS($C$4:C61, C61, $D$4:D61, D61, $E$4:E61, E61)=1, 1, 0)</f>
@@ -47938,7 +47962,7 @@
         <v>517</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="G62" s="28">
         <f>IF(COUNTIFS($C$4:C62, C62, $D$4:D62, D62, $E$4:E62, E62)=1, 1, 0)</f>
@@ -48012,7 +48036,7 @@
         <v>190</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="G63" s="28">
         <f>IF(COUNTIFS($C$4:C63, C63, $D$4:D63, D63, $E$4:E63, E63)=1, 1, 0)</f>
@@ -48086,7 +48110,7 @@
         <v>215</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="G64" s="28">
         <f>IF(COUNTIFS($C$4:C64, C64, $D$4:D64, D64, $E$4:E64, E64)=1, 1, 0)</f>
@@ -48160,7 +48184,7 @@
         <v>539</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="G65" s="28">
         <f>IF(COUNTIFS($C$4:C65, C65, $D$4:D65, D65, $E$4:E65, E65)=1, 1, 0)</f>
@@ -48234,7 +48258,7 @@
         <v>552</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="G66" s="28">
         <f>IF(COUNTIFS($C$4:C66, C66, $D$4:D66, D66, $E$4:E66, E66)=1, 1, 0)</f>
@@ -48308,7 +48332,7 @@
         <v>565</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="G67" s="28">
         <f>IF(COUNTIFS($C$4:C67, C67, $D$4:D67, D67, $E$4:E67, E67)=1, 1, 0)</f>
@@ -48382,7 +48406,7 @@
         <v>370</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="G68" s="28">
         <f>IF(COUNTIFS($C$4:C68, C68, $D$4:D68, D68, $E$4:E68, E68)=1, 1, 0)</f>
@@ -48456,7 +48480,7 @@
         <v>586</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="G69" s="28">
         <f>IF(COUNTIFS($C$4:C69, C69, $D$4:D69, D69, $E$4:E69, E69)=1, 1, 0)</f>
@@ -48530,7 +48554,7 @@
         <v>600</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="G70" s="28">
         <f>IF(COUNTIFS($C$4:C70, C70, $D$4:D70, D70, $E$4:E70, E70)=1, 1, 0)</f>

--- a/TABLERO_PA_C.xlsx
+++ b/TABLERO_PA_C.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e2a95cfba4fb0187/Escritorio/Tableros de Control/2. Contraloría/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="531" documentId="13_ncr:1_{5037B3AD-B0A2-4521-8F49-D3B2F1605E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB263BA1-7E00-42DC-B7D8-8FC96CE532F1}"/>
+  <xr:revisionPtr revIDLastSave="546" documentId="13_ncr:1_{5037B3AD-B0A2-4521-8F49-D3B2F1605E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{100297DA-0767-435A-85AF-2FF500A1ACD1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="10" xr2:uid="{E38B2051-8614-49B4-943E-B3707D980583}"/>
   </bookViews>
@@ -2771,9 +2771,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -3284,7 +3285,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="242">
+  <cellXfs count="243">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3970,6 +3971,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -27894,6 +27898,76 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3B3AE9AA-616F-416E-8D70-C9530CA01C24}" name="TablaDinámica4" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A19:B23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="19">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="-2"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+    <i i="3">
+      <x v="3"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="4">
+    <dataField name="Suma de Alerta 5" fld="12" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Alerta 10" fld="9" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Alerta 20" fld="10" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Alerta 30" fld="11" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="1">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="0">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A9C7B425-127F-4B5F-B2E3-C2AB4F050E7C}" name="TablaDinámica3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A12:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
@@ -27948,10 +28022,10 @@
     <dataField name="Suma de Total Planes de acción" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="1">
+    <format dxfId="3">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="0">
+    <format dxfId="2">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -27967,7 +28041,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{53017CE7-FCFE-4C73-9C32-3A18A27FC23C}" name="TablaDinámica7" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
   <location ref="F13:G16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
@@ -28142,7 +28216,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DD0BBB6E-FA08-4903-950F-5C10965A7D8D}" name="TablaDinámica6" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A26:B31" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
@@ -28265,76 +28339,6 @@
     <dataField name="Suma de Abiertos" fld="6" baseField="0" baseItem="0"/>
     <dataField name="Suma de Vencidos" fld="7" baseField="0" baseItem="0"/>
     <dataField name="Suma de Finalizados" fld="8" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="3">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="2">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3B3AE9AA-616F-416E-8D70-C9530CA01C24}" name="TablaDinámica4" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A19:B23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="19">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="-2"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-    <i i="2">
-      <x v="2"/>
-    </i>
-    <i i="3">
-      <x v="3"/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="4">
-    <dataField name="Suma de Alerta 5" fld="12" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Alerta 10" fld="9" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Alerta 20" fld="10" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Alerta 30" fld="11" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
     <format dxfId="5">
@@ -28610,7 +28614,14 @@
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CEA19F0D-D53E-4776-BB60-8DAF8AF7C40F}" name="Tabla2" displayName="Tabla2" ref="A1:AJ85" totalsRowShown="0" headerRowDxfId="299" dataDxfId="298" tableBorderDxfId="297">
-  <autoFilter ref="A1:AJ85" xr:uid="{CEA19F0D-D53E-4776-BB60-8DAF8AF7C40F}"/>
+  <autoFilter ref="A1:AJ85" xr:uid="{CEA19F0D-D53E-4776-BB60-8DAF8AF7C40F}">
+    <filterColumn colId="26">
+      <filters>
+        <filter val="Abierta"/>
+        <filter val="Vencida"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="36">
     <tableColumn id="1" xr3:uid="{7A8D3A5E-E004-426E-B403-310EC9C105F1}" name="No." dataDxfId="296"/>
     <tableColumn id="2" xr3:uid="{657020D6-E9B2-4900-BBA6-15C5F0ADC46D}" name="FECHA REPORTE DE LA INFORMACIÓN" dataDxfId="295"/>
@@ -29387,7 +29398,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="3" spans="1:36" ht="125.4">
+    <row r="3" spans="1:36" ht="125.4" hidden="1">
       <c r="A3" s="59">
         <v>118</v>
       </c>
@@ -29496,7 +29507,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="4" spans="1:36" ht="125.4">
+    <row r="4" spans="1:36" ht="125.4" hidden="1">
       <c r="A4" s="59">
         <v>123</v>
       </c>
@@ -29605,7 +29616,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:36" ht="125.4">
+    <row r="5" spans="1:36" ht="125.4" hidden="1">
       <c r="A5" s="59">
         <v>124</v>
       </c>
@@ -29712,7 +29723,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:36" ht="136.80000000000001">
+    <row r="6" spans="1:36" ht="136.80000000000001" hidden="1">
       <c r="A6" s="59">
         <v>189</v>
       </c>
@@ -29821,7 +29832,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="7" spans="1:36" ht="136.80000000000001">
+    <row r="7" spans="1:36" ht="136.80000000000001" hidden="1">
       <c r="A7" s="59">
         <v>190</v>
       </c>
@@ -29930,7 +29941,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="8" spans="1:36" ht="136.80000000000001">
+    <row r="8" spans="1:36" ht="136.80000000000001" hidden="1">
       <c r="A8" s="59">
         <v>191</v>
       </c>
@@ -30039,7 +30050,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="9" spans="1:36" ht="136.80000000000001">
+    <row r="9" spans="1:36" ht="136.80000000000001" hidden="1">
       <c r="A9" s="141">
         <v>193</v>
       </c>
@@ -30148,7 +30159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:36" ht="171">
+    <row r="10" spans="1:36" ht="171" hidden="1">
       <c r="A10" s="59">
         <v>196</v>
       </c>
@@ -30336,7 +30347,7 @@
       </c>
       <c r="AC11" s="232">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AD11" s="233">
         <f t="shared" ca="1" si="1"/>
@@ -30441,7 +30452,7 @@
       </c>
       <c r="AC12" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AD12" s="67">
         <f t="shared" ca="1" si="1"/>
@@ -30467,7 +30478,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="13" spans="1:36" ht="91.2">
+    <row r="13" spans="1:36" ht="91.2" hidden="1">
       <c r="A13" s="59">
         <v>199</v>
       </c>
@@ -30576,7 +30587,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="14" spans="1:36" ht="125.4">
+    <row r="14" spans="1:36" ht="125.4" hidden="1">
       <c r="A14" s="59">
         <v>200</v>
       </c>
@@ -30685,7 +30696,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="15" spans="1:36" ht="159.6">
+    <row r="15" spans="1:36" ht="159.6" hidden="1">
       <c r="A15" s="59">
         <v>213</v>
       </c>
@@ -30855,7 +30866,7 @@
       <c r="V16" s="137" t="s">
         <v>38</v>
       </c>
-      <c r="W16" s="138">
+      <c r="W16" s="242">
         <v>46308</v>
       </c>
       <c r="X16" s="60" t="s">
@@ -30899,7 +30910,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="17" spans="1:36" ht="182.4">
+    <row r="17" spans="1:36" ht="182.4" hidden="1">
       <c r="A17" s="59">
         <v>215</v>
       </c>
@@ -31008,7 +31019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:36" ht="68.400000000000006">
+    <row r="18" spans="1:36" ht="68.400000000000006" hidden="1">
       <c r="A18" s="59">
         <v>221</v>
       </c>
@@ -31117,7 +31128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:36" ht="114">
+    <row r="19" spans="1:36" ht="114" hidden="1">
       <c r="A19" s="59">
         <v>222</v>
       </c>
@@ -31226,7 +31237,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:36" ht="114">
+    <row r="20" spans="1:36" ht="114" hidden="1">
       <c r="A20" s="59">
         <v>223</v>
       </c>
@@ -31396,7 +31407,7 @@
       <c r="V21" s="142" t="s">
         <v>38</v>
       </c>
-      <c r="W21" s="143" t="s">
+      <c r="W21" s="242" t="s">
         <v>775</v>
       </c>
       <c r="X21" s="75" t="s">
@@ -31650,7 +31661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:36" ht="148.19999999999999">
+    <row r="24" spans="1:36" ht="148.19999999999999" hidden="1">
       <c r="A24" s="141">
         <v>244</v>
       </c>
@@ -31759,7 +31770,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="25" spans="1:36" ht="193.8">
+    <row r="25" spans="1:36" ht="193.8" hidden="1">
       <c r="A25" s="59">
         <v>245</v>
       </c>
@@ -31947,7 +31958,7 @@
       </c>
       <c r="AC26" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AD26" s="67">
         <f t="shared" ca="1" si="1"/>
@@ -32052,7 +32063,7 @@
       </c>
       <c r="AC27" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AD27" s="67">
         <f t="shared" ca="1" si="1"/>
@@ -32157,7 +32168,7 @@
       </c>
       <c r="AC28" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AD28" s="67">
         <f t="shared" ca="1" si="1"/>
@@ -32262,7 +32273,7 @@
       </c>
       <c r="AC29" s="66">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AD29" s="67">
         <f t="shared" ca="1" si="1"/>
@@ -32288,7 +32299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:36" ht="91.2">
+    <row r="30" spans="1:36" ht="91.2" hidden="1">
       <c r="A30" s="151">
         <v>259</v>
       </c>
@@ -32397,7 +32408,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="31" spans="1:36" ht="91.2">
+    <row r="31" spans="1:36" ht="91.2" hidden="1">
       <c r="A31" s="141">
         <v>260</v>
       </c>
@@ -32611,7 +32622,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="33" spans="1:36" ht="136.80000000000001">
+    <row r="33" spans="1:36" ht="136.80000000000001" hidden="1">
       <c r="A33" s="141">
         <v>262</v>
       </c>
@@ -32720,7 +32731,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="34" spans="1:36" ht="136.80000000000001">
+    <row r="34" spans="1:36" ht="136.80000000000001" hidden="1">
       <c r="A34" s="59">
         <v>263</v>
       </c>
@@ -32827,7 +32838,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="35" spans="1:36" ht="148.19999999999999">
+    <row r="35" spans="1:36" ht="148.19999999999999" hidden="1">
       <c r="A35" s="59">
         <v>281</v>
       </c>
@@ -32936,7 +32947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:36" ht="136.80000000000001">
+    <row r="36" spans="1:36" ht="136.80000000000001" hidden="1">
       <c r="A36" s="59">
         <v>181</v>
       </c>
@@ -33045,7 +33056,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="37" spans="1:36" ht="91.2">
+    <row r="37" spans="1:36" ht="91.2" hidden="1">
       <c r="A37" s="59">
         <v>182</v>
       </c>
@@ -33152,7 +33163,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="38" spans="1:36" ht="125.4">
+    <row r="38" spans="1:36" ht="125.4" hidden="1">
       <c r="A38" s="59">
         <v>183</v>
       </c>
@@ -33366,7 +33377,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="40" spans="1:36" ht="159.6">
+    <row r="40" spans="1:36" ht="159.6" hidden="1">
       <c r="A40" s="59">
         <v>190</v>
       </c>
@@ -33473,7 +33484,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="41" spans="1:36" ht="102.6">
+    <row r="41" spans="1:36" ht="102.6" hidden="1">
       <c r="A41" s="78">
         <v>191</v>
       </c>
@@ -33582,7 +33593,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="42" spans="1:36" ht="125.4">
+    <row r="42" spans="1:36" ht="125.4" hidden="1">
       <c r="A42" s="59">
         <v>194</v>
       </c>
@@ -33798,7 +33809,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="44" spans="1:36" ht="216.6">
+    <row r="44" spans="1:36" ht="216.6" hidden="1">
       <c r="A44" s="59">
         <v>214</v>
       </c>
@@ -33905,7 +33916,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="45" spans="1:36" ht="125.4">
+    <row r="45" spans="1:36" ht="125.4" hidden="1">
       <c r="A45" s="83">
         <v>215</v>
       </c>
@@ -34012,7 +34023,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="46" spans="1:36" ht="102.6">
+    <row r="46" spans="1:36" ht="102.6" hidden="1">
       <c r="A46" s="78">
         <v>216</v>
       </c>
@@ -34119,7 +34130,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="47" spans="1:36" ht="182.4">
+    <row r="47" spans="1:36" ht="182.4" hidden="1">
       <c r="A47" s="78">
         <v>217</v>
       </c>
@@ -34226,7 +34237,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="48" spans="1:36" ht="131.4" customHeight="1">
+    <row r="48" spans="1:36" ht="131.4" hidden="1" customHeight="1">
       <c r="A48" s="78">
         <v>218</v>
       </c>
@@ -34335,7 +34346,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="49" spans="1:36" ht="171">
+    <row r="49" spans="1:36" ht="171" hidden="1">
       <c r="A49" s="59">
         <v>219</v>
       </c>
@@ -34442,7 +34453,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="50" spans="1:36" ht="205.2">
+    <row r="50" spans="1:36" ht="205.2" hidden="1">
       <c r="A50" s="59">
         <v>220</v>
       </c>
@@ -34549,7 +34560,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="51" spans="1:36" ht="171">
+    <row r="51" spans="1:36" ht="171" hidden="1">
       <c r="A51" s="59">
         <v>223</v>
       </c>
@@ -34656,7 +34667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:36" ht="125.4">
+    <row r="52" spans="1:36" ht="125.4" hidden="1">
       <c r="A52" s="59">
         <v>226</v>
       </c>
@@ -34763,7 +34774,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="53" spans="1:36" ht="125.4">
+    <row r="53" spans="1:36" ht="125.4" hidden="1">
       <c r="A53" s="59">
         <v>227</v>
       </c>
@@ -34870,7 +34881,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="54" spans="1:36" ht="193.8">
+    <row r="54" spans="1:36" ht="193.8" hidden="1">
       <c r="A54" s="59">
         <v>228</v>
       </c>
@@ -34977,7 +34988,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="55" spans="1:36" ht="125.4">
+    <row r="55" spans="1:36" ht="125.4" hidden="1">
       <c r="A55" s="78">
         <v>229</v>
       </c>
@@ -35084,7 +35095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:36" ht="136.80000000000001">
+    <row r="56" spans="1:36" ht="136.80000000000001" hidden="1">
       <c r="A56" s="78">
         <v>230</v>
       </c>
@@ -35191,7 +35202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:36" ht="114">
+    <row r="57" spans="1:36" ht="114" hidden="1">
       <c r="A57" s="59">
         <v>231</v>
       </c>
@@ -35298,7 +35309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:36" ht="171">
+    <row r="58" spans="1:36" ht="171" hidden="1">
       <c r="A58" s="78">
         <v>240</v>
       </c>
@@ -35405,7 +35416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:36" ht="205.2">
+    <row r="59" spans="1:36" ht="205.2" hidden="1">
       <c r="A59" s="59">
         <v>245</v>
       </c>
@@ -35512,7 +35523,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="60" spans="1:36" ht="68.400000000000006">
+    <row r="60" spans="1:36" ht="68.400000000000006" hidden="1">
       <c r="A60" s="78">
         <v>246</v>
       </c>
@@ -35619,7 +35630,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="61" spans="1:36" ht="148.19999999999999">
+    <row r="61" spans="1:36" ht="148.19999999999999" hidden="1">
       <c r="A61" s="78">
         <v>247</v>
       </c>
@@ -35726,7 +35737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:36" ht="228">
+    <row r="62" spans="1:36" ht="228" hidden="1">
       <c r="A62" s="59">
         <v>120</v>
       </c>
@@ -35837,7 +35848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:36" ht="262.2">
+    <row r="63" spans="1:36" ht="262.2" hidden="1">
       <c r="A63" s="78">
         <v>123</v>
       </c>
@@ -35948,7 +35959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:36" ht="273.60000000000002">
+    <row r="64" spans="1:36" ht="273.60000000000002" hidden="1">
       <c r="A64" s="59">
         <v>125</v>
       </c>
@@ -36059,7 +36070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:36" ht="171">
+    <row r="65" spans="1:36" ht="171" hidden="1">
       <c r="A65" s="59">
         <v>184</v>
       </c>
@@ -36172,7 +36183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:36" ht="205.2">
+    <row r="66" spans="1:36" ht="205.2" hidden="1">
       <c r="A66" s="59">
         <v>186</v>
       </c>
@@ -36285,7 +36296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:36" ht="171">
+    <row r="67" spans="1:36" ht="171" hidden="1">
       <c r="A67" s="59">
         <v>187</v>
       </c>
@@ -36398,7 +36409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:36" ht="171">
+    <row r="68" spans="1:36" ht="171" hidden="1">
       <c r="A68" s="59">
         <v>188</v>
       </c>
@@ -36511,7 +36522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:36" ht="193.8">
+    <row r="69" spans="1:36" ht="193.8" hidden="1">
       <c r="A69" s="59">
         <v>213</v>
       </c>
@@ -36622,7 +36633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:36" ht="228">
+    <row r="70" spans="1:36" ht="228" hidden="1">
       <c r="A70" s="59">
         <v>221</v>
       </c>
@@ -36733,7 +36744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:36" ht="239.4">
+    <row r="71" spans="1:36" ht="239.4" hidden="1">
       <c r="A71" s="59">
         <v>222</v>
       </c>
@@ -36844,7 +36855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:36" ht="228">
+    <row r="72" spans="1:36" ht="228" hidden="1">
       <c r="A72" s="78">
         <v>224</v>
       </c>
@@ -36955,7 +36966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:36" ht="239.4">
+    <row r="73" spans="1:36" ht="239.4" hidden="1">
       <c r="A73" s="59">
         <v>225</v>
       </c>
@@ -37068,7 +37079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:36" ht="193.8">
+    <row r="74" spans="1:36" ht="193.8" hidden="1">
       <c r="A74" s="59">
         <v>232</v>
       </c>
@@ -37181,7 +37192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:36" ht="182.4">
+    <row r="75" spans="1:36" ht="182.4" hidden="1">
       <c r="A75" s="59">
         <v>233</v>
       </c>
@@ -37292,7 +37303,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="76" spans="1:36" ht="262.2">
+    <row r="76" spans="1:36" ht="262.2" hidden="1">
       <c r="A76" s="59">
         <v>234</v>
       </c>
@@ -37403,7 +37414,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="77" spans="1:36" ht="205.2">
+    <row r="77" spans="1:36" ht="205.2" hidden="1">
       <c r="A77" s="59">
         <v>235</v>
       </c>
@@ -37516,7 +37527,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="78" spans="1:36" ht="262.2">
+    <row r="78" spans="1:36" ht="262.2" hidden="1">
       <c r="A78" s="59">
         <v>236</v>
       </c>
@@ -37629,7 +37640,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="79" spans="1:36" ht="159.6">
+    <row r="79" spans="1:36" ht="159.6" hidden="1">
       <c r="A79" s="59">
         <v>237</v>
       </c>
@@ -37742,7 +37753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:36" ht="205.2">
+    <row r="80" spans="1:36" ht="205.2" hidden="1">
       <c r="A80" s="59">
         <v>238</v>
       </c>
@@ -37853,7 +37864,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="81" spans="1:36" ht="250.8">
+    <row r="81" spans="1:36" ht="250.8" hidden="1">
       <c r="A81" s="59">
         <v>239</v>
       </c>
@@ -37964,7 +37975,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="82" spans="1:36" ht="125.4">
+    <row r="82" spans="1:36" ht="125.4" hidden="1">
       <c r="A82" s="59">
         <v>241</v>
       </c>
@@ -38075,7 +38086,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="83" spans="1:36" ht="114">
+    <row r="83" spans="1:36" ht="114" hidden="1">
       <c r="A83" s="59">
         <v>242</v>
       </c>
@@ -38186,7 +38197,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="84" spans="1:36" ht="228">
+    <row r="84" spans="1:36" ht="228" hidden="1">
       <c r="A84" s="59">
         <v>243</v>
       </c>
@@ -38297,7 +38308,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="85" spans="1:36" ht="205.2">
+    <row r="85" spans="1:36" ht="205.2" hidden="1">
       <c r="A85" s="59">
         <v>244</v>
       </c>
